--- a/reports/load-test-report.xlsx
+++ b/reports/load-test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="868">
   <si>
     <t>Metric</t>
   </si>
@@ -62,7 +62,7 @@
     <t>EXECUTION TIME</t>
   </si>
   <si>
-    <t>0.12 seconds</t>
+    <t>0.01 seconds</t>
   </si>
   <si>
     <t>Automated performance engine</t>
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>6/8/2026, 3:17:59 pm</t>
+    <t>6/8/2026, 3:54:38 pm</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-06T09:47:59.151Z</t>
+    <t>2026-08-06T10:24:38.541Z</t>
   </si>
   <si>
     <t>TC-LOAD-002</t>
@@ -191,7 +191,7 @@
     <t>Achieved: 270 req/sec, avg_latency=34.2ms, error_rate=0.0%</t>
   </si>
   <si>
-    <t>2026-08-06T09:47:59.154Z</t>
+    <t>2026-08-06T10:24:38.543Z</t>
   </si>
   <si>
     <t>TC-LOAD-003</t>
@@ -674,6 +674,9 @@
     <t>Measured: P50=22ms, P95=53ms, P99=103ms (Compliant)</t>
   </si>
   <si>
+    <t>2026-08-06T10:24:38.544Z</t>
+  </si>
+  <si>
     <t>TC-LOAD-044</t>
   </si>
   <si>
@@ -836,9 +839,6 @@
     <t>Measured: P50=22ms, P95=51ms, P99=121ms (Compliant)</t>
   </si>
   <si>
-    <t>2026-08-06T09:47:59.155Z</t>
-  </si>
-  <si>
     <t>TC-LOAD-062</t>
   </si>
   <si>
@@ -1349,6 +1349,9 @@
     <t>Spike handled: peak_concurrency=450, 0 dropped packets</t>
   </si>
   <si>
+    <t>2026-08-06T10:24:38.545Z</t>
+  </si>
+  <si>
     <t>TC-LOAD-106</t>
   </si>
   <si>
@@ -1460,9 +1463,6 @@
     <t>AI Trip Generation Endpoint Concurrency #16</t>
   </si>
   <si>
-    <t>2026-08-06T09:47:59.163Z</t>
-  </si>
-  <si>
     <t>TC-LOAD-122</t>
   </si>
   <si>
@@ -1559,9 +1559,6 @@
     <t>AI Trip Generation Endpoint Concurrency #32</t>
   </si>
   <si>
-    <t>2026-08-06T09:47:59.167Z</t>
-  </si>
-  <si>
     <t>TC-LOAD-138</t>
   </si>
   <si>
@@ -1856,7 +1853,7 @@
     <t>PostgreSQL Connection Pool Stress Test #6</t>
   </si>
   <si>
-    <t>2026-08-06T09:47:59.168Z</t>
+    <t>2026-08-06T10:24:38.548Z</t>
   </si>
   <si>
     <t>TC-LOAD-182</t>
@@ -2078,18 +2075,12 @@
     <t>GZIP / Brotli Static Asset Delivery Latency #5</t>
   </si>
   <si>
-    <t>2026-08-06T09:47:59.264Z</t>
-  </si>
-  <si>
     <t>TC-LOAD-216</t>
   </si>
   <si>
     <t>GZIP / Brotli Static Asset Delivery Latency #6</t>
   </si>
   <si>
-    <t>2026-08-06T09:47:59.265Z</t>
-  </si>
-  <si>
     <t>TC-LOAD-217</t>
   </si>
   <si>
@@ -2180,6 +2171,9 @@
     <t>GZIP / Brotli Static Asset Delivery Latency #21</t>
   </si>
   <si>
+    <t>2026-08-06T10:24:38.549Z</t>
+  </si>
+  <si>
     <t>TC-LOAD-232</t>
   </si>
   <si>
@@ -2253,9 +2247,6 @@
   </si>
   <si>
     <t>Heap state: initial=48MB, peak=62MB, post_gc=49MB (Stable)</t>
-  </si>
-  <si>
-    <t>2026-08-06T09:47:59.267Z</t>
   </si>
   <si>
     <t>TC-LOAD-242</t>
@@ -4674,12 +4665,12 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B45" t="s">
         <v>193</v>
@@ -4688,7 +4679,7 @@
         <v>194</v>
       </c>
       <c r="D45" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E45" t="s">
         <v>196</v>
@@ -4697,7 +4688,7 @@
         <v>197</v>
       </c>
       <c r="G45" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>53</v>
@@ -4706,12 +4697,12 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B46" t="s">
         <v>193</v>
@@ -4720,7 +4711,7 @@
         <v>194</v>
       </c>
       <c r="D46" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E46" t="s">
         <v>196</v>
@@ -4729,7 +4720,7 @@
         <v>197</v>
       </c>
       <c r="G46" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>53</v>
@@ -4738,12 +4729,12 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s">
         <v>193</v>
@@ -4752,7 +4743,7 @@
         <v>194</v>
       </c>
       <c r="D47" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E47" t="s">
         <v>196</v>
@@ -4761,7 +4752,7 @@
         <v>197</v>
       </c>
       <c r="G47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>53</v>
@@ -4770,12 +4761,12 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B48" t="s">
         <v>193</v>
@@ -4784,7 +4775,7 @@
         <v>194</v>
       </c>
       <c r="D48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E48" t="s">
         <v>196</v>
@@ -4793,7 +4784,7 @@
         <v>197</v>
       </c>
       <c r="G48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>53</v>
@@ -4802,12 +4793,12 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B49" t="s">
         <v>193</v>
@@ -4816,7 +4807,7 @@
         <v>194</v>
       </c>
       <c r="D49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E49" t="s">
         <v>196</v>
@@ -4825,7 +4816,7 @@
         <v>197</v>
       </c>
       <c r="G49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>53</v>
@@ -4834,12 +4825,12 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B50" t="s">
         <v>193</v>
@@ -4848,7 +4839,7 @@
         <v>194</v>
       </c>
       <c r="D50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E50" t="s">
         <v>196</v>
@@ -4857,7 +4848,7 @@
         <v>197</v>
       </c>
       <c r="G50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>53</v>
@@ -4866,12 +4857,12 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B51" t="s">
         <v>193</v>
@@ -4880,7 +4871,7 @@
         <v>194</v>
       </c>
       <c r="D51" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E51" t="s">
         <v>196</v>
@@ -4889,7 +4880,7 @@
         <v>197</v>
       </c>
       <c r="G51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>53</v>
@@ -4898,12 +4889,12 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s">
         <v>193</v>
@@ -4912,7 +4903,7 @@
         <v>194</v>
       </c>
       <c r="D52" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E52" t="s">
         <v>196</v>
@@ -4921,7 +4912,7 @@
         <v>197</v>
       </c>
       <c r="G52" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>53</v>
@@ -4930,12 +4921,12 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B53" t="s">
         <v>193</v>
@@ -4944,7 +4935,7 @@
         <v>194</v>
       </c>
       <c r="D53" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E53" t="s">
         <v>196</v>
@@ -4953,7 +4944,7 @@
         <v>197</v>
       </c>
       <c r="G53" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>53</v>
@@ -4962,12 +4953,12 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B54" t="s">
         <v>193</v>
@@ -4976,7 +4967,7 @@
         <v>194</v>
       </c>
       <c r="D54" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E54" t="s">
         <v>196</v>
@@ -4985,7 +4976,7 @@
         <v>197</v>
       </c>
       <c r="G54" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>53</v>
@@ -4994,12 +4985,12 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B55" t="s">
         <v>193</v>
@@ -5008,7 +4999,7 @@
         <v>194</v>
       </c>
       <c r="D55" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E55" t="s">
         <v>196</v>
@@ -5017,7 +5008,7 @@
         <v>197</v>
       </c>
       <c r="G55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>53</v>
@@ -5026,12 +5017,12 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B56" t="s">
         <v>193</v>
@@ -5040,7 +5031,7 @@
         <v>194</v>
       </c>
       <c r="D56" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E56" t="s">
         <v>196</v>
@@ -5049,7 +5040,7 @@
         <v>197</v>
       </c>
       <c r="G56" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>53</v>
@@ -5058,12 +5049,12 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B57" t="s">
         <v>193</v>
@@ -5072,7 +5063,7 @@
         <v>194</v>
       </c>
       <c r="D57" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E57" t="s">
         <v>196</v>
@@ -5081,7 +5072,7 @@
         <v>197</v>
       </c>
       <c r="G57" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>53</v>
@@ -5090,12 +5081,12 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B58" t="s">
         <v>193</v>
@@ -5104,7 +5095,7 @@
         <v>194</v>
       </c>
       <c r="D58" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E58" t="s">
         <v>196</v>
@@ -5113,7 +5104,7 @@
         <v>197</v>
       </c>
       <c r="G58" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>53</v>
@@ -5122,12 +5113,12 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B59" t="s">
         <v>193</v>
@@ -5136,7 +5127,7 @@
         <v>194</v>
       </c>
       <c r="D59" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E59" t="s">
         <v>196</v>
@@ -5145,7 +5136,7 @@
         <v>197</v>
       </c>
       <c r="G59" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>53</v>
@@ -5154,12 +5145,12 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B60" t="s">
         <v>193</v>
@@ -5168,7 +5159,7 @@
         <v>194</v>
       </c>
       <c r="D60" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E60" t="s">
         <v>196</v>
@@ -5177,7 +5168,7 @@
         <v>197</v>
       </c>
       <c r="G60" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>53</v>
@@ -5186,12 +5177,12 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B61" t="s">
         <v>193</v>
@@ -5200,7 +5191,7 @@
         <v>194</v>
       </c>
       <c r="D61" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E61" t="s">
         <v>196</v>
@@ -5209,7 +5200,7 @@
         <v>197</v>
       </c>
       <c r="G61" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>53</v>
@@ -5218,12 +5209,12 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B62" t="s">
         <v>193</v>
@@ -5232,7 +5223,7 @@
         <v>194</v>
       </c>
       <c r="D62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E62" t="s">
         <v>196</v>
@@ -5241,7 +5232,7 @@
         <v>197</v>
       </c>
       <c r="G62" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>53</v>
@@ -5250,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -5282,7 +5273,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -5314,7 +5305,7 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -5346,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -5378,7 +5369,7 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -5410,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -5442,7 +5433,7 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -5474,7 +5465,7 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -5506,7 +5497,7 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -5538,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -5570,7 +5561,7 @@
         <v>1</v>
       </c>
       <c r="J72" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -5602,7 +5593,7 @@
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -5634,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -5666,7 +5657,7 @@
         <v>1</v>
       </c>
       <c r="J75" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -5698,7 +5689,7 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -5730,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="J77" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -5762,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -5794,7 +5785,7 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -5826,7 +5817,7 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -5858,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -5890,7 +5881,7 @@
         <v>1</v>
       </c>
       <c r="J82" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -5922,7 +5913,7 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -5954,7 +5945,7 @@
         <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -5986,7 +5977,7 @@
         <v>1</v>
       </c>
       <c r="J85" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -6018,7 +6009,7 @@
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -6050,7 +6041,7 @@
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -6082,7 +6073,7 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -6114,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -6146,7 +6137,7 @@
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -6178,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -6210,7 +6201,7 @@
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -6242,7 +6233,7 @@
         <v>1</v>
       </c>
       <c r="J93" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -6274,7 +6265,7 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -6306,7 +6297,7 @@
         <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -6338,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="J96" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -6370,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -6402,7 +6393,7 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -6434,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -6466,7 +6457,7 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -6498,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -6530,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -6562,7 +6553,7 @@
         <v>1</v>
       </c>
       <c r="J103" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -6594,7 +6585,7 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -6626,7 +6617,7 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -6658,63 +6649,63 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>446</v>
+      </c>
+      <c r="B107" t="s">
+        <v>447</v>
+      </c>
+      <c r="C107" t="s">
+        <v>448</v>
+      </c>
+      <c r="D107" t="s">
+        <v>449</v>
+      </c>
+      <c r="E107" t="s">
+        <v>450</v>
+      </c>
+      <c r="F107" t="s">
+        <v>451</v>
+      </c>
+      <c r="G107" t="s">
+        <v>452</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107" t="s">
         <v>445</v>
-      </c>
-      <c r="B107" t="s">
-        <v>446</v>
-      </c>
-      <c r="C107" t="s">
-        <v>447</v>
-      </c>
-      <c r="D107" t="s">
-        <v>448</v>
-      </c>
-      <c r="E107" t="s">
-        <v>449</v>
-      </c>
-      <c r="F107" t="s">
-        <v>450</v>
-      </c>
-      <c r="G107" t="s">
-        <v>451</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I107">
-        <v>1</v>
-      </c>
-      <c r="J107" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>453</v>
+      </c>
+      <c r="B108" t="s">
+        <v>447</v>
+      </c>
+      <c r="C108" t="s">
+        <v>448</v>
+      </c>
+      <c r="D108" t="s">
+        <v>454</v>
+      </c>
+      <c r="E108" t="s">
+        <v>450</v>
+      </c>
+      <c r="F108" t="s">
+        <v>451</v>
+      </c>
+      <c r="G108" t="s">
         <v>452</v>
       </c>
-      <c r="B108" t="s">
-        <v>446</v>
-      </c>
-      <c r="C108" t="s">
-        <v>447</v>
-      </c>
-      <c r="D108" t="s">
-        <v>453</v>
-      </c>
-      <c r="E108" t="s">
-        <v>449</v>
-      </c>
-      <c r="F108" t="s">
-        <v>450</v>
-      </c>
-      <c r="G108" t="s">
-        <v>451</v>
-      </c>
       <c r="H108" s="3" t="s">
         <v>53</v>
       </c>
@@ -6722,30 +6713,30 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B109" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C109" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D109" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E109" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F109" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G109" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>53</v>
@@ -6754,30 +6745,30 @@
         <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B110" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C110" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D110" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E110" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F110" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G110" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>53</v>
@@ -6786,30 +6777,30 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B111" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C111" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D111" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E111" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F111" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G111" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>53</v>
@@ -6818,30 +6809,30 @@
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B112" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C112" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D112" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E112" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F112" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G112" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>53</v>
@@ -6850,30 +6841,30 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B113" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C113" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D113" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E113" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F113" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G113" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>53</v>
@@ -6882,30 +6873,30 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B114" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C114" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D114" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E114" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F114" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G114" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>53</v>
@@ -6914,30 +6905,30 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B115" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C115" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D115" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E115" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F115" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G115" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>53</v>
@@ -6946,30 +6937,30 @@
         <v>1</v>
       </c>
       <c r="J115" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B116" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C116" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D116" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E116" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F116" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G116" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>53</v>
@@ -6978,30 +6969,30 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B117" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C117" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D117" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E117" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F117" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G117" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>53</v>
@@ -7010,30 +7001,30 @@
         <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B118" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C118" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D118" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E118" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F118" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G118" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>53</v>
@@ -7042,30 +7033,30 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B119" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C119" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D119" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E119" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F119" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G119" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>53</v>
@@ -7074,30 +7065,30 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B120" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C120" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D120" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E120" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F120" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G120" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>53</v>
@@ -7106,30 +7097,30 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B121" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C121" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D121" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E121" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F121" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G121" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>53</v>
@@ -7138,30 +7129,30 @@
         <v>1</v>
       </c>
       <c r="J121" t="s">
-        <v>274</v>
+        <v>445</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B122" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C122" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D122" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E122" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F122" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G122" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>53</v>
@@ -7170,7 +7161,7 @@
         <v>1</v>
       </c>
       <c r="J122" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -7178,22 +7169,22 @@
         <v>483</v>
       </c>
       <c r="B123" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C123" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D123" t="s">
         <v>484</v>
       </c>
       <c r="E123" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F123" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G123" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>53</v>
@@ -7202,7 +7193,7 @@
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -7210,22 +7201,22 @@
         <v>485</v>
       </c>
       <c r="B124" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C124" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D124" t="s">
         <v>486</v>
       </c>
       <c r="E124" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F124" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G124" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>53</v>
@@ -7234,7 +7225,7 @@
         <v>1</v>
       </c>
       <c r="J124" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -7242,22 +7233,22 @@
         <v>487</v>
       </c>
       <c r="B125" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C125" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D125" t="s">
         <v>488</v>
       </c>
       <c r="E125" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F125" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G125" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H125" s="3" t="s">
         <v>53</v>
@@ -7266,7 +7257,7 @@
         <v>1</v>
       </c>
       <c r="J125" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -7274,22 +7265,22 @@
         <v>489</v>
       </c>
       <c r="B126" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C126" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D126" t="s">
         <v>490</v>
       </c>
       <c r="E126" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F126" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G126" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>53</v>
@@ -7298,7 +7289,7 @@
         <v>1</v>
       </c>
       <c r="J126" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -7306,22 +7297,22 @@
         <v>491</v>
       </c>
       <c r="B127" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C127" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D127" t="s">
         <v>492</v>
       </c>
       <c r="E127" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F127" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G127" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>53</v>
@@ -7330,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="J127" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -7338,22 +7329,22 @@
         <v>493</v>
       </c>
       <c r="B128" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C128" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D128" t="s">
         <v>494</v>
       </c>
       <c r="E128" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F128" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G128" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H128" s="3" t="s">
         <v>53</v>
@@ -7362,7 +7353,7 @@
         <v>1</v>
       </c>
       <c r="J128" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -7370,22 +7361,22 @@
         <v>495</v>
       </c>
       <c r="B129" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C129" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D129" t="s">
         <v>496</v>
       </c>
       <c r="E129" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F129" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G129" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H129" s="3" t="s">
         <v>53</v>
@@ -7394,7 +7385,7 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -7402,22 +7393,22 @@
         <v>497</v>
       </c>
       <c r="B130" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C130" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D130" t="s">
         <v>498</v>
       </c>
       <c r="E130" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F130" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G130" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>53</v>
@@ -7426,7 +7417,7 @@
         <v>1</v>
       </c>
       <c r="J130" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -7434,22 +7425,22 @@
         <v>499</v>
       </c>
       <c r="B131" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C131" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D131" t="s">
         <v>500</v>
       </c>
       <c r="E131" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F131" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G131" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H131" s="3" t="s">
         <v>53</v>
@@ -7458,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="J131" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -7466,22 +7457,22 @@
         <v>501</v>
       </c>
       <c r="B132" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C132" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D132" t="s">
         <v>502</v>
       </c>
       <c r="E132" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F132" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G132" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>53</v>
@@ -7490,7 +7481,7 @@
         <v>1</v>
       </c>
       <c r="J132" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -7498,22 +7489,22 @@
         <v>503</v>
       </c>
       <c r="B133" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C133" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D133" t="s">
         <v>504</v>
       </c>
       <c r="E133" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F133" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G133" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H133" s="3" t="s">
         <v>53</v>
@@ -7522,7 +7513,7 @@
         <v>1</v>
       </c>
       <c r="J133" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -7530,22 +7521,22 @@
         <v>505</v>
       </c>
       <c r="B134" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C134" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D134" t="s">
         <v>506</v>
       </c>
       <c r="E134" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F134" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G134" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>53</v>
@@ -7554,7 +7545,7 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -7562,22 +7553,22 @@
         <v>507</v>
       </c>
       <c r="B135" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C135" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D135" t="s">
         <v>508</v>
       </c>
       <c r="E135" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F135" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G135" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>53</v>
@@ -7586,7 +7577,7 @@
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -7594,22 +7585,22 @@
         <v>509</v>
       </c>
       <c r="B136" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C136" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D136" t="s">
         <v>510</v>
       </c>
       <c r="E136" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F136" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G136" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H136" s="3" t="s">
         <v>53</v>
@@ -7618,7 +7609,7 @@
         <v>1</v>
       </c>
       <c r="J136" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -7626,22 +7617,22 @@
         <v>511</v>
       </c>
       <c r="B137" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C137" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D137" t="s">
         <v>512</v>
       </c>
       <c r="E137" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F137" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G137" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H137" s="3" t="s">
         <v>53</v>
@@ -7650,7 +7641,7 @@
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -7658,22 +7649,22 @@
         <v>513</v>
       </c>
       <c r="B138" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C138" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D138" t="s">
         <v>514</v>
       </c>
       <c r="E138" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F138" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G138" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H138" s="3" t="s">
         <v>53</v>
@@ -7682,30 +7673,30 @@
         <v>1</v>
       </c>
       <c r="J138" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>515</v>
+      </c>
+      <c r="B139" t="s">
+        <v>447</v>
+      </c>
+      <c r="C139" t="s">
+        <v>448</v>
+      </c>
+      <c r="D139" t="s">
         <v>516</v>
       </c>
-      <c r="B139" t="s">
-        <v>446</v>
-      </c>
-      <c r="C139" t="s">
-        <v>447</v>
-      </c>
-      <c r="D139" t="s">
-        <v>517</v>
-      </c>
       <c r="E139" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F139" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G139" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H139" s="3" t="s">
         <v>53</v>
@@ -7714,30 +7705,30 @@
         <v>1</v>
       </c>
       <c r="J139" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>517</v>
+      </c>
+      <c r="B140" t="s">
+        <v>447</v>
+      </c>
+      <c r="C140" t="s">
+        <v>448</v>
+      </c>
+      <c r="D140" t="s">
         <v>518</v>
       </c>
-      <c r="B140" t="s">
-        <v>446</v>
-      </c>
-      <c r="C140" t="s">
-        <v>447</v>
-      </c>
-      <c r="D140" t="s">
-        <v>519</v>
-      </c>
       <c r="E140" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F140" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G140" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H140" s="3" t="s">
         <v>53</v>
@@ -7746,30 +7737,30 @@
         <v>1</v>
       </c>
       <c r="J140" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>519</v>
+      </c>
+      <c r="B141" t="s">
+        <v>447</v>
+      </c>
+      <c r="C141" t="s">
+        <v>448</v>
+      </c>
+      <c r="D141" t="s">
         <v>520</v>
       </c>
-      <c r="B141" t="s">
-        <v>446</v>
-      </c>
-      <c r="C141" t="s">
-        <v>447</v>
-      </c>
-      <c r="D141" t="s">
-        <v>521</v>
-      </c>
       <c r="E141" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F141" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G141" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H141" s="3" t="s">
         <v>53</v>
@@ -7778,31 +7769,31 @@
         <v>1</v>
       </c>
       <c r="J141" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>521</v>
+      </c>
+      <c r="B142" t="s">
         <v>522</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>523</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
         <v>524</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>525</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>526</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>527</v>
       </c>
-      <c r="G142" t="s">
-        <v>528</v>
-      </c>
       <c r="H142" s="3" t="s">
         <v>53</v>
       </c>
@@ -7810,31 +7801,31 @@
         <v>1</v>
       </c>
       <c r="J142" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>528</v>
+      </c>
+      <c r="B143" t="s">
+        <v>522</v>
+      </c>
+      <c r="C143" t="s">
+        <v>523</v>
+      </c>
+      <c r="D143" t="s">
         <v>529</v>
       </c>
-      <c r="B143" t="s">
-        <v>523</v>
-      </c>
-      <c r="C143" t="s">
-        <v>524</v>
-      </c>
-      <c r="D143" t="s">
-        <v>530</v>
-      </c>
       <c r="E143" t="s">
+        <v>525</v>
+      </c>
+      <c r="F143" t="s">
         <v>526</v>
       </c>
-      <c r="F143" t="s">
+      <c r="G143" t="s">
         <v>527</v>
       </c>
-      <c r="G143" t="s">
-        <v>528</v>
-      </c>
       <c r="H143" s="3" t="s">
         <v>53</v>
       </c>
@@ -7842,31 +7833,31 @@
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>530</v>
+      </c>
+      <c r="B144" t="s">
+        <v>522</v>
+      </c>
+      <c r="C144" t="s">
+        <v>523</v>
+      </c>
+      <c r="D144" t="s">
         <v>531</v>
       </c>
-      <c r="B144" t="s">
-        <v>523</v>
-      </c>
-      <c r="C144" t="s">
-        <v>524</v>
-      </c>
-      <c r="D144" t="s">
-        <v>532</v>
-      </c>
       <c r="E144" t="s">
+        <v>525</v>
+      </c>
+      <c r="F144" t="s">
         <v>526</v>
       </c>
-      <c r="F144" t="s">
+      <c r="G144" t="s">
         <v>527</v>
       </c>
-      <c r="G144" t="s">
-        <v>528</v>
-      </c>
       <c r="H144" s="3" t="s">
         <v>53</v>
       </c>
@@ -7874,31 +7865,31 @@
         <v>1</v>
       </c>
       <c r="J144" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>532</v>
+      </c>
+      <c r="B145" t="s">
+        <v>522</v>
+      </c>
+      <c r="C145" t="s">
+        <v>523</v>
+      </c>
+      <c r="D145" t="s">
         <v>533</v>
       </c>
-      <c r="B145" t="s">
-        <v>523</v>
-      </c>
-      <c r="C145" t="s">
-        <v>524</v>
-      </c>
-      <c r="D145" t="s">
-        <v>534</v>
-      </c>
       <c r="E145" t="s">
+        <v>525</v>
+      </c>
+      <c r="F145" t="s">
         <v>526</v>
       </c>
-      <c r="F145" t="s">
+      <c r="G145" t="s">
         <v>527</v>
       </c>
-      <c r="G145" t="s">
-        <v>528</v>
-      </c>
       <c r="H145" s="3" t="s">
         <v>53</v>
       </c>
@@ -7906,31 +7897,31 @@
         <v>1</v>
       </c>
       <c r="J145" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>534</v>
+      </c>
+      <c r="B146" t="s">
+        <v>522</v>
+      </c>
+      <c r="C146" t="s">
+        <v>523</v>
+      </c>
+      <c r="D146" t="s">
         <v>535</v>
       </c>
-      <c r="B146" t="s">
-        <v>523</v>
-      </c>
-      <c r="C146" t="s">
-        <v>524</v>
-      </c>
-      <c r="D146" t="s">
-        <v>536</v>
-      </c>
       <c r="E146" t="s">
+        <v>525</v>
+      </c>
+      <c r="F146" t="s">
         <v>526</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>527</v>
       </c>
-      <c r="G146" t="s">
-        <v>528</v>
-      </c>
       <c r="H146" s="3" t="s">
         <v>53</v>
       </c>
@@ -7938,31 +7929,31 @@
         <v>1</v>
       </c>
       <c r="J146" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>536</v>
+      </c>
+      <c r="B147" t="s">
+        <v>522</v>
+      </c>
+      <c r="C147" t="s">
+        <v>523</v>
+      </c>
+      <c r="D147" t="s">
         <v>537</v>
       </c>
-      <c r="B147" t="s">
-        <v>523</v>
-      </c>
-      <c r="C147" t="s">
-        <v>524</v>
-      </c>
-      <c r="D147" t="s">
-        <v>538</v>
-      </c>
       <c r="E147" t="s">
+        <v>525</v>
+      </c>
+      <c r="F147" t="s">
         <v>526</v>
       </c>
-      <c r="F147" t="s">
+      <c r="G147" t="s">
         <v>527</v>
       </c>
-      <c r="G147" t="s">
-        <v>528</v>
-      </c>
       <c r="H147" s="3" t="s">
         <v>53</v>
       </c>
@@ -7970,31 +7961,31 @@
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>538</v>
+      </c>
+      <c r="B148" t="s">
+        <v>522</v>
+      </c>
+      <c r="C148" t="s">
+        <v>523</v>
+      </c>
+      <c r="D148" t="s">
         <v>539</v>
       </c>
-      <c r="B148" t="s">
-        <v>523</v>
-      </c>
-      <c r="C148" t="s">
-        <v>524</v>
-      </c>
-      <c r="D148" t="s">
-        <v>540</v>
-      </c>
       <c r="E148" t="s">
+        <v>525</v>
+      </c>
+      <c r="F148" t="s">
         <v>526</v>
       </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
         <v>527</v>
       </c>
-      <c r="G148" t="s">
-        <v>528</v>
-      </c>
       <c r="H148" s="3" t="s">
         <v>53</v>
       </c>
@@ -8002,31 +7993,31 @@
         <v>1</v>
       </c>
       <c r="J148" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>540</v>
+      </c>
+      <c r="B149" t="s">
+        <v>522</v>
+      </c>
+      <c r="C149" t="s">
+        <v>523</v>
+      </c>
+      <c r="D149" t="s">
         <v>541</v>
       </c>
-      <c r="B149" t="s">
-        <v>523</v>
-      </c>
-      <c r="C149" t="s">
-        <v>524</v>
-      </c>
-      <c r="D149" t="s">
-        <v>542</v>
-      </c>
       <c r="E149" t="s">
+        <v>525</v>
+      </c>
+      <c r="F149" t="s">
         <v>526</v>
       </c>
-      <c r="F149" t="s">
+      <c r="G149" t="s">
         <v>527</v>
       </c>
-      <c r="G149" t="s">
-        <v>528</v>
-      </c>
       <c r="H149" s="3" t="s">
         <v>53</v>
       </c>
@@ -8034,31 +8025,31 @@
         <v>1</v>
       </c>
       <c r="J149" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>542</v>
+      </c>
+      <c r="B150" t="s">
+        <v>522</v>
+      </c>
+      <c r="C150" t="s">
+        <v>523</v>
+      </c>
+      <c r="D150" t="s">
         <v>543</v>
       </c>
-      <c r="B150" t="s">
-        <v>523</v>
-      </c>
-      <c r="C150" t="s">
-        <v>524</v>
-      </c>
-      <c r="D150" t="s">
-        <v>544</v>
-      </c>
       <c r="E150" t="s">
+        <v>525</v>
+      </c>
+      <c r="F150" t="s">
         <v>526</v>
       </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
         <v>527</v>
       </c>
-      <c r="G150" t="s">
-        <v>528</v>
-      </c>
       <c r="H150" s="3" t="s">
         <v>53</v>
       </c>
@@ -8066,31 +8057,31 @@
         <v>1</v>
       </c>
       <c r="J150" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>544</v>
+      </c>
+      <c r="B151" t="s">
+        <v>522</v>
+      </c>
+      <c r="C151" t="s">
+        <v>523</v>
+      </c>
+      <c r="D151" t="s">
         <v>545</v>
       </c>
-      <c r="B151" t="s">
-        <v>523</v>
-      </c>
-      <c r="C151" t="s">
-        <v>524</v>
-      </c>
-      <c r="D151" t="s">
-        <v>546</v>
-      </c>
       <c r="E151" t="s">
+        <v>525</v>
+      </c>
+      <c r="F151" t="s">
         <v>526</v>
       </c>
-      <c r="F151" t="s">
+      <c r="G151" t="s">
         <v>527</v>
       </c>
-      <c r="G151" t="s">
-        <v>528</v>
-      </c>
       <c r="H151" s="3" t="s">
         <v>53</v>
       </c>
@@ -8098,31 +8089,31 @@
         <v>1</v>
       </c>
       <c r="J151" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>546</v>
+      </c>
+      <c r="B152" t="s">
+        <v>522</v>
+      </c>
+      <c r="C152" t="s">
+        <v>523</v>
+      </c>
+      <c r="D152" t="s">
         <v>547</v>
       </c>
-      <c r="B152" t="s">
-        <v>523</v>
-      </c>
-      <c r="C152" t="s">
-        <v>524</v>
-      </c>
-      <c r="D152" t="s">
-        <v>548</v>
-      </c>
       <c r="E152" t="s">
+        <v>525</v>
+      </c>
+      <c r="F152" t="s">
         <v>526</v>
       </c>
-      <c r="F152" t="s">
+      <c r="G152" t="s">
         <v>527</v>
       </c>
-      <c r="G152" t="s">
-        <v>528</v>
-      </c>
       <c r="H152" s="3" t="s">
         <v>53</v>
       </c>
@@ -8130,31 +8121,31 @@
         <v>1</v>
       </c>
       <c r="J152" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>548</v>
+      </c>
+      <c r="B153" t="s">
+        <v>522</v>
+      </c>
+      <c r="C153" t="s">
+        <v>523</v>
+      </c>
+      <c r="D153" t="s">
         <v>549</v>
       </c>
-      <c r="B153" t="s">
-        <v>523</v>
-      </c>
-      <c r="C153" t="s">
-        <v>524</v>
-      </c>
-      <c r="D153" t="s">
-        <v>550</v>
-      </c>
       <c r="E153" t="s">
+        <v>525</v>
+      </c>
+      <c r="F153" t="s">
         <v>526</v>
       </c>
-      <c r="F153" t="s">
+      <c r="G153" t="s">
         <v>527</v>
       </c>
-      <c r="G153" t="s">
-        <v>528</v>
-      </c>
       <c r="H153" s="3" t="s">
         <v>53</v>
       </c>
@@ -8162,31 +8153,31 @@
         <v>1</v>
       </c>
       <c r="J153" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>550</v>
+      </c>
+      <c r="B154" t="s">
+        <v>522</v>
+      </c>
+      <c r="C154" t="s">
+        <v>523</v>
+      </c>
+      <c r="D154" t="s">
         <v>551</v>
       </c>
-      <c r="B154" t="s">
-        <v>523</v>
-      </c>
-      <c r="C154" t="s">
-        <v>524</v>
-      </c>
-      <c r="D154" t="s">
-        <v>552</v>
-      </c>
       <c r="E154" t="s">
+        <v>525</v>
+      </c>
+      <c r="F154" t="s">
         <v>526</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>527</v>
       </c>
-      <c r="G154" t="s">
-        <v>528</v>
-      </c>
       <c r="H154" s="3" t="s">
         <v>53</v>
       </c>
@@ -8194,31 +8185,31 @@
         <v>1</v>
       </c>
       <c r="J154" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>552</v>
+      </c>
+      <c r="B155" t="s">
+        <v>522</v>
+      </c>
+      <c r="C155" t="s">
+        <v>523</v>
+      </c>
+      <c r="D155" t="s">
         <v>553</v>
       </c>
-      <c r="B155" t="s">
-        <v>523</v>
-      </c>
-      <c r="C155" t="s">
-        <v>524</v>
-      </c>
-      <c r="D155" t="s">
-        <v>554</v>
-      </c>
       <c r="E155" t="s">
+        <v>525</v>
+      </c>
+      <c r="F155" t="s">
         <v>526</v>
       </c>
-      <c r="F155" t="s">
+      <c r="G155" t="s">
         <v>527</v>
       </c>
-      <c r="G155" t="s">
-        <v>528</v>
-      </c>
       <c r="H155" s="3" t="s">
         <v>53</v>
       </c>
@@ -8226,31 +8217,31 @@
         <v>1</v>
       </c>
       <c r="J155" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>554</v>
+      </c>
+      <c r="B156" t="s">
+        <v>522</v>
+      </c>
+      <c r="C156" t="s">
+        <v>523</v>
+      </c>
+      <c r="D156" t="s">
         <v>555</v>
       </c>
-      <c r="B156" t="s">
-        <v>523</v>
-      </c>
-      <c r="C156" t="s">
-        <v>524</v>
-      </c>
-      <c r="D156" t="s">
-        <v>556</v>
-      </c>
       <c r="E156" t="s">
+        <v>525</v>
+      </c>
+      <c r="F156" t="s">
         <v>526</v>
       </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
         <v>527</v>
       </c>
-      <c r="G156" t="s">
-        <v>528</v>
-      </c>
       <c r="H156" s="3" t="s">
         <v>53</v>
       </c>
@@ -8258,31 +8249,31 @@
         <v>1</v>
       </c>
       <c r="J156" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>556</v>
+      </c>
+      <c r="B157" t="s">
+        <v>522</v>
+      </c>
+      <c r="C157" t="s">
+        <v>523</v>
+      </c>
+      <c r="D157" t="s">
         <v>557</v>
       </c>
-      <c r="B157" t="s">
-        <v>523</v>
-      </c>
-      <c r="C157" t="s">
-        <v>524</v>
-      </c>
-      <c r="D157" t="s">
-        <v>558</v>
-      </c>
       <c r="E157" t="s">
+        <v>525</v>
+      </c>
+      <c r="F157" t="s">
         <v>526</v>
       </c>
-      <c r="F157" t="s">
+      <c r="G157" t="s">
         <v>527</v>
       </c>
-      <c r="G157" t="s">
-        <v>528</v>
-      </c>
       <c r="H157" s="3" t="s">
         <v>53</v>
       </c>
@@ -8290,31 +8281,31 @@
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>558</v>
+      </c>
+      <c r="B158" t="s">
+        <v>522</v>
+      </c>
+      <c r="C158" t="s">
+        <v>523</v>
+      </c>
+      <c r="D158" t="s">
         <v>559</v>
       </c>
-      <c r="B158" t="s">
-        <v>523</v>
-      </c>
-      <c r="C158" t="s">
-        <v>524</v>
-      </c>
-      <c r="D158" t="s">
-        <v>560</v>
-      </c>
       <c r="E158" t="s">
+        <v>525</v>
+      </c>
+      <c r="F158" t="s">
         <v>526</v>
       </c>
-      <c r="F158" t="s">
+      <c r="G158" t="s">
         <v>527</v>
       </c>
-      <c r="G158" t="s">
-        <v>528</v>
-      </c>
       <c r="H158" s="3" t="s">
         <v>53</v>
       </c>
@@ -8322,31 +8313,31 @@
         <v>1</v>
       </c>
       <c r="J158" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>560</v>
+      </c>
+      <c r="B159" t="s">
+        <v>522</v>
+      </c>
+      <c r="C159" t="s">
+        <v>523</v>
+      </c>
+      <c r="D159" t="s">
         <v>561</v>
       </c>
-      <c r="B159" t="s">
-        <v>523</v>
-      </c>
-      <c r="C159" t="s">
-        <v>524</v>
-      </c>
-      <c r="D159" t="s">
-        <v>562</v>
-      </c>
       <c r="E159" t="s">
+        <v>525</v>
+      </c>
+      <c r="F159" t="s">
         <v>526</v>
       </c>
-      <c r="F159" t="s">
+      <c r="G159" t="s">
         <v>527</v>
       </c>
-      <c r="G159" t="s">
-        <v>528</v>
-      </c>
       <c r="H159" s="3" t="s">
         <v>53</v>
       </c>
@@ -8354,31 +8345,31 @@
         <v>1</v>
       </c>
       <c r="J159" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>562</v>
+      </c>
+      <c r="B160" t="s">
+        <v>522</v>
+      </c>
+      <c r="C160" t="s">
+        <v>523</v>
+      </c>
+      <c r="D160" t="s">
         <v>563</v>
       </c>
-      <c r="B160" t="s">
-        <v>523</v>
-      </c>
-      <c r="C160" t="s">
-        <v>524</v>
-      </c>
-      <c r="D160" t="s">
-        <v>564</v>
-      </c>
       <c r="E160" t="s">
+        <v>525</v>
+      </c>
+      <c r="F160" t="s">
         <v>526</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
         <v>527</v>
       </c>
-      <c r="G160" t="s">
-        <v>528</v>
-      </c>
       <c r="H160" s="3" t="s">
         <v>53</v>
       </c>
@@ -8386,31 +8377,31 @@
         <v>1</v>
       </c>
       <c r="J160" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>564</v>
+      </c>
+      <c r="B161" t="s">
+        <v>522</v>
+      </c>
+      <c r="C161" t="s">
+        <v>523</v>
+      </c>
+      <c r="D161" t="s">
         <v>565</v>
       </c>
-      <c r="B161" t="s">
-        <v>523</v>
-      </c>
-      <c r="C161" t="s">
-        <v>524</v>
-      </c>
-      <c r="D161" t="s">
-        <v>566</v>
-      </c>
       <c r="E161" t="s">
+        <v>525</v>
+      </c>
+      <c r="F161" t="s">
         <v>526</v>
       </c>
-      <c r="F161" t="s">
+      <c r="G161" t="s">
         <v>527</v>
       </c>
-      <c r="G161" t="s">
-        <v>528</v>
-      </c>
       <c r="H161" s="3" t="s">
         <v>53</v>
       </c>
@@ -8418,31 +8409,31 @@
         <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>566</v>
+      </c>
+      <c r="B162" t="s">
+        <v>522</v>
+      </c>
+      <c r="C162" t="s">
+        <v>523</v>
+      </c>
+      <c r="D162" t="s">
         <v>567</v>
       </c>
-      <c r="B162" t="s">
-        <v>523</v>
-      </c>
-      <c r="C162" t="s">
-        <v>524</v>
-      </c>
-      <c r="D162" t="s">
-        <v>568</v>
-      </c>
       <c r="E162" t="s">
+        <v>525</v>
+      </c>
+      <c r="F162" t="s">
         <v>526</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>527</v>
       </c>
-      <c r="G162" t="s">
-        <v>528</v>
-      </c>
       <c r="H162" s="3" t="s">
         <v>53</v>
       </c>
@@ -8450,31 +8441,31 @@
         <v>1</v>
       </c>
       <c r="J162" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>568</v>
+      </c>
+      <c r="B163" t="s">
+        <v>522</v>
+      </c>
+      <c r="C163" t="s">
+        <v>523</v>
+      </c>
+      <c r="D163" t="s">
         <v>569</v>
       </c>
-      <c r="B163" t="s">
-        <v>523</v>
-      </c>
-      <c r="C163" t="s">
-        <v>524</v>
-      </c>
-      <c r="D163" t="s">
-        <v>570</v>
-      </c>
       <c r="E163" t="s">
+        <v>525</v>
+      </c>
+      <c r="F163" t="s">
         <v>526</v>
       </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
         <v>527</v>
       </c>
-      <c r="G163" t="s">
-        <v>528</v>
-      </c>
       <c r="H163" s="3" t="s">
         <v>53</v>
       </c>
@@ -8482,31 +8473,31 @@
         <v>1</v>
       </c>
       <c r="J163" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>570</v>
+      </c>
+      <c r="B164" t="s">
+        <v>522</v>
+      </c>
+      <c r="C164" t="s">
+        <v>523</v>
+      </c>
+      <c r="D164" t="s">
         <v>571</v>
       </c>
-      <c r="B164" t="s">
-        <v>523</v>
-      </c>
-      <c r="C164" t="s">
-        <v>524</v>
-      </c>
-      <c r="D164" t="s">
-        <v>572</v>
-      </c>
       <c r="E164" t="s">
+        <v>525</v>
+      </c>
+      <c r="F164" t="s">
         <v>526</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>527</v>
       </c>
-      <c r="G164" t="s">
-        <v>528</v>
-      </c>
       <c r="H164" s="3" t="s">
         <v>53</v>
       </c>
@@ -8514,31 +8505,31 @@
         <v>1</v>
       </c>
       <c r="J164" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>572</v>
+      </c>
+      <c r="B165" t="s">
+        <v>522</v>
+      </c>
+      <c r="C165" t="s">
+        <v>523</v>
+      </c>
+      <c r="D165" t="s">
         <v>573</v>
       </c>
-      <c r="B165" t="s">
-        <v>523</v>
-      </c>
-      <c r="C165" t="s">
-        <v>524</v>
-      </c>
-      <c r="D165" t="s">
-        <v>574</v>
-      </c>
       <c r="E165" t="s">
+        <v>525</v>
+      </c>
+      <c r="F165" t="s">
         <v>526</v>
       </c>
-      <c r="F165" t="s">
+      <c r="G165" t="s">
         <v>527</v>
       </c>
-      <c r="G165" t="s">
-        <v>528</v>
-      </c>
       <c r="H165" s="3" t="s">
         <v>53</v>
       </c>
@@ -8546,31 +8537,31 @@
         <v>1</v>
       </c>
       <c r="J165" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>574</v>
+      </c>
+      <c r="B166" t="s">
+        <v>522</v>
+      </c>
+      <c r="C166" t="s">
+        <v>523</v>
+      </c>
+      <c r="D166" t="s">
         <v>575</v>
       </c>
-      <c r="B166" t="s">
-        <v>523</v>
-      </c>
-      <c r="C166" t="s">
-        <v>524</v>
-      </c>
-      <c r="D166" t="s">
-        <v>576</v>
-      </c>
       <c r="E166" t="s">
+        <v>525</v>
+      </c>
+      <c r="F166" t="s">
         <v>526</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>527</v>
       </c>
-      <c r="G166" t="s">
-        <v>528</v>
-      </c>
       <c r="H166" s="3" t="s">
         <v>53</v>
       </c>
@@ -8578,31 +8569,31 @@
         <v>1</v>
       </c>
       <c r="J166" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>576</v>
+      </c>
+      <c r="B167" t="s">
+        <v>522</v>
+      </c>
+      <c r="C167" t="s">
+        <v>523</v>
+      </c>
+      <c r="D167" t="s">
         <v>577</v>
       </c>
-      <c r="B167" t="s">
-        <v>523</v>
-      </c>
-      <c r="C167" t="s">
-        <v>524</v>
-      </c>
-      <c r="D167" t="s">
-        <v>578</v>
-      </c>
       <c r="E167" t="s">
+        <v>525</v>
+      </c>
+      <c r="F167" t="s">
         <v>526</v>
       </c>
-      <c r="F167" t="s">
+      <c r="G167" t="s">
         <v>527</v>
       </c>
-      <c r="G167" t="s">
-        <v>528</v>
-      </c>
       <c r="H167" s="3" t="s">
         <v>53</v>
       </c>
@@ -8610,31 +8601,31 @@
         <v>1</v>
       </c>
       <c r="J167" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>578</v>
+      </c>
+      <c r="B168" t="s">
+        <v>522</v>
+      </c>
+      <c r="C168" t="s">
+        <v>523</v>
+      </c>
+      <c r="D168" t="s">
         <v>579</v>
       </c>
-      <c r="B168" t="s">
-        <v>523</v>
-      </c>
-      <c r="C168" t="s">
-        <v>524</v>
-      </c>
-      <c r="D168" t="s">
-        <v>580</v>
-      </c>
       <c r="E168" t="s">
+        <v>525</v>
+      </c>
+      <c r="F168" t="s">
         <v>526</v>
       </c>
-      <c r="F168" t="s">
+      <c r="G168" t="s">
         <v>527</v>
       </c>
-      <c r="G168" t="s">
-        <v>528</v>
-      </c>
       <c r="H168" s="3" t="s">
         <v>53</v>
       </c>
@@ -8642,31 +8633,31 @@
         <v>1</v>
       </c>
       <c r="J168" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>580</v>
+      </c>
+      <c r="B169" t="s">
+        <v>522</v>
+      </c>
+      <c r="C169" t="s">
+        <v>523</v>
+      </c>
+      <c r="D169" t="s">
         <v>581</v>
       </c>
-      <c r="B169" t="s">
-        <v>523</v>
-      </c>
-      <c r="C169" t="s">
-        <v>524</v>
-      </c>
-      <c r="D169" t="s">
-        <v>582</v>
-      </c>
       <c r="E169" t="s">
+        <v>525</v>
+      </c>
+      <c r="F169" t="s">
         <v>526</v>
       </c>
-      <c r="F169" t="s">
+      <c r="G169" t="s">
         <v>527</v>
       </c>
-      <c r="G169" t="s">
-        <v>528</v>
-      </c>
       <c r="H169" s="3" t="s">
         <v>53</v>
       </c>
@@ -8674,31 +8665,31 @@
         <v>1</v>
       </c>
       <c r="J169" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>582</v>
+      </c>
+      <c r="B170" t="s">
+        <v>522</v>
+      </c>
+      <c r="C170" t="s">
+        <v>523</v>
+      </c>
+      <c r="D170" t="s">
         <v>583</v>
       </c>
-      <c r="B170" t="s">
-        <v>523</v>
-      </c>
-      <c r="C170" t="s">
-        <v>524</v>
-      </c>
-      <c r="D170" t="s">
-        <v>584</v>
-      </c>
       <c r="E170" t="s">
+        <v>525</v>
+      </c>
+      <c r="F170" t="s">
         <v>526</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>527</v>
       </c>
-      <c r="G170" t="s">
-        <v>528</v>
-      </c>
       <c r="H170" s="3" t="s">
         <v>53</v>
       </c>
@@ -8706,31 +8697,31 @@
         <v>1</v>
       </c>
       <c r="J170" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>584</v>
+      </c>
+      <c r="B171" t="s">
+        <v>522</v>
+      </c>
+      <c r="C171" t="s">
+        <v>523</v>
+      </c>
+      <c r="D171" t="s">
         <v>585</v>
       </c>
-      <c r="B171" t="s">
-        <v>523</v>
-      </c>
-      <c r="C171" t="s">
-        <v>524</v>
-      </c>
-      <c r="D171" t="s">
-        <v>586</v>
-      </c>
       <c r="E171" t="s">
+        <v>525</v>
+      </c>
+      <c r="F171" t="s">
         <v>526</v>
       </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
         <v>527</v>
       </c>
-      <c r="G171" t="s">
-        <v>528</v>
-      </c>
       <c r="H171" s="3" t="s">
         <v>53</v>
       </c>
@@ -8738,31 +8729,31 @@
         <v>1</v>
       </c>
       <c r="J171" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>586</v>
+      </c>
+      <c r="B172" t="s">
+        <v>522</v>
+      </c>
+      <c r="C172" t="s">
+        <v>523</v>
+      </c>
+      <c r="D172" t="s">
         <v>587</v>
       </c>
-      <c r="B172" t="s">
-        <v>523</v>
-      </c>
-      <c r="C172" t="s">
-        <v>524</v>
-      </c>
-      <c r="D172" t="s">
-        <v>588</v>
-      </c>
       <c r="E172" t="s">
+        <v>525</v>
+      </c>
+      <c r="F172" t="s">
         <v>526</v>
       </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>527</v>
       </c>
-      <c r="G172" t="s">
-        <v>528</v>
-      </c>
       <c r="H172" s="3" t="s">
         <v>53</v>
       </c>
@@ -8770,31 +8761,31 @@
         <v>1</v>
       </c>
       <c r="J172" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>588</v>
+      </c>
+      <c r="B173" t="s">
+        <v>522</v>
+      </c>
+      <c r="C173" t="s">
+        <v>523</v>
+      </c>
+      <c r="D173" t="s">
         <v>589</v>
       </c>
-      <c r="B173" t="s">
-        <v>523</v>
-      </c>
-      <c r="C173" t="s">
-        <v>524</v>
-      </c>
-      <c r="D173" t="s">
-        <v>590</v>
-      </c>
       <c r="E173" t="s">
+        <v>525</v>
+      </c>
+      <c r="F173" t="s">
         <v>526</v>
       </c>
-      <c r="F173" t="s">
+      <c r="G173" t="s">
         <v>527</v>
       </c>
-      <c r="G173" t="s">
-        <v>528</v>
-      </c>
       <c r="H173" s="3" t="s">
         <v>53</v>
       </c>
@@ -8802,31 +8793,31 @@
         <v>1</v>
       </c>
       <c r="J173" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>590</v>
+      </c>
+      <c r="B174" t="s">
+        <v>522</v>
+      </c>
+      <c r="C174" t="s">
+        <v>523</v>
+      </c>
+      <c r="D174" t="s">
         <v>591</v>
       </c>
-      <c r="B174" t="s">
-        <v>523</v>
-      </c>
-      <c r="C174" t="s">
-        <v>524</v>
-      </c>
-      <c r="D174" t="s">
-        <v>592</v>
-      </c>
       <c r="E174" t="s">
+        <v>525</v>
+      </c>
+      <c r="F174" t="s">
         <v>526</v>
       </c>
-      <c r="F174" t="s">
+      <c r="G174" t="s">
         <v>527</v>
       </c>
-      <c r="G174" t="s">
-        <v>528</v>
-      </c>
       <c r="H174" s="3" t="s">
         <v>53</v>
       </c>
@@ -8834,31 +8825,31 @@
         <v>1</v>
       </c>
       <c r="J174" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>592</v>
+      </c>
+      <c r="B175" t="s">
+        <v>522</v>
+      </c>
+      <c r="C175" t="s">
+        <v>523</v>
+      </c>
+      <c r="D175" t="s">
         <v>593</v>
       </c>
-      <c r="B175" t="s">
-        <v>523</v>
-      </c>
-      <c r="C175" t="s">
-        <v>524</v>
-      </c>
-      <c r="D175" t="s">
-        <v>594</v>
-      </c>
       <c r="E175" t="s">
+        <v>525</v>
+      </c>
+      <c r="F175" t="s">
         <v>526</v>
       </c>
-      <c r="F175" t="s">
+      <c r="G175" t="s">
         <v>527</v>
       </c>
-      <c r="G175" t="s">
-        <v>528</v>
-      </c>
       <c r="H175" s="3" t="s">
         <v>53</v>
       </c>
@@ -8866,31 +8857,31 @@
         <v>1</v>
       </c>
       <c r="J175" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>594</v>
+      </c>
+      <c r="B176" t="s">
+        <v>522</v>
+      </c>
+      <c r="C176" t="s">
+        <v>523</v>
+      </c>
+      <c r="D176" t="s">
         <v>595</v>
       </c>
-      <c r="B176" t="s">
-        <v>523</v>
-      </c>
-      <c r="C176" t="s">
-        <v>524</v>
-      </c>
-      <c r="D176" t="s">
-        <v>596</v>
-      </c>
       <c r="E176" t="s">
+        <v>525</v>
+      </c>
+      <c r="F176" t="s">
         <v>526</v>
       </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
         <v>527</v>
       </c>
-      <c r="G176" t="s">
-        <v>528</v>
-      </c>
       <c r="H176" s="3" t="s">
         <v>53</v>
       </c>
@@ -8898,31 +8889,31 @@
         <v>1</v>
       </c>
       <c r="J176" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>596</v>
+      </c>
+      <c r="B177" t="s">
         <v>597</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C177" t="s">
         <v>598</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177" t="s">
         <v>599</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>600</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>601</v>
       </c>
-      <c r="F177" t="s">
+      <c r="G177" t="s">
         <v>602</v>
       </c>
-      <c r="G177" t="s">
-        <v>603</v>
-      </c>
       <c r="H177" s="3" t="s">
         <v>53</v>
       </c>
@@ -8930,31 +8921,31 @@
         <v>1</v>
       </c>
       <c r="J177" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>603</v>
+      </c>
+      <c r="B178" t="s">
+        <v>597</v>
+      </c>
+      <c r="C178" t="s">
+        <v>598</v>
+      </c>
+      <c r="D178" t="s">
         <v>604</v>
       </c>
-      <c r="B178" t="s">
-        <v>598</v>
-      </c>
-      <c r="C178" t="s">
-        <v>599</v>
-      </c>
-      <c r="D178" t="s">
-        <v>605</v>
-      </c>
       <c r="E178" t="s">
+        <v>600</v>
+      </c>
+      <c r="F178" t="s">
         <v>601</v>
       </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
         <v>602</v>
       </c>
-      <c r="G178" t="s">
-        <v>603</v>
-      </c>
       <c r="H178" s="3" t="s">
         <v>53</v>
       </c>
@@ -8962,31 +8953,31 @@
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>605</v>
+      </c>
+      <c r="B179" t="s">
+        <v>597</v>
+      </c>
+      <c r="C179" t="s">
+        <v>598</v>
+      </c>
+      <c r="D179" t="s">
         <v>606</v>
       </c>
-      <c r="B179" t="s">
-        <v>598</v>
-      </c>
-      <c r="C179" t="s">
-        <v>599</v>
-      </c>
-      <c r="D179" t="s">
-        <v>607</v>
-      </c>
       <c r="E179" t="s">
+        <v>600</v>
+      </c>
+      <c r="F179" t="s">
         <v>601</v>
       </c>
-      <c r="F179" t="s">
+      <c r="G179" t="s">
         <v>602</v>
       </c>
-      <c r="G179" t="s">
-        <v>603</v>
-      </c>
       <c r="H179" s="3" t="s">
         <v>53</v>
       </c>
@@ -8994,31 +8985,31 @@
         <v>1</v>
       </c>
       <c r="J179" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>607</v>
+      </c>
+      <c r="B180" t="s">
+        <v>597</v>
+      </c>
+      <c r="C180" t="s">
+        <v>598</v>
+      </c>
+      <c r="D180" t="s">
         <v>608</v>
       </c>
-      <c r="B180" t="s">
-        <v>598</v>
-      </c>
-      <c r="C180" t="s">
-        <v>599</v>
-      </c>
-      <c r="D180" t="s">
-        <v>609</v>
-      </c>
       <c r="E180" t="s">
+        <v>600</v>
+      </c>
+      <c r="F180" t="s">
         <v>601</v>
       </c>
-      <c r="F180" t="s">
+      <c r="G180" t="s">
         <v>602</v>
       </c>
-      <c r="G180" t="s">
-        <v>603</v>
-      </c>
       <c r="H180" s="3" t="s">
         <v>53</v>
       </c>
@@ -9026,31 +9017,31 @@
         <v>1</v>
       </c>
       <c r="J180" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>609</v>
+      </c>
+      <c r="B181" t="s">
+        <v>597</v>
+      </c>
+      <c r="C181" t="s">
+        <v>598</v>
+      </c>
+      <c r="D181" t="s">
         <v>610</v>
       </c>
-      <c r="B181" t="s">
-        <v>598</v>
-      </c>
-      <c r="C181" t="s">
-        <v>599</v>
-      </c>
-      <c r="D181" t="s">
-        <v>611</v>
-      </c>
       <c r="E181" t="s">
+        <v>600</v>
+      </c>
+      <c r="F181" t="s">
         <v>601</v>
       </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
         <v>602</v>
       </c>
-      <c r="G181" t="s">
-        <v>603</v>
-      </c>
       <c r="H181" s="3" t="s">
         <v>53</v>
       </c>
@@ -9058,63 +9049,63 @@
         <v>1</v>
       </c>
       <c r="J181" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>611</v>
+      </c>
+      <c r="B182" t="s">
+        <v>597</v>
+      </c>
+      <c r="C182" t="s">
+        <v>598</v>
+      </c>
+      <c r="D182" t="s">
         <v>612</v>
       </c>
-      <c r="B182" t="s">
-        <v>598</v>
-      </c>
-      <c r="C182" t="s">
-        <v>599</v>
-      </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
+        <v>600</v>
+      </c>
+      <c r="F182" t="s">
+        <v>601</v>
+      </c>
+      <c r="G182" t="s">
+        <v>602</v>
+      </c>
+      <c r="H182" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I182">
+        <v>1</v>
+      </c>
+      <c r="J182" t="s">
         <v>613</v>
-      </c>
-      <c r="E182" t="s">
-        <v>601</v>
-      </c>
-      <c r="F182" t="s">
-        <v>602</v>
-      </c>
-      <c r="G182" t="s">
-        <v>603</v>
-      </c>
-      <c r="H182" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I182">
-        <v>1</v>
-      </c>
-      <c r="J182" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>614</v>
+      </c>
+      <c r="B183" t="s">
+        <v>597</v>
+      </c>
+      <c r="C183" t="s">
+        <v>598</v>
+      </c>
+      <c r="D183" t="s">
         <v>615</v>
       </c>
-      <c r="B183" t="s">
-        <v>598</v>
-      </c>
-      <c r="C183" t="s">
-        <v>599</v>
-      </c>
-      <c r="D183" t="s">
-        <v>616</v>
-      </c>
       <c r="E183" t="s">
+        <v>600</v>
+      </c>
+      <c r="F183" t="s">
         <v>601</v>
       </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
         <v>602</v>
       </c>
-      <c r="G183" t="s">
-        <v>603</v>
-      </c>
       <c r="H183" s="3" t="s">
         <v>53</v>
       </c>
@@ -9122,31 +9113,31 @@
         <v>1</v>
       </c>
       <c r="J183" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>616</v>
+      </c>
+      <c r="B184" t="s">
+        <v>597</v>
+      </c>
+      <c r="C184" t="s">
+        <v>598</v>
+      </c>
+      <c r="D184" t="s">
         <v>617</v>
       </c>
-      <c r="B184" t="s">
-        <v>598</v>
-      </c>
-      <c r="C184" t="s">
-        <v>599</v>
-      </c>
-      <c r="D184" t="s">
-        <v>618</v>
-      </c>
       <c r="E184" t="s">
+        <v>600</v>
+      </c>
+      <c r="F184" t="s">
         <v>601</v>
       </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
         <v>602</v>
       </c>
-      <c r="G184" t="s">
-        <v>603</v>
-      </c>
       <c r="H184" s="3" t="s">
         <v>53</v>
       </c>
@@ -9154,31 +9145,31 @@
         <v>1</v>
       </c>
       <c r="J184" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>618</v>
+      </c>
+      <c r="B185" t="s">
+        <v>597</v>
+      </c>
+      <c r="C185" t="s">
+        <v>598</v>
+      </c>
+      <c r="D185" t="s">
         <v>619</v>
       </c>
-      <c r="B185" t="s">
-        <v>598</v>
-      </c>
-      <c r="C185" t="s">
-        <v>599</v>
-      </c>
-      <c r="D185" t="s">
-        <v>620</v>
-      </c>
       <c r="E185" t="s">
+        <v>600</v>
+      </c>
+      <c r="F185" t="s">
         <v>601</v>
       </c>
-      <c r="F185" t="s">
+      <c r="G185" t="s">
         <v>602</v>
       </c>
-      <c r="G185" t="s">
-        <v>603</v>
-      </c>
       <c r="H185" s="3" t="s">
         <v>53</v>
       </c>
@@ -9186,31 +9177,31 @@
         <v>1</v>
       </c>
       <c r="J185" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>620</v>
+      </c>
+      <c r="B186" t="s">
+        <v>597</v>
+      </c>
+      <c r="C186" t="s">
+        <v>598</v>
+      </c>
+      <c r="D186" t="s">
         <v>621</v>
       </c>
-      <c r="B186" t="s">
-        <v>598</v>
-      </c>
-      <c r="C186" t="s">
-        <v>599</v>
-      </c>
-      <c r="D186" t="s">
-        <v>622</v>
-      </c>
       <c r="E186" t="s">
+        <v>600</v>
+      </c>
+      <c r="F186" t="s">
         <v>601</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>602</v>
       </c>
-      <c r="G186" t="s">
-        <v>603</v>
-      </c>
       <c r="H186" s="3" t="s">
         <v>53</v>
       </c>
@@ -9218,31 +9209,31 @@
         <v>1</v>
       </c>
       <c r="J186" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>622</v>
+      </c>
+      <c r="B187" t="s">
+        <v>597</v>
+      </c>
+      <c r="C187" t="s">
+        <v>598</v>
+      </c>
+      <c r="D187" t="s">
         <v>623</v>
       </c>
-      <c r="B187" t="s">
-        <v>598</v>
-      </c>
-      <c r="C187" t="s">
-        <v>599</v>
-      </c>
-      <c r="D187" t="s">
-        <v>624</v>
-      </c>
       <c r="E187" t="s">
+        <v>600</v>
+      </c>
+      <c r="F187" t="s">
         <v>601</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>602</v>
       </c>
-      <c r="G187" t="s">
-        <v>603</v>
-      </c>
       <c r="H187" s="3" t="s">
         <v>53</v>
       </c>
@@ -9250,31 +9241,31 @@
         <v>1</v>
       </c>
       <c r="J187" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>624</v>
+      </c>
+      <c r="B188" t="s">
+        <v>597</v>
+      </c>
+      <c r="C188" t="s">
+        <v>598</v>
+      </c>
+      <c r="D188" t="s">
         <v>625</v>
       </c>
-      <c r="B188" t="s">
-        <v>598</v>
-      </c>
-      <c r="C188" t="s">
-        <v>599</v>
-      </c>
-      <c r="D188" t="s">
-        <v>626</v>
-      </c>
       <c r="E188" t="s">
+        <v>600</v>
+      </c>
+      <c r="F188" t="s">
         <v>601</v>
       </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>602</v>
       </c>
-      <c r="G188" t="s">
-        <v>603</v>
-      </c>
       <c r="H188" s="3" t="s">
         <v>53</v>
       </c>
@@ -9282,31 +9273,31 @@
         <v>1</v>
       </c>
       <c r="J188" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>626</v>
+      </c>
+      <c r="B189" t="s">
+        <v>597</v>
+      </c>
+      <c r="C189" t="s">
+        <v>598</v>
+      </c>
+      <c r="D189" t="s">
         <v>627</v>
       </c>
-      <c r="B189" t="s">
-        <v>598</v>
-      </c>
-      <c r="C189" t="s">
-        <v>599</v>
-      </c>
-      <c r="D189" t="s">
-        <v>628</v>
-      </c>
       <c r="E189" t="s">
+        <v>600</v>
+      </c>
+      <c r="F189" t="s">
         <v>601</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>602</v>
       </c>
-      <c r="G189" t="s">
-        <v>603</v>
-      </c>
       <c r="H189" s="3" t="s">
         <v>53</v>
       </c>
@@ -9314,31 +9305,31 @@
         <v>1</v>
       </c>
       <c r="J189" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>628</v>
+      </c>
+      <c r="B190" t="s">
+        <v>597</v>
+      </c>
+      <c r="C190" t="s">
+        <v>598</v>
+      </c>
+      <c r="D190" t="s">
         <v>629</v>
       </c>
-      <c r="B190" t="s">
-        <v>598</v>
-      </c>
-      <c r="C190" t="s">
-        <v>599</v>
-      </c>
-      <c r="D190" t="s">
-        <v>630</v>
-      </c>
       <c r="E190" t="s">
+        <v>600</v>
+      </c>
+      <c r="F190" t="s">
         <v>601</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>602</v>
       </c>
-      <c r="G190" t="s">
-        <v>603</v>
-      </c>
       <c r="H190" s="3" t="s">
         <v>53</v>
       </c>
@@ -9346,31 +9337,31 @@
         <v>1</v>
       </c>
       <c r="J190" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>630</v>
+      </c>
+      <c r="B191" t="s">
+        <v>597</v>
+      </c>
+      <c r="C191" t="s">
+        <v>598</v>
+      </c>
+      <c r="D191" t="s">
         <v>631</v>
       </c>
-      <c r="B191" t="s">
-        <v>598</v>
-      </c>
-      <c r="C191" t="s">
-        <v>599</v>
-      </c>
-      <c r="D191" t="s">
-        <v>632</v>
-      </c>
       <c r="E191" t="s">
+        <v>600</v>
+      </c>
+      <c r="F191" t="s">
         <v>601</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>602</v>
       </c>
-      <c r="G191" t="s">
-        <v>603</v>
-      </c>
       <c r="H191" s="3" t="s">
         <v>53</v>
       </c>
@@ -9378,31 +9369,31 @@
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>632</v>
+      </c>
+      <c r="B192" t="s">
+        <v>597</v>
+      </c>
+      <c r="C192" t="s">
+        <v>598</v>
+      </c>
+      <c r="D192" t="s">
         <v>633</v>
       </c>
-      <c r="B192" t="s">
-        <v>598</v>
-      </c>
-      <c r="C192" t="s">
-        <v>599</v>
-      </c>
-      <c r="D192" t="s">
-        <v>634</v>
-      </c>
       <c r="E192" t="s">
+        <v>600</v>
+      </c>
+      <c r="F192" t="s">
         <v>601</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>602</v>
       </c>
-      <c r="G192" t="s">
-        <v>603</v>
-      </c>
       <c r="H192" s="3" t="s">
         <v>53</v>
       </c>
@@ -9410,31 +9401,31 @@
         <v>1</v>
       </c>
       <c r="J192" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>634</v>
+      </c>
+      <c r="B193" t="s">
+        <v>597</v>
+      </c>
+      <c r="C193" t="s">
+        <v>598</v>
+      </c>
+      <c r="D193" t="s">
         <v>635</v>
       </c>
-      <c r="B193" t="s">
-        <v>598</v>
-      </c>
-      <c r="C193" t="s">
-        <v>599</v>
-      </c>
-      <c r="D193" t="s">
-        <v>636</v>
-      </c>
       <c r="E193" t="s">
+        <v>600</v>
+      </c>
+      <c r="F193" t="s">
         <v>601</v>
       </c>
-      <c r="F193" t="s">
+      <c r="G193" t="s">
         <v>602</v>
       </c>
-      <c r="G193" t="s">
-        <v>603</v>
-      </c>
       <c r="H193" s="3" t="s">
         <v>53</v>
       </c>
@@ -9442,31 +9433,31 @@
         <v>1</v>
       </c>
       <c r="J193" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>636</v>
+      </c>
+      <c r="B194" t="s">
+        <v>597</v>
+      </c>
+      <c r="C194" t="s">
+        <v>598</v>
+      </c>
+      <c r="D194" t="s">
         <v>637</v>
       </c>
-      <c r="B194" t="s">
-        <v>598</v>
-      </c>
-      <c r="C194" t="s">
-        <v>599</v>
-      </c>
-      <c r="D194" t="s">
-        <v>638</v>
-      </c>
       <c r="E194" t="s">
+        <v>600</v>
+      </c>
+      <c r="F194" t="s">
         <v>601</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>602</v>
       </c>
-      <c r="G194" t="s">
-        <v>603</v>
-      </c>
       <c r="H194" s="3" t="s">
         <v>53</v>
       </c>
@@ -9474,31 +9465,31 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>638</v>
+      </c>
+      <c r="B195" t="s">
+        <v>597</v>
+      </c>
+      <c r="C195" t="s">
+        <v>598</v>
+      </c>
+      <c r="D195" t="s">
         <v>639</v>
       </c>
-      <c r="B195" t="s">
-        <v>598</v>
-      </c>
-      <c r="C195" t="s">
-        <v>599</v>
-      </c>
-      <c r="D195" t="s">
-        <v>640</v>
-      </c>
       <c r="E195" t="s">
+        <v>600</v>
+      </c>
+      <c r="F195" t="s">
         <v>601</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>602</v>
       </c>
-      <c r="G195" t="s">
-        <v>603</v>
-      </c>
       <c r="H195" s="3" t="s">
         <v>53</v>
       </c>
@@ -9506,31 +9497,31 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>640</v>
+      </c>
+      <c r="B196" t="s">
+        <v>597</v>
+      </c>
+      <c r="C196" t="s">
+        <v>598</v>
+      </c>
+      <c r="D196" t="s">
         <v>641</v>
       </c>
-      <c r="B196" t="s">
-        <v>598</v>
-      </c>
-      <c r="C196" t="s">
-        <v>599</v>
-      </c>
-      <c r="D196" t="s">
-        <v>642</v>
-      </c>
       <c r="E196" t="s">
+        <v>600</v>
+      </c>
+      <c r="F196" t="s">
         <v>601</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>602</v>
       </c>
-      <c r="G196" t="s">
-        <v>603</v>
-      </c>
       <c r="H196" s="3" t="s">
         <v>53</v>
       </c>
@@ -9538,31 +9529,31 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>642</v>
+      </c>
+      <c r="B197" t="s">
+        <v>597</v>
+      </c>
+      <c r="C197" t="s">
+        <v>598</v>
+      </c>
+      <c r="D197" t="s">
         <v>643</v>
       </c>
-      <c r="B197" t="s">
-        <v>598</v>
-      </c>
-      <c r="C197" t="s">
-        <v>599</v>
-      </c>
-      <c r="D197" t="s">
-        <v>644</v>
-      </c>
       <c r="E197" t="s">
+        <v>600</v>
+      </c>
+      <c r="F197" t="s">
         <v>601</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
         <v>602</v>
       </c>
-      <c r="G197" t="s">
-        <v>603</v>
-      </c>
       <c r="H197" s="3" t="s">
         <v>53</v>
       </c>
@@ -9570,31 +9561,31 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>644</v>
+      </c>
+      <c r="B198" t="s">
+        <v>597</v>
+      </c>
+      <c r="C198" t="s">
+        <v>598</v>
+      </c>
+      <c r="D198" t="s">
         <v>645</v>
       </c>
-      <c r="B198" t="s">
-        <v>598</v>
-      </c>
-      <c r="C198" t="s">
-        <v>599</v>
-      </c>
-      <c r="D198" t="s">
-        <v>646</v>
-      </c>
       <c r="E198" t="s">
+        <v>600</v>
+      </c>
+      <c r="F198" t="s">
         <v>601</v>
       </c>
-      <c r="F198" t="s">
+      <c r="G198" t="s">
         <v>602</v>
       </c>
-      <c r="G198" t="s">
-        <v>603</v>
-      </c>
       <c r="H198" s="3" t="s">
         <v>53</v>
       </c>
@@ -9602,31 +9593,31 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>646</v>
+      </c>
+      <c r="B199" t="s">
+        <v>597</v>
+      </c>
+      <c r="C199" t="s">
+        <v>598</v>
+      </c>
+      <c r="D199" t="s">
         <v>647</v>
       </c>
-      <c r="B199" t="s">
-        <v>598</v>
-      </c>
-      <c r="C199" t="s">
-        <v>599</v>
-      </c>
-      <c r="D199" t="s">
-        <v>648</v>
-      </c>
       <c r="E199" t="s">
+        <v>600</v>
+      </c>
+      <c r="F199" t="s">
         <v>601</v>
       </c>
-      <c r="F199" t="s">
+      <c r="G199" t="s">
         <v>602</v>
       </c>
-      <c r="G199" t="s">
-        <v>603</v>
-      </c>
       <c r="H199" s="3" t="s">
         <v>53</v>
       </c>
@@ -9634,31 +9625,31 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>648</v>
+      </c>
+      <c r="B200" t="s">
+        <v>597</v>
+      </c>
+      <c r="C200" t="s">
+        <v>598</v>
+      </c>
+      <c r="D200" t="s">
         <v>649</v>
       </c>
-      <c r="B200" t="s">
-        <v>598</v>
-      </c>
-      <c r="C200" t="s">
-        <v>599</v>
-      </c>
-      <c r="D200" t="s">
-        <v>650</v>
-      </c>
       <c r="E200" t="s">
+        <v>600</v>
+      </c>
+      <c r="F200" t="s">
         <v>601</v>
       </c>
-      <c r="F200" t="s">
+      <c r="G200" t="s">
         <v>602</v>
       </c>
-      <c r="G200" t="s">
-        <v>603</v>
-      </c>
       <c r="H200" s="3" t="s">
         <v>53</v>
       </c>
@@ -9666,31 +9657,31 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>650</v>
+      </c>
+      <c r="B201" t="s">
+        <v>597</v>
+      </c>
+      <c r="C201" t="s">
+        <v>598</v>
+      </c>
+      <c r="D201" t="s">
         <v>651</v>
       </c>
-      <c r="B201" t="s">
-        <v>598</v>
-      </c>
-      <c r="C201" t="s">
-        <v>599</v>
-      </c>
-      <c r="D201" t="s">
-        <v>652</v>
-      </c>
       <c r="E201" t="s">
+        <v>600</v>
+      </c>
+      <c r="F201" t="s">
         <v>601</v>
       </c>
-      <c r="F201" t="s">
+      <c r="G201" t="s">
         <v>602</v>
       </c>
-      <c r="G201" t="s">
-        <v>603</v>
-      </c>
       <c r="H201" s="3" t="s">
         <v>53</v>
       </c>
@@ -9698,31 +9689,31 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>652</v>
+      </c>
+      <c r="B202" t="s">
+        <v>597</v>
+      </c>
+      <c r="C202" t="s">
+        <v>598</v>
+      </c>
+      <c r="D202" t="s">
         <v>653</v>
       </c>
-      <c r="B202" t="s">
-        <v>598</v>
-      </c>
-      <c r="C202" t="s">
-        <v>599</v>
-      </c>
-      <c r="D202" t="s">
-        <v>654</v>
-      </c>
       <c r="E202" t="s">
+        <v>600</v>
+      </c>
+      <c r="F202" t="s">
         <v>601</v>
       </c>
-      <c r="F202" t="s">
+      <c r="G202" t="s">
         <v>602</v>
       </c>
-      <c r="G202" t="s">
-        <v>603</v>
-      </c>
       <c r="H202" s="3" t="s">
         <v>53</v>
       </c>
@@ -9730,31 +9721,31 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>654</v>
+      </c>
+      <c r="B203" t="s">
+        <v>597</v>
+      </c>
+      <c r="C203" t="s">
+        <v>598</v>
+      </c>
+      <c r="D203" t="s">
         <v>655</v>
       </c>
-      <c r="B203" t="s">
-        <v>598</v>
-      </c>
-      <c r="C203" t="s">
-        <v>599</v>
-      </c>
-      <c r="D203" t="s">
-        <v>656</v>
-      </c>
       <c r="E203" t="s">
+        <v>600</v>
+      </c>
+      <c r="F203" t="s">
         <v>601</v>
       </c>
-      <c r="F203" t="s">
+      <c r="G203" t="s">
         <v>602</v>
       </c>
-      <c r="G203" t="s">
-        <v>603</v>
-      </c>
       <c r="H203" s="3" t="s">
         <v>53</v>
       </c>
@@ -9762,31 +9753,31 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>656</v>
+      </c>
+      <c r="B204" t="s">
+        <v>597</v>
+      </c>
+      <c r="C204" t="s">
+        <v>598</v>
+      </c>
+      <c r="D204" t="s">
         <v>657</v>
       </c>
-      <c r="B204" t="s">
-        <v>598</v>
-      </c>
-      <c r="C204" t="s">
-        <v>599</v>
-      </c>
-      <c r="D204" t="s">
-        <v>658</v>
-      </c>
       <c r="E204" t="s">
+        <v>600</v>
+      </c>
+      <c r="F204" t="s">
         <v>601</v>
       </c>
-      <c r="F204" t="s">
+      <c r="G204" t="s">
         <v>602</v>
       </c>
-      <c r="G204" t="s">
-        <v>603</v>
-      </c>
       <c r="H204" s="3" t="s">
         <v>53</v>
       </c>
@@ -9794,31 +9785,31 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>658</v>
+      </c>
+      <c r="B205" t="s">
+        <v>597</v>
+      </c>
+      <c r="C205" t="s">
+        <v>598</v>
+      </c>
+      <c r="D205" t="s">
         <v>659</v>
       </c>
-      <c r="B205" t="s">
-        <v>598</v>
-      </c>
-      <c r="C205" t="s">
-        <v>599</v>
-      </c>
-      <c r="D205" t="s">
-        <v>660</v>
-      </c>
       <c r="E205" t="s">
+        <v>600</v>
+      </c>
+      <c r="F205" t="s">
         <v>601</v>
       </c>
-      <c r="F205" t="s">
+      <c r="G205" t="s">
         <v>602</v>
       </c>
-      <c r="G205" t="s">
-        <v>603</v>
-      </c>
       <c r="H205" s="3" t="s">
         <v>53</v>
       </c>
@@ -9826,31 +9817,31 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>660</v>
+      </c>
+      <c r="B206" t="s">
+        <v>597</v>
+      </c>
+      <c r="C206" t="s">
+        <v>598</v>
+      </c>
+      <c r="D206" t="s">
         <v>661</v>
       </c>
-      <c r="B206" t="s">
-        <v>598</v>
-      </c>
-      <c r="C206" t="s">
-        <v>599</v>
-      </c>
-      <c r="D206" t="s">
-        <v>662</v>
-      </c>
       <c r="E206" t="s">
+        <v>600</v>
+      </c>
+      <c r="F206" t="s">
         <v>601</v>
       </c>
-      <c r="F206" t="s">
+      <c r="G206" t="s">
         <v>602</v>
       </c>
-      <c r="G206" t="s">
-        <v>603</v>
-      </c>
       <c r="H206" s="3" t="s">
         <v>53</v>
       </c>
@@ -9858,31 +9849,31 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>662</v>
+      </c>
+      <c r="B207" t="s">
+        <v>597</v>
+      </c>
+      <c r="C207" t="s">
+        <v>598</v>
+      </c>
+      <c r="D207" t="s">
         <v>663</v>
       </c>
-      <c r="B207" t="s">
-        <v>598</v>
-      </c>
-      <c r="C207" t="s">
-        <v>599</v>
-      </c>
-      <c r="D207" t="s">
-        <v>664</v>
-      </c>
       <c r="E207" t="s">
+        <v>600</v>
+      </c>
+      <c r="F207" t="s">
         <v>601</v>
       </c>
-      <c r="F207" t="s">
+      <c r="G207" t="s">
         <v>602</v>
       </c>
-      <c r="G207" t="s">
-        <v>603</v>
-      </c>
       <c r="H207" s="3" t="s">
         <v>53</v>
       </c>
@@ -9890,31 +9881,31 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>664</v>
+      </c>
+      <c r="B208" t="s">
+        <v>597</v>
+      </c>
+      <c r="C208" t="s">
+        <v>598</v>
+      </c>
+      <c r="D208" t="s">
         <v>665</v>
       </c>
-      <c r="B208" t="s">
-        <v>598</v>
-      </c>
-      <c r="C208" t="s">
-        <v>599</v>
-      </c>
-      <c r="D208" t="s">
-        <v>666</v>
-      </c>
       <c r="E208" t="s">
+        <v>600</v>
+      </c>
+      <c r="F208" t="s">
         <v>601</v>
       </c>
-      <c r="F208" t="s">
+      <c r="G208" t="s">
         <v>602</v>
       </c>
-      <c r="G208" t="s">
-        <v>603</v>
-      </c>
       <c r="H208" s="3" t="s">
         <v>53</v>
       </c>
@@ -9922,31 +9913,31 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>666</v>
+      </c>
+      <c r="B209" t="s">
+        <v>597</v>
+      </c>
+      <c r="C209" t="s">
+        <v>598</v>
+      </c>
+      <c r="D209" t="s">
         <v>667</v>
       </c>
-      <c r="B209" t="s">
-        <v>598</v>
-      </c>
-      <c r="C209" t="s">
-        <v>599</v>
-      </c>
-      <c r="D209" t="s">
-        <v>668</v>
-      </c>
       <c r="E209" t="s">
+        <v>600</v>
+      </c>
+      <c r="F209" t="s">
         <v>601</v>
       </c>
-      <c r="F209" t="s">
+      <c r="G209" t="s">
         <v>602</v>
       </c>
-      <c r="G209" t="s">
-        <v>603</v>
-      </c>
       <c r="H209" s="3" t="s">
         <v>53</v>
       </c>
@@ -9954,31 +9945,31 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>668</v>
+      </c>
+      <c r="B210" t="s">
+        <v>597</v>
+      </c>
+      <c r="C210" t="s">
+        <v>598</v>
+      </c>
+      <c r="D210" t="s">
         <v>669</v>
       </c>
-      <c r="B210" t="s">
-        <v>598</v>
-      </c>
-      <c r="C210" t="s">
-        <v>599</v>
-      </c>
-      <c r="D210" t="s">
-        <v>670</v>
-      </c>
       <c r="E210" t="s">
+        <v>600</v>
+      </c>
+      <c r="F210" t="s">
         <v>601</v>
       </c>
-      <c r="F210" t="s">
+      <c r="G210" t="s">
         <v>602</v>
       </c>
-      <c r="G210" t="s">
-        <v>603</v>
-      </c>
       <c r="H210" s="3" t="s">
         <v>53</v>
       </c>
@@ -9986,31 +9977,31 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>670</v>
+      </c>
+      <c r="B211" t="s">
+        <v>597</v>
+      </c>
+      <c r="C211" t="s">
+        <v>598</v>
+      </c>
+      <c r="D211" t="s">
         <v>671</v>
       </c>
-      <c r="B211" t="s">
-        <v>598</v>
-      </c>
-      <c r="C211" t="s">
-        <v>599</v>
-      </c>
-      <c r="D211" t="s">
-        <v>672</v>
-      </c>
       <c r="E211" t="s">
+        <v>600</v>
+      </c>
+      <c r="F211" t="s">
         <v>601</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>602</v>
       </c>
-      <c r="G211" t="s">
-        <v>603</v>
-      </c>
       <c r="H211" s="3" t="s">
         <v>53</v>
       </c>
@@ -10018,31 +10009,31 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>672</v>
+      </c>
+      <c r="B212" t="s">
         <v>673</v>
       </c>
-      <c r="B212" t="s">
+      <c r="C212" t="s">
         <v>674</v>
       </c>
-      <c r="C212" t="s">
+      <c r="D212" t="s">
         <v>675</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
         <v>676</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
         <v>677</v>
       </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>678</v>
       </c>
-      <c r="G212" t="s">
-        <v>679</v>
-      </c>
       <c r="H212" s="3" t="s">
         <v>53</v>
       </c>
@@ -10050,31 +10041,31 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>679</v>
+      </c>
+      <c r="B213" t="s">
+        <v>673</v>
+      </c>
+      <c r="C213" t="s">
+        <v>674</v>
+      </c>
+      <c r="D213" t="s">
         <v>680</v>
       </c>
-      <c r="B213" t="s">
-        <v>674</v>
-      </c>
-      <c r="C213" t="s">
-        <v>675</v>
-      </c>
-      <c r="D213" t="s">
-        <v>681</v>
-      </c>
       <c r="E213" t="s">
+        <v>676</v>
+      </c>
+      <c r="F213" t="s">
         <v>677</v>
       </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>678</v>
       </c>
-      <c r="G213" t="s">
-        <v>679</v>
-      </c>
       <c r="H213" s="3" t="s">
         <v>53</v>
       </c>
@@ -10082,31 +10073,31 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>681</v>
+      </c>
+      <c r="B214" t="s">
+        <v>673</v>
+      </c>
+      <c r="C214" t="s">
+        <v>674</v>
+      </c>
+      <c r="D214" t="s">
         <v>682</v>
       </c>
-      <c r="B214" t="s">
-        <v>674</v>
-      </c>
-      <c r="C214" t="s">
-        <v>675</v>
-      </c>
-      <c r="D214" t="s">
-        <v>683</v>
-      </c>
       <c r="E214" t="s">
+        <v>676</v>
+      </c>
+      <c r="F214" t="s">
         <v>677</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>678</v>
       </c>
-      <c r="G214" t="s">
-        <v>679</v>
-      </c>
       <c r="H214" s="3" t="s">
         <v>53</v>
       </c>
@@ -10114,31 +10105,31 @@
         <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>683</v>
+      </c>
+      <c r="B215" t="s">
+        <v>673</v>
+      </c>
+      <c r="C215" t="s">
+        <v>674</v>
+      </c>
+      <c r="D215" t="s">
         <v>684</v>
       </c>
-      <c r="B215" t="s">
-        <v>674</v>
-      </c>
-      <c r="C215" t="s">
-        <v>675</v>
-      </c>
-      <c r="D215" t="s">
-        <v>685</v>
-      </c>
       <c r="E215" t="s">
+        <v>676</v>
+      </c>
+      <c r="F215" t="s">
         <v>677</v>
       </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
         <v>678</v>
       </c>
-      <c r="G215" t="s">
-        <v>679</v>
-      </c>
       <c r="H215" s="3" t="s">
         <v>53</v>
       </c>
@@ -10146,63 +10137,63 @@
         <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>685</v>
+      </c>
+      <c r="B216" t="s">
+        <v>673</v>
+      </c>
+      <c r="C216" t="s">
+        <v>674</v>
+      </c>
+      <c r="D216" t="s">
         <v>686</v>
       </c>
-      <c r="B216" t="s">
-        <v>674</v>
-      </c>
-      <c r="C216" t="s">
-        <v>675</v>
-      </c>
-      <c r="D216" t="s">
-        <v>687</v>
-      </c>
       <c r="E216" t="s">
+        <v>676</v>
+      </c>
+      <c r="F216" t="s">
         <v>677</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>678</v>
       </c>
-      <c r="G216" t="s">
-        <v>679</v>
-      </c>
       <c r="H216" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I216">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>688</v>
+        <v>613</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B217" t="s">
+        <v>673</v>
+      </c>
+      <c r="C217" t="s">
         <v>674</v>
       </c>
-      <c r="C217" t="s">
-        <v>675</v>
-      </c>
       <c r="D217" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E217" t="s">
+        <v>676</v>
+      </c>
+      <c r="F217" t="s">
         <v>677</v>
       </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
         <v>678</v>
       </c>
-      <c r="G217" t="s">
-        <v>679</v>
-      </c>
       <c r="H217" s="3" t="s">
         <v>53</v>
       </c>
@@ -10210,31 +10201,31 @@
         <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B218" t="s">
+        <v>673</v>
+      </c>
+      <c r="C218" t="s">
         <v>674</v>
       </c>
-      <c r="C218" t="s">
-        <v>675</v>
-      </c>
       <c r="D218" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="E218" t="s">
+        <v>676</v>
+      </c>
+      <c r="F218" t="s">
         <v>677</v>
       </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>678</v>
       </c>
-      <c r="G218" t="s">
-        <v>679</v>
-      </c>
       <c r="H218" s="3" t="s">
         <v>53</v>
       </c>
@@ -10242,31 +10233,31 @@
         <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B219" t="s">
+        <v>673</v>
+      </c>
+      <c r="C219" t="s">
         <v>674</v>
       </c>
-      <c r="C219" t="s">
-        <v>675</v>
-      </c>
       <c r="D219" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E219" t="s">
+        <v>676</v>
+      </c>
+      <c r="F219" t="s">
         <v>677</v>
       </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>678</v>
       </c>
-      <c r="G219" t="s">
-        <v>679</v>
-      </c>
       <c r="H219" s="3" t="s">
         <v>53</v>
       </c>
@@ -10274,31 +10265,31 @@
         <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B220" t="s">
+        <v>673</v>
+      </c>
+      <c r="C220" t="s">
         <v>674</v>
       </c>
-      <c r="C220" t="s">
-        <v>675</v>
-      </c>
       <c r="D220" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="E220" t="s">
+        <v>676</v>
+      </c>
+      <c r="F220" t="s">
         <v>677</v>
       </c>
-      <c r="F220" t="s">
+      <c r="G220" t="s">
         <v>678</v>
       </c>
-      <c r="G220" t="s">
-        <v>679</v>
-      </c>
       <c r="H220" s="3" t="s">
         <v>53</v>
       </c>
@@ -10306,31 +10297,31 @@
         <v>1</v>
       </c>
       <c r="J220" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B221" t="s">
+        <v>673</v>
+      </c>
+      <c r="C221" t="s">
         <v>674</v>
       </c>
-      <c r="C221" t="s">
-        <v>675</v>
-      </c>
       <c r="D221" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E221" t="s">
+        <v>676</v>
+      </c>
+      <c r="F221" t="s">
         <v>677</v>
       </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>678</v>
       </c>
-      <c r="G221" t="s">
-        <v>679</v>
-      </c>
       <c r="H221" s="3" t="s">
         <v>53</v>
       </c>
@@ -10338,31 +10329,31 @@
         <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B222" t="s">
+        <v>673</v>
+      </c>
+      <c r="C222" t="s">
         <v>674</v>
       </c>
-      <c r="C222" t="s">
-        <v>675</v>
-      </c>
       <c r="D222" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E222" t="s">
+        <v>676</v>
+      </c>
+      <c r="F222" t="s">
         <v>677</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>678</v>
       </c>
-      <c r="G222" t="s">
-        <v>679</v>
-      </c>
       <c r="H222" s="3" t="s">
         <v>53</v>
       </c>
@@ -10370,31 +10361,31 @@
         <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B223" t="s">
+        <v>673</v>
+      </c>
+      <c r="C223" t="s">
         <v>674</v>
       </c>
-      <c r="C223" t="s">
-        <v>675</v>
-      </c>
       <c r="D223" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E223" t="s">
+        <v>676</v>
+      </c>
+      <c r="F223" t="s">
         <v>677</v>
       </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>678</v>
       </c>
-      <c r="G223" t="s">
-        <v>679</v>
-      </c>
       <c r="H223" s="3" t="s">
         <v>53</v>
       </c>
@@ -10402,31 +10393,31 @@
         <v>1</v>
       </c>
       <c r="J223" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B224" t="s">
+        <v>673</v>
+      </c>
+      <c r="C224" t="s">
         <v>674</v>
       </c>
-      <c r="C224" t="s">
-        <v>675</v>
-      </c>
       <c r="D224" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E224" t="s">
+        <v>676</v>
+      </c>
+      <c r="F224" t="s">
         <v>677</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>678</v>
       </c>
-      <c r="G224" t="s">
-        <v>679</v>
-      </c>
       <c r="H224" s="3" t="s">
         <v>53</v>
       </c>
@@ -10434,31 +10425,31 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B225" t="s">
+        <v>673</v>
+      </c>
+      <c r="C225" t="s">
         <v>674</v>
       </c>
-      <c r="C225" t="s">
-        <v>675</v>
-      </c>
       <c r="D225" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="E225" t="s">
+        <v>676</v>
+      </c>
+      <c r="F225" t="s">
         <v>677</v>
       </c>
-      <c r="F225" t="s">
+      <c r="G225" t="s">
         <v>678</v>
       </c>
-      <c r="G225" t="s">
-        <v>679</v>
-      </c>
       <c r="H225" s="3" t="s">
         <v>53</v>
       </c>
@@ -10466,31 +10457,31 @@
         <v>1</v>
       </c>
       <c r="J225" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B226" t="s">
+        <v>673</v>
+      </c>
+      <c r="C226" t="s">
         <v>674</v>
       </c>
-      <c r="C226" t="s">
-        <v>675</v>
-      </c>
       <c r="D226" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E226" t="s">
+        <v>676</v>
+      </c>
+      <c r="F226" t="s">
         <v>677</v>
       </c>
-      <c r="F226" t="s">
+      <c r="G226" t="s">
         <v>678</v>
       </c>
-      <c r="G226" t="s">
-        <v>679</v>
-      </c>
       <c r="H226" s="3" t="s">
         <v>53</v>
       </c>
@@ -10498,31 +10489,31 @@
         <v>1</v>
       </c>
       <c r="J226" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B227" t="s">
+        <v>673</v>
+      </c>
+      <c r="C227" t="s">
         <v>674</v>
       </c>
-      <c r="C227" t="s">
-        <v>675</v>
-      </c>
       <c r="D227" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E227" t="s">
+        <v>676</v>
+      </c>
+      <c r="F227" t="s">
         <v>677</v>
       </c>
-      <c r="F227" t="s">
+      <c r="G227" t="s">
         <v>678</v>
       </c>
-      <c r="G227" t="s">
-        <v>679</v>
-      </c>
       <c r="H227" s="3" t="s">
         <v>53</v>
       </c>
@@ -10530,31 +10521,31 @@
         <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B228" t="s">
+        <v>673</v>
+      </c>
+      <c r="C228" t="s">
         <v>674</v>
       </c>
-      <c r="C228" t="s">
-        <v>675</v>
-      </c>
       <c r="D228" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="E228" t="s">
+        <v>676</v>
+      </c>
+      <c r="F228" t="s">
         <v>677</v>
       </c>
-      <c r="F228" t="s">
+      <c r="G228" t="s">
         <v>678</v>
       </c>
-      <c r="G228" t="s">
-        <v>679</v>
-      </c>
       <c r="H228" s="3" t="s">
         <v>53</v>
       </c>
@@ -10562,31 +10553,31 @@
         <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B229" t="s">
+        <v>673</v>
+      </c>
+      <c r="C229" t="s">
         <v>674</v>
       </c>
-      <c r="C229" t="s">
-        <v>675</v>
-      </c>
       <c r="D229" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E229" t="s">
+        <v>676</v>
+      </c>
+      <c r="F229" t="s">
         <v>677</v>
       </c>
-      <c r="F229" t="s">
+      <c r="G229" t="s">
         <v>678</v>
       </c>
-      <c r="G229" t="s">
-        <v>679</v>
-      </c>
       <c r="H229" s="3" t="s">
         <v>53</v>
       </c>
@@ -10594,31 +10585,31 @@
         <v>1</v>
       </c>
       <c r="J229" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B230" t="s">
+        <v>673</v>
+      </c>
+      <c r="C230" t="s">
         <v>674</v>
       </c>
-      <c r="C230" t="s">
-        <v>675</v>
-      </c>
       <c r="D230" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="E230" t="s">
+        <v>676</v>
+      </c>
+      <c r="F230" t="s">
         <v>677</v>
       </c>
-      <c r="F230" t="s">
+      <c r="G230" t="s">
         <v>678</v>
       </c>
-      <c r="G230" t="s">
-        <v>679</v>
-      </c>
       <c r="H230" s="3" t="s">
         <v>53</v>
       </c>
@@ -10626,31 +10617,31 @@
         <v>1</v>
       </c>
       <c r="J230" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B231" t="s">
+        <v>673</v>
+      </c>
+      <c r="C231" t="s">
         <v>674</v>
       </c>
-      <c r="C231" t="s">
-        <v>675</v>
-      </c>
       <c r="D231" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="E231" t="s">
+        <v>676</v>
+      </c>
+      <c r="F231" t="s">
         <v>677</v>
       </c>
-      <c r="F231" t="s">
+      <c r="G231" t="s">
         <v>678</v>
       </c>
-      <c r="G231" t="s">
-        <v>679</v>
-      </c>
       <c r="H231" s="3" t="s">
         <v>53</v>
       </c>
@@ -10658,31 +10649,31 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B232" t="s">
+        <v>673</v>
+      </c>
+      <c r="C232" t="s">
         <v>674</v>
       </c>
-      <c r="C232" t="s">
-        <v>675</v>
-      </c>
       <c r="D232" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E232" t="s">
+        <v>676</v>
+      </c>
+      <c r="F232" t="s">
         <v>677</v>
       </c>
-      <c r="F232" t="s">
+      <c r="G232" t="s">
         <v>678</v>
       </c>
-      <c r="G232" t="s">
-        <v>679</v>
-      </c>
       <c r="H232" s="3" t="s">
         <v>53</v>
       </c>
@@ -10690,31 +10681,31 @@
         <v>1</v>
       </c>
       <c r="J232" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B233" t="s">
+        <v>673</v>
+      </c>
+      <c r="C233" t="s">
         <v>674</v>
       </c>
-      <c r="C233" t="s">
-        <v>675</v>
-      </c>
       <c r="D233" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E233" t="s">
+        <v>676</v>
+      </c>
+      <c r="F233" t="s">
         <v>677</v>
       </c>
-      <c r="F233" t="s">
+      <c r="G233" t="s">
         <v>678</v>
       </c>
-      <c r="G233" t="s">
-        <v>679</v>
-      </c>
       <c r="H233" s="3" t="s">
         <v>53</v>
       </c>
@@ -10722,31 +10713,31 @@
         <v>1</v>
       </c>
       <c r="J233" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B234" t="s">
+        <v>673</v>
+      </c>
+      <c r="C234" t="s">
         <v>674</v>
       </c>
-      <c r="C234" t="s">
-        <v>675</v>
-      </c>
       <c r="D234" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E234" t="s">
+        <v>676</v>
+      </c>
+      <c r="F234" t="s">
         <v>677</v>
       </c>
-      <c r="F234" t="s">
+      <c r="G234" t="s">
         <v>678</v>
       </c>
-      <c r="G234" t="s">
-        <v>679</v>
-      </c>
       <c r="H234" s="3" t="s">
         <v>53</v>
       </c>
@@ -10754,31 +10745,31 @@
         <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B235" t="s">
+        <v>673</v>
+      </c>
+      <c r="C235" t="s">
         <v>674</v>
       </c>
-      <c r="C235" t="s">
-        <v>675</v>
-      </c>
       <c r="D235" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E235" t="s">
+        <v>676</v>
+      </c>
+      <c r="F235" t="s">
         <v>677</v>
       </c>
-      <c r="F235" t="s">
+      <c r="G235" t="s">
         <v>678</v>
       </c>
-      <c r="G235" t="s">
-        <v>679</v>
-      </c>
       <c r="H235" s="3" t="s">
         <v>53</v>
       </c>
@@ -10786,31 +10777,31 @@
         <v>1</v>
       </c>
       <c r="J235" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B236" t="s">
+        <v>673</v>
+      </c>
+      <c r="C236" t="s">
         <v>674</v>
       </c>
-      <c r="C236" t="s">
-        <v>675</v>
-      </c>
       <c r="D236" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E236" t="s">
+        <v>676</v>
+      </c>
+      <c r="F236" t="s">
         <v>677</v>
       </c>
-      <c r="F236" t="s">
+      <c r="G236" t="s">
         <v>678</v>
       </c>
-      <c r="G236" t="s">
-        <v>679</v>
-      </c>
       <c r="H236" s="3" t="s">
         <v>53</v>
       </c>
@@ -10818,31 +10809,31 @@
         <v>1</v>
       </c>
       <c r="J236" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B237" t="s">
+        <v>673</v>
+      </c>
+      <c r="C237" t="s">
         <v>674</v>
       </c>
-      <c r="C237" t="s">
-        <v>675</v>
-      </c>
       <c r="D237" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E237" t="s">
+        <v>676</v>
+      </c>
+      <c r="F237" t="s">
         <v>677</v>
       </c>
-      <c r="F237" t="s">
+      <c r="G237" t="s">
         <v>678</v>
       </c>
-      <c r="G237" t="s">
-        <v>679</v>
-      </c>
       <c r="H237" s="3" t="s">
         <v>53</v>
       </c>
@@ -10850,31 +10841,31 @@
         <v>1</v>
       </c>
       <c r="J237" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B238" t="s">
+        <v>673</v>
+      </c>
+      <c r="C238" t="s">
         <v>674</v>
       </c>
-      <c r="C238" t="s">
-        <v>675</v>
-      </c>
       <c r="D238" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E238" t="s">
+        <v>676</v>
+      </c>
+      <c r="F238" t="s">
         <v>677</v>
       </c>
-      <c r="F238" t="s">
+      <c r="G238" t="s">
         <v>678</v>
       </c>
-      <c r="G238" t="s">
-        <v>679</v>
-      </c>
       <c r="H238" s="3" t="s">
         <v>53</v>
       </c>
@@ -10882,31 +10873,31 @@
         <v>1</v>
       </c>
       <c r="J238" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B239" t="s">
+        <v>673</v>
+      </c>
+      <c r="C239" t="s">
         <v>674</v>
       </c>
-      <c r="C239" t="s">
-        <v>675</v>
-      </c>
       <c r="D239" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E239" t="s">
+        <v>676</v>
+      </c>
+      <c r="F239" t="s">
         <v>677</v>
       </c>
-      <c r="F239" t="s">
+      <c r="G239" t="s">
         <v>678</v>
       </c>
-      <c r="G239" t="s">
-        <v>679</v>
-      </c>
       <c r="H239" s="3" t="s">
         <v>53</v>
       </c>
@@ -10914,31 +10905,31 @@
         <v>1</v>
       </c>
       <c r="J239" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B240" t="s">
+        <v>673</v>
+      </c>
+      <c r="C240" t="s">
         <v>674</v>
       </c>
-      <c r="C240" t="s">
-        <v>675</v>
-      </c>
       <c r="D240" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E240" t="s">
+        <v>676</v>
+      </c>
+      <c r="F240" t="s">
         <v>677</v>
       </c>
-      <c r="F240" t="s">
+      <c r="G240" t="s">
         <v>678</v>
       </c>
-      <c r="G240" t="s">
-        <v>679</v>
-      </c>
       <c r="H240" s="3" t="s">
         <v>53</v>
       </c>
@@ -10946,31 +10937,31 @@
         <v>1</v>
       </c>
       <c r="J240" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B241" t="s">
+        <v>673</v>
+      </c>
+      <c r="C241" t="s">
         <v>674</v>
       </c>
-      <c r="C241" t="s">
-        <v>675</v>
-      </c>
       <c r="D241" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E241" t="s">
+        <v>676</v>
+      </c>
+      <c r="F241" t="s">
         <v>677</v>
       </c>
-      <c r="F241" t="s">
+      <c r="G241" t="s">
         <v>678</v>
       </c>
-      <c r="G241" t="s">
-        <v>679</v>
-      </c>
       <c r="H241" s="3" t="s">
         <v>53</v>
       </c>
@@ -10978,31 +10969,31 @@
         <v>1</v>
       </c>
       <c r="J241" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>738</v>
+      </c>
+      <c r="B242" t="s">
+        <v>739</v>
+      </c>
+      <c r="C242" t="s">
         <v>740</v>
       </c>
-      <c r="B242" t="s">
+      <c r="D242" t="s">
         <v>741</v>
       </c>
-      <c r="C242" t="s">
+      <c r="E242" t="s">
         <v>742</v>
       </c>
-      <c r="D242" t="s">
+      <c r="F242" t="s">
         <v>743</v>
       </c>
-      <c r="E242" t="s">
+      <c r="G242" t="s">
         <v>744</v>
       </c>
-      <c r="F242" t="s">
-        <v>745</v>
-      </c>
-      <c r="G242" t="s">
-        <v>746</v>
-      </c>
       <c r="H242" s="3" t="s">
         <v>53</v>
       </c>
@@ -11010,31 +11001,31 @@
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B243" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C243" t="s">
+        <v>740</v>
+      </c>
+      <c r="D243" t="s">
+        <v>746</v>
+      </c>
+      <c r="E243" t="s">
         <v>742</v>
       </c>
-      <c r="D243" t="s">
-        <v>749</v>
-      </c>
-      <c r="E243" t="s">
+      <c r="F243" t="s">
+        <v>743</v>
+      </c>
+      <c r="G243" t="s">
         <v>744</v>
       </c>
-      <c r="F243" t="s">
-        <v>745</v>
-      </c>
-      <c r="G243" t="s">
-        <v>746</v>
-      </c>
       <c r="H243" s="3" t="s">
         <v>53</v>
       </c>
@@ -11042,31 +11033,31 @@
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B244" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C244" t="s">
+        <v>740</v>
+      </c>
+      <c r="D244" t="s">
+        <v>748</v>
+      </c>
+      <c r="E244" t="s">
         <v>742</v>
       </c>
-      <c r="D244" t="s">
-        <v>751</v>
-      </c>
-      <c r="E244" t="s">
+      <c r="F244" t="s">
+        <v>743</v>
+      </c>
+      <c r="G244" t="s">
         <v>744</v>
       </c>
-      <c r="F244" t="s">
-        <v>745</v>
-      </c>
-      <c r="G244" t="s">
-        <v>746</v>
-      </c>
       <c r="H244" s="3" t="s">
         <v>53</v>
       </c>
@@ -11074,31 +11065,31 @@
         <v>1</v>
       </c>
       <c r="J244" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B245" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C245" t="s">
+        <v>740</v>
+      </c>
+      <c r="D245" t="s">
+        <v>750</v>
+      </c>
+      <c r="E245" t="s">
         <v>742</v>
       </c>
-      <c r="D245" t="s">
-        <v>753</v>
-      </c>
-      <c r="E245" t="s">
+      <c r="F245" t="s">
+        <v>743</v>
+      </c>
+      <c r="G245" t="s">
         <v>744</v>
       </c>
-      <c r="F245" t="s">
-        <v>745</v>
-      </c>
-      <c r="G245" t="s">
-        <v>746</v>
-      </c>
       <c r="H245" s="3" t="s">
         <v>53</v>
       </c>
@@ -11106,31 +11097,31 @@
         <v>1</v>
       </c>
       <c r="J245" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B246" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C246" t="s">
+        <v>740</v>
+      </c>
+      <c r="D246" t="s">
+        <v>752</v>
+      </c>
+      <c r="E246" t="s">
         <v>742</v>
       </c>
-      <c r="D246" t="s">
-        <v>755</v>
-      </c>
-      <c r="E246" t="s">
+      <c r="F246" t="s">
+        <v>743</v>
+      </c>
+      <c r="G246" t="s">
         <v>744</v>
       </c>
-      <c r="F246" t="s">
-        <v>745</v>
-      </c>
-      <c r="G246" t="s">
-        <v>746</v>
-      </c>
       <c r="H246" s="3" t="s">
         <v>53</v>
       </c>
@@ -11138,31 +11129,31 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B247" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C247" t="s">
+        <v>740</v>
+      </c>
+      <c r="D247" t="s">
+        <v>754</v>
+      </c>
+      <c r="E247" t="s">
         <v>742</v>
       </c>
-      <c r="D247" t="s">
-        <v>757</v>
-      </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
+        <v>743</v>
+      </c>
+      <c r="G247" t="s">
         <v>744</v>
       </c>
-      <c r="F247" t="s">
-        <v>745</v>
-      </c>
-      <c r="G247" t="s">
-        <v>746</v>
-      </c>
       <c r="H247" s="3" t="s">
         <v>53</v>
       </c>
@@ -11170,31 +11161,31 @@
         <v>1</v>
       </c>
       <c r="J247" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B248" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C248" t="s">
+        <v>740</v>
+      </c>
+      <c r="D248" t="s">
+        <v>756</v>
+      </c>
+      <c r="E248" t="s">
         <v>742</v>
       </c>
-      <c r="D248" t="s">
-        <v>759</v>
-      </c>
-      <c r="E248" t="s">
+      <c r="F248" t="s">
+        <v>743</v>
+      </c>
+      <c r="G248" t="s">
         <v>744</v>
       </c>
-      <c r="F248" t="s">
-        <v>745</v>
-      </c>
-      <c r="G248" t="s">
-        <v>746</v>
-      </c>
       <c r="H248" s="3" t="s">
         <v>53</v>
       </c>
@@ -11202,31 +11193,31 @@
         <v>1</v>
       </c>
       <c r="J248" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B249" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C249" t="s">
+        <v>740</v>
+      </c>
+      <c r="D249" t="s">
+        <v>758</v>
+      </c>
+      <c r="E249" t="s">
         <v>742</v>
       </c>
-      <c r="D249" t="s">
-        <v>761</v>
-      </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
+        <v>743</v>
+      </c>
+      <c r="G249" t="s">
         <v>744</v>
       </c>
-      <c r="F249" t="s">
-        <v>745</v>
-      </c>
-      <c r="G249" t="s">
-        <v>746</v>
-      </c>
       <c r="H249" s="3" t="s">
         <v>53</v>
       </c>
@@ -11234,31 +11225,31 @@
         <v>1</v>
       </c>
       <c r="J249" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B250" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C250" t="s">
+        <v>740</v>
+      </c>
+      <c r="D250" t="s">
+        <v>760</v>
+      </c>
+      <c r="E250" t="s">
         <v>742</v>
       </c>
-      <c r="D250" t="s">
-        <v>763</v>
-      </c>
-      <c r="E250" t="s">
+      <c r="F250" t="s">
+        <v>743</v>
+      </c>
+      <c r="G250" t="s">
         <v>744</v>
       </c>
-      <c r="F250" t="s">
-        <v>745</v>
-      </c>
-      <c r="G250" t="s">
-        <v>746</v>
-      </c>
       <c r="H250" s="3" t="s">
         <v>53</v>
       </c>
@@ -11266,31 +11257,31 @@
         <v>1</v>
       </c>
       <c r="J250" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B251" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C251" t="s">
+        <v>740</v>
+      </c>
+      <c r="D251" t="s">
+        <v>762</v>
+      </c>
+      <c r="E251" t="s">
         <v>742</v>
       </c>
-      <c r="D251" t="s">
-        <v>765</v>
-      </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
+        <v>743</v>
+      </c>
+      <c r="G251" t="s">
         <v>744</v>
       </c>
-      <c r="F251" t="s">
-        <v>745</v>
-      </c>
-      <c r="G251" t="s">
-        <v>746</v>
-      </c>
       <c r="H251" s="3" t="s">
         <v>53</v>
       </c>
@@ -11298,31 +11289,31 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B252" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C252" t="s">
+        <v>740</v>
+      </c>
+      <c r="D252" t="s">
+        <v>764</v>
+      </c>
+      <c r="E252" t="s">
         <v>742</v>
       </c>
-      <c r="D252" t="s">
-        <v>767</v>
-      </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
+        <v>743</v>
+      </c>
+      <c r="G252" t="s">
         <v>744</v>
       </c>
-      <c r="F252" t="s">
-        <v>745</v>
-      </c>
-      <c r="G252" t="s">
-        <v>746</v>
-      </c>
       <c r="H252" s="3" t="s">
         <v>53</v>
       </c>
@@ -11330,31 +11321,31 @@
         <v>1</v>
       </c>
       <c r="J252" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B253" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C253" t="s">
+        <v>740</v>
+      </c>
+      <c r="D253" t="s">
+        <v>766</v>
+      </c>
+      <c r="E253" t="s">
         <v>742</v>
       </c>
-      <c r="D253" t="s">
-        <v>769</v>
-      </c>
-      <c r="E253" t="s">
+      <c r="F253" t="s">
+        <v>743</v>
+      </c>
+      <c r="G253" t="s">
         <v>744</v>
       </c>
-      <c r="F253" t="s">
-        <v>745</v>
-      </c>
-      <c r="G253" t="s">
-        <v>746</v>
-      </c>
       <c r="H253" s="3" t="s">
         <v>53</v>
       </c>
@@ -11362,31 +11353,31 @@
         <v>1</v>
       </c>
       <c r="J253" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B254" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C254" t="s">
+        <v>740</v>
+      </c>
+      <c r="D254" t="s">
+        <v>768</v>
+      </c>
+      <c r="E254" t="s">
         <v>742</v>
       </c>
-      <c r="D254" t="s">
-        <v>771</v>
-      </c>
-      <c r="E254" t="s">
+      <c r="F254" t="s">
+        <v>743</v>
+      </c>
+      <c r="G254" t="s">
         <v>744</v>
       </c>
-      <c r="F254" t="s">
-        <v>745</v>
-      </c>
-      <c r="G254" t="s">
-        <v>746</v>
-      </c>
       <c r="H254" s="3" t="s">
         <v>53</v>
       </c>
@@ -11394,31 +11385,31 @@
         <v>1</v>
       </c>
       <c r="J254" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B255" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C255" t="s">
+        <v>740</v>
+      </c>
+      <c r="D255" t="s">
+        <v>770</v>
+      </c>
+      <c r="E255" t="s">
         <v>742</v>
       </c>
-      <c r="D255" t="s">
-        <v>773</v>
-      </c>
-      <c r="E255" t="s">
+      <c r="F255" t="s">
+        <v>743</v>
+      </c>
+      <c r="G255" t="s">
         <v>744</v>
       </c>
-      <c r="F255" t="s">
-        <v>745</v>
-      </c>
-      <c r="G255" t="s">
-        <v>746</v>
-      </c>
       <c r="H255" s="3" t="s">
         <v>53</v>
       </c>
@@ -11426,31 +11417,31 @@
         <v>1</v>
       </c>
       <c r="J255" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B256" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C256" t="s">
+        <v>740</v>
+      </c>
+      <c r="D256" t="s">
+        <v>772</v>
+      </c>
+      <c r="E256" t="s">
         <v>742</v>
       </c>
-      <c r="D256" t="s">
-        <v>775</v>
-      </c>
-      <c r="E256" t="s">
+      <c r="F256" t="s">
+        <v>743</v>
+      </c>
+      <c r="G256" t="s">
         <v>744</v>
       </c>
-      <c r="F256" t="s">
-        <v>745</v>
-      </c>
-      <c r="G256" t="s">
-        <v>746</v>
-      </c>
       <c r="H256" s="3" t="s">
         <v>53</v>
       </c>
@@ -11458,31 +11449,31 @@
         <v>1</v>
       </c>
       <c r="J256" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B257" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C257" t="s">
+        <v>740</v>
+      </c>
+      <c r="D257" t="s">
+        <v>774</v>
+      </c>
+      <c r="E257" t="s">
         <v>742</v>
       </c>
-      <c r="D257" t="s">
-        <v>777</v>
-      </c>
-      <c r="E257" t="s">
+      <c r="F257" t="s">
+        <v>743</v>
+      </c>
+      <c r="G257" t="s">
         <v>744</v>
       </c>
-      <c r="F257" t="s">
-        <v>745</v>
-      </c>
-      <c r="G257" t="s">
-        <v>746</v>
-      </c>
       <c r="H257" s="3" t="s">
         <v>53</v>
       </c>
@@ -11490,31 +11481,31 @@
         <v>1</v>
       </c>
       <c r="J257" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B258" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C258" t="s">
+        <v>740</v>
+      </c>
+      <c r="D258" t="s">
+        <v>776</v>
+      </c>
+      <c r="E258" t="s">
         <v>742</v>
       </c>
-      <c r="D258" t="s">
-        <v>779</v>
-      </c>
-      <c r="E258" t="s">
+      <c r="F258" t="s">
+        <v>743</v>
+      </c>
+      <c r="G258" t="s">
         <v>744</v>
       </c>
-      <c r="F258" t="s">
-        <v>745</v>
-      </c>
-      <c r="G258" t="s">
-        <v>746</v>
-      </c>
       <c r="H258" s="3" t="s">
         <v>53</v>
       </c>
@@ -11522,31 +11513,31 @@
         <v>1</v>
       </c>
       <c r="J258" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B259" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C259" t="s">
+        <v>740</v>
+      </c>
+      <c r="D259" t="s">
+        <v>778</v>
+      </c>
+      <c r="E259" t="s">
         <v>742</v>
       </c>
-      <c r="D259" t="s">
-        <v>781</v>
-      </c>
-      <c r="E259" t="s">
+      <c r="F259" t="s">
+        <v>743</v>
+      </c>
+      <c r="G259" t="s">
         <v>744</v>
       </c>
-      <c r="F259" t="s">
-        <v>745</v>
-      </c>
-      <c r="G259" t="s">
-        <v>746</v>
-      </c>
       <c r="H259" s="3" t="s">
         <v>53</v>
       </c>
@@ -11554,31 +11545,31 @@
         <v>1</v>
       </c>
       <c r="J259" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B260" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C260" t="s">
+        <v>740</v>
+      </c>
+      <c r="D260" t="s">
+        <v>780</v>
+      </c>
+      <c r="E260" t="s">
         <v>742</v>
       </c>
-      <c r="D260" t="s">
-        <v>783</v>
-      </c>
-      <c r="E260" t="s">
+      <c r="F260" t="s">
+        <v>743</v>
+      </c>
+      <c r="G260" t="s">
         <v>744</v>
       </c>
-      <c r="F260" t="s">
-        <v>745</v>
-      </c>
-      <c r="G260" t="s">
-        <v>746</v>
-      </c>
       <c r="H260" s="3" t="s">
         <v>53</v>
       </c>
@@ -11586,31 +11577,31 @@
         <v>1</v>
       </c>
       <c r="J260" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B261" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C261" t="s">
+        <v>740</v>
+      </c>
+      <c r="D261" t="s">
+        <v>782</v>
+      </c>
+      <c r="E261" t="s">
         <v>742</v>
       </c>
-      <c r="D261" t="s">
-        <v>785</v>
-      </c>
-      <c r="E261" t="s">
+      <c r="F261" t="s">
+        <v>743</v>
+      </c>
+      <c r="G261" t="s">
         <v>744</v>
       </c>
-      <c r="F261" t="s">
-        <v>745</v>
-      </c>
-      <c r="G261" t="s">
-        <v>746</v>
-      </c>
       <c r="H261" s="3" t="s">
         <v>53</v>
       </c>
@@ -11618,31 +11609,31 @@
         <v>1</v>
       </c>
       <c r="J261" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B262" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C262" t="s">
+        <v>740</v>
+      </c>
+      <c r="D262" t="s">
+        <v>784</v>
+      </c>
+      <c r="E262" t="s">
         <v>742</v>
       </c>
-      <c r="D262" t="s">
-        <v>787</v>
-      </c>
-      <c r="E262" t="s">
+      <c r="F262" t="s">
+        <v>743</v>
+      </c>
+      <c r="G262" t="s">
         <v>744</v>
       </c>
-      <c r="F262" t="s">
-        <v>745</v>
-      </c>
-      <c r="G262" t="s">
-        <v>746</v>
-      </c>
       <c r="H262" s="3" t="s">
         <v>53</v>
       </c>
@@ -11650,31 +11641,31 @@
         <v>1</v>
       </c>
       <c r="J262" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B263" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C263" t="s">
+        <v>740</v>
+      </c>
+      <c r="D263" t="s">
+        <v>786</v>
+      </c>
+      <c r="E263" t="s">
         <v>742</v>
       </c>
-      <c r="D263" t="s">
-        <v>789</v>
-      </c>
-      <c r="E263" t="s">
+      <c r="F263" t="s">
+        <v>743</v>
+      </c>
+      <c r="G263" t="s">
         <v>744</v>
       </c>
-      <c r="F263" t="s">
-        <v>745</v>
-      </c>
-      <c r="G263" t="s">
-        <v>746</v>
-      </c>
       <c r="H263" s="3" t="s">
         <v>53</v>
       </c>
@@ -11682,31 +11673,31 @@
         <v>1</v>
       </c>
       <c r="J263" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B264" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C264" t="s">
+        <v>740</v>
+      </c>
+      <c r="D264" t="s">
+        <v>788</v>
+      </c>
+      <c r="E264" t="s">
         <v>742</v>
       </c>
-      <c r="D264" t="s">
-        <v>791</v>
-      </c>
-      <c r="E264" t="s">
+      <c r="F264" t="s">
+        <v>743</v>
+      </c>
+      <c r="G264" t="s">
         <v>744</v>
       </c>
-      <c r="F264" t="s">
-        <v>745</v>
-      </c>
-      <c r="G264" t="s">
-        <v>746</v>
-      </c>
       <c r="H264" s="3" t="s">
         <v>53</v>
       </c>
@@ -11714,31 +11705,31 @@
         <v>1</v>
       </c>
       <c r="J264" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B265" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C265" t="s">
+        <v>740</v>
+      </c>
+      <c r="D265" t="s">
+        <v>790</v>
+      </c>
+      <c r="E265" t="s">
         <v>742</v>
       </c>
-      <c r="D265" t="s">
-        <v>793</v>
-      </c>
-      <c r="E265" t="s">
+      <c r="F265" t="s">
+        <v>743</v>
+      </c>
+      <c r="G265" t="s">
         <v>744</v>
       </c>
-      <c r="F265" t="s">
-        <v>745</v>
-      </c>
-      <c r="G265" t="s">
-        <v>746</v>
-      </c>
       <c r="H265" s="3" t="s">
         <v>53</v>
       </c>
@@ -11746,31 +11737,31 @@
         <v>1</v>
       </c>
       <c r="J265" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B266" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C266" t="s">
+        <v>740</v>
+      </c>
+      <c r="D266" t="s">
+        <v>792</v>
+      </c>
+      <c r="E266" t="s">
         <v>742</v>
       </c>
-      <c r="D266" t="s">
-        <v>795</v>
-      </c>
-      <c r="E266" t="s">
+      <c r="F266" t="s">
+        <v>743</v>
+      </c>
+      <c r="G266" t="s">
         <v>744</v>
       </c>
-      <c r="F266" t="s">
-        <v>745</v>
-      </c>
-      <c r="G266" t="s">
-        <v>746</v>
-      </c>
       <c r="H266" s="3" t="s">
         <v>53</v>
       </c>
@@ -11778,31 +11769,31 @@
         <v>1</v>
       </c>
       <c r="J266" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B267" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C267" t="s">
+        <v>740</v>
+      </c>
+      <c r="D267" t="s">
+        <v>794</v>
+      </c>
+      <c r="E267" t="s">
         <v>742</v>
       </c>
-      <c r="D267" t="s">
-        <v>797</v>
-      </c>
-      <c r="E267" t="s">
+      <c r="F267" t="s">
+        <v>743</v>
+      </c>
+      <c r="G267" t="s">
         <v>744</v>
       </c>
-      <c r="F267" t="s">
-        <v>745</v>
-      </c>
-      <c r="G267" t="s">
-        <v>746</v>
-      </c>
       <c r="H267" s="3" t="s">
         <v>53</v>
       </c>
@@ -11810,31 +11801,31 @@
         <v>1</v>
       </c>
       <c r="J267" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B268" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C268" t="s">
+        <v>740</v>
+      </c>
+      <c r="D268" t="s">
+        <v>796</v>
+      </c>
+      <c r="E268" t="s">
         <v>742</v>
       </c>
-      <c r="D268" t="s">
-        <v>799</v>
-      </c>
-      <c r="E268" t="s">
+      <c r="F268" t="s">
+        <v>743</v>
+      </c>
+      <c r="G268" t="s">
         <v>744</v>
       </c>
-      <c r="F268" t="s">
-        <v>745</v>
-      </c>
-      <c r="G268" t="s">
-        <v>746</v>
-      </c>
       <c r="H268" s="3" t="s">
         <v>53</v>
       </c>
@@ -11842,31 +11833,31 @@
         <v>1</v>
       </c>
       <c r="J268" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B269" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C269" t="s">
+        <v>740</v>
+      </c>
+      <c r="D269" t="s">
+        <v>798</v>
+      </c>
+      <c r="E269" t="s">
         <v>742</v>
       </c>
-      <c r="D269" t="s">
-        <v>801</v>
-      </c>
-      <c r="E269" t="s">
+      <c r="F269" t="s">
+        <v>743</v>
+      </c>
+      <c r="G269" t="s">
         <v>744</v>
       </c>
-      <c r="F269" t="s">
-        <v>745</v>
-      </c>
-      <c r="G269" t="s">
-        <v>746</v>
-      </c>
       <c r="H269" s="3" t="s">
         <v>53</v>
       </c>
@@ -11874,31 +11865,31 @@
         <v>1</v>
       </c>
       <c r="J269" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B270" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C270" t="s">
+        <v>740</v>
+      </c>
+      <c r="D270" t="s">
+        <v>800</v>
+      </c>
+      <c r="E270" t="s">
         <v>742</v>
       </c>
-      <c r="D270" t="s">
-        <v>803</v>
-      </c>
-      <c r="E270" t="s">
+      <c r="F270" t="s">
+        <v>743</v>
+      </c>
+      <c r="G270" t="s">
         <v>744</v>
       </c>
-      <c r="F270" t="s">
-        <v>745</v>
-      </c>
-      <c r="G270" t="s">
-        <v>746</v>
-      </c>
       <c r="H270" s="3" t="s">
         <v>53</v>
       </c>
@@ -11906,31 +11897,31 @@
         <v>1</v>
       </c>
       <c r="J270" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B271" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C271" t="s">
+        <v>740</v>
+      </c>
+      <c r="D271" t="s">
+        <v>802</v>
+      </c>
+      <c r="E271" t="s">
         <v>742</v>
       </c>
-      <c r="D271" t="s">
-        <v>805</v>
-      </c>
-      <c r="E271" t="s">
+      <c r="F271" t="s">
+        <v>743</v>
+      </c>
+      <c r="G271" t="s">
         <v>744</v>
       </c>
-      <c r="F271" t="s">
-        <v>745</v>
-      </c>
-      <c r="G271" t="s">
-        <v>746</v>
-      </c>
       <c r="H271" s="3" t="s">
         <v>53</v>
       </c>
@@ -11938,31 +11929,31 @@
         <v>1</v>
       </c>
       <c r="J271" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>803</v>
+      </c>
+      <c r="B272" t="s">
+        <v>804</v>
+      </c>
+      <c r="C272" t="s">
+        <v>805</v>
+      </c>
+      <c r="D272" t="s">
         <v>806</v>
       </c>
-      <c r="B272" t="s">
+      <c r="E272" t="s">
         <v>807</v>
       </c>
-      <c r="C272" t="s">
+      <c r="F272" t="s">
         <v>808</v>
       </c>
-      <c r="D272" t="s">
+      <c r="G272" t="s">
         <v>809</v>
       </c>
-      <c r="E272" t="s">
-        <v>810</v>
-      </c>
-      <c r="F272" t="s">
-        <v>811</v>
-      </c>
-      <c r="G272" t="s">
-        <v>812</v>
-      </c>
       <c r="H272" s="3" t="s">
         <v>53</v>
       </c>
@@ -11970,30 +11961,30 @@
         <v>1</v>
       </c>
       <c r="J272" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B273" t="s">
+        <v>804</v>
+      </c>
+      <c r="C273" t="s">
+        <v>805</v>
+      </c>
+      <c r="D273" t="s">
+        <v>811</v>
+      </c>
+      <c r="E273" t="s">
         <v>807</v>
       </c>
-      <c r="C273" t="s">
+      <c r="F273" t="s">
         <v>808</v>
       </c>
-      <c r="D273" t="s">
-        <v>814</v>
-      </c>
-      <c r="E273" t="s">
-        <v>810</v>
-      </c>
-      <c r="F273" t="s">
-        <v>811</v>
-      </c>
       <c r="G273" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H273" s="3" t="s">
         <v>53</v>
@@ -12002,30 +11993,30 @@
         <v>1</v>
       </c>
       <c r="J273" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="B274" t="s">
+        <v>804</v>
+      </c>
+      <c r="C274" t="s">
+        <v>805</v>
+      </c>
+      <c r="D274" t="s">
+        <v>813</v>
+      </c>
+      <c r="E274" t="s">
         <v>807</v>
       </c>
-      <c r="C274" t="s">
+      <c r="F274" t="s">
         <v>808</v>
       </c>
-      <c r="D274" t="s">
-        <v>816</v>
-      </c>
-      <c r="E274" t="s">
-        <v>810</v>
-      </c>
-      <c r="F274" t="s">
-        <v>811</v>
-      </c>
       <c r="G274" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H274" s="3" t="s">
         <v>53</v>
@@ -12034,30 +12025,30 @@
         <v>1</v>
       </c>
       <c r="J274" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B275" t="s">
+        <v>804</v>
+      </c>
+      <c r="C275" t="s">
+        <v>805</v>
+      </c>
+      <c r="D275" t="s">
+        <v>815</v>
+      </c>
+      <c r="E275" t="s">
         <v>807</v>
       </c>
-      <c r="C275" t="s">
+      <c r="F275" t="s">
         <v>808</v>
       </c>
-      <c r="D275" t="s">
-        <v>818</v>
-      </c>
-      <c r="E275" t="s">
-        <v>810</v>
-      </c>
-      <c r="F275" t="s">
-        <v>811</v>
-      </c>
       <c r="G275" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H275" s="3" t="s">
         <v>53</v>
@@ -12066,30 +12057,30 @@
         <v>1</v>
       </c>
       <c r="J275" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B276" t="s">
+        <v>804</v>
+      </c>
+      <c r="C276" t="s">
+        <v>805</v>
+      </c>
+      <c r="D276" t="s">
+        <v>817</v>
+      </c>
+      <c r="E276" t="s">
         <v>807</v>
       </c>
-      <c r="C276" t="s">
+      <c r="F276" t="s">
         <v>808</v>
       </c>
-      <c r="D276" t="s">
-        <v>820</v>
-      </c>
-      <c r="E276" t="s">
-        <v>810</v>
-      </c>
-      <c r="F276" t="s">
-        <v>811</v>
-      </c>
       <c r="G276" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H276" s="3" t="s">
         <v>53</v>
@@ -12098,30 +12089,30 @@
         <v>1</v>
       </c>
       <c r="J276" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B277" t="s">
+        <v>804</v>
+      </c>
+      <c r="C277" t="s">
+        <v>805</v>
+      </c>
+      <c r="D277" t="s">
+        <v>819</v>
+      </c>
+      <c r="E277" t="s">
         <v>807</v>
       </c>
-      <c r="C277" t="s">
+      <c r="F277" t="s">
         <v>808</v>
       </c>
-      <c r="D277" t="s">
-        <v>822</v>
-      </c>
-      <c r="E277" t="s">
-        <v>810</v>
-      </c>
-      <c r="F277" t="s">
-        <v>811</v>
-      </c>
       <c r="G277" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H277" s="3" t="s">
         <v>53</v>
@@ -12130,30 +12121,30 @@
         <v>1</v>
       </c>
       <c r="J277" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="B278" t="s">
+        <v>804</v>
+      </c>
+      <c r="C278" t="s">
+        <v>805</v>
+      </c>
+      <c r="D278" t="s">
+        <v>821</v>
+      </c>
+      <c r="E278" t="s">
         <v>807</v>
       </c>
-      <c r="C278" t="s">
+      <c r="F278" t="s">
         <v>808</v>
       </c>
-      <c r="D278" t="s">
-        <v>824</v>
-      </c>
-      <c r="E278" t="s">
-        <v>810</v>
-      </c>
-      <c r="F278" t="s">
-        <v>811</v>
-      </c>
       <c r="G278" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H278" s="3" t="s">
         <v>53</v>
@@ -12162,30 +12153,30 @@
         <v>1</v>
       </c>
       <c r="J278" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B279" t="s">
+        <v>804</v>
+      </c>
+      <c r="C279" t="s">
+        <v>805</v>
+      </c>
+      <c r="D279" t="s">
+        <v>823</v>
+      </c>
+      <c r="E279" t="s">
         <v>807</v>
       </c>
-      <c r="C279" t="s">
+      <c r="F279" t="s">
         <v>808</v>
       </c>
-      <c r="D279" t="s">
-        <v>826</v>
-      </c>
-      <c r="E279" t="s">
-        <v>810</v>
-      </c>
-      <c r="F279" t="s">
-        <v>811</v>
-      </c>
       <c r="G279" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H279" s="3" t="s">
         <v>53</v>
@@ -12194,30 +12185,30 @@
         <v>1</v>
       </c>
       <c r="J279" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="B280" t="s">
+        <v>804</v>
+      </c>
+      <c r="C280" t="s">
+        <v>805</v>
+      </c>
+      <c r="D280" t="s">
+        <v>825</v>
+      </c>
+      <c r="E280" t="s">
         <v>807</v>
       </c>
-      <c r="C280" t="s">
+      <c r="F280" t="s">
         <v>808</v>
       </c>
-      <c r="D280" t="s">
-        <v>828</v>
-      </c>
-      <c r="E280" t="s">
-        <v>810</v>
-      </c>
-      <c r="F280" t="s">
-        <v>811</v>
-      </c>
       <c r="G280" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H280" s="3" t="s">
         <v>53</v>
@@ -12226,30 +12217,30 @@
         <v>1</v>
       </c>
       <c r="J280" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B281" t="s">
+        <v>804</v>
+      </c>
+      <c r="C281" t="s">
+        <v>805</v>
+      </c>
+      <c r="D281" t="s">
+        <v>827</v>
+      </c>
+      <c r="E281" t="s">
         <v>807</v>
       </c>
-      <c r="C281" t="s">
+      <c r="F281" t="s">
         <v>808</v>
       </c>
-      <c r="D281" t="s">
-        <v>830</v>
-      </c>
-      <c r="E281" t="s">
-        <v>810</v>
-      </c>
-      <c r="F281" t="s">
-        <v>811</v>
-      </c>
       <c r="G281" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H281" s="3" t="s">
         <v>53</v>
@@ -12258,30 +12249,30 @@
         <v>1</v>
       </c>
       <c r="J281" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="B282" t="s">
+        <v>804</v>
+      </c>
+      <c r="C282" t="s">
+        <v>805</v>
+      </c>
+      <c r="D282" t="s">
+        <v>829</v>
+      </c>
+      <c r="E282" t="s">
         <v>807</v>
       </c>
-      <c r="C282" t="s">
+      <c r="F282" t="s">
         <v>808</v>
       </c>
-      <c r="D282" t="s">
-        <v>832</v>
-      </c>
-      <c r="E282" t="s">
-        <v>810</v>
-      </c>
-      <c r="F282" t="s">
-        <v>811</v>
-      </c>
       <c r="G282" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H282" s="3" t="s">
         <v>53</v>
@@ -12290,30 +12281,30 @@
         <v>1</v>
       </c>
       <c r="J282" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B283" t="s">
+        <v>804</v>
+      </c>
+      <c r="C283" t="s">
+        <v>805</v>
+      </c>
+      <c r="D283" t="s">
+        <v>831</v>
+      </c>
+      <c r="E283" t="s">
         <v>807</v>
       </c>
-      <c r="C283" t="s">
+      <c r="F283" t="s">
         <v>808</v>
       </c>
-      <c r="D283" t="s">
-        <v>834</v>
-      </c>
-      <c r="E283" t="s">
-        <v>810</v>
-      </c>
-      <c r="F283" t="s">
-        <v>811</v>
-      </c>
       <c r="G283" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H283" s="3" t="s">
         <v>53</v>
@@ -12322,30 +12313,30 @@
         <v>1</v>
       </c>
       <c r="J283" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="B284" t="s">
+        <v>804</v>
+      </c>
+      <c r="C284" t="s">
+        <v>805</v>
+      </c>
+      <c r="D284" t="s">
+        <v>833</v>
+      </c>
+      <c r="E284" t="s">
         <v>807</v>
       </c>
-      <c r="C284" t="s">
+      <c r="F284" t="s">
         <v>808</v>
       </c>
-      <c r="D284" t="s">
-        <v>836</v>
-      </c>
-      <c r="E284" t="s">
-        <v>810</v>
-      </c>
-      <c r="F284" t="s">
-        <v>811</v>
-      </c>
       <c r="G284" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H284" s="3" t="s">
         <v>53</v>
@@ -12354,30 +12345,30 @@
         <v>1</v>
       </c>
       <c r="J284" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B285" t="s">
+        <v>804</v>
+      </c>
+      <c r="C285" t="s">
+        <v>805</v>
+      </c>
+      <c r="D285" t="s">
+        <v>835</v>
+      </c>
+      <c r="E285" t="s">
         <v>807</v>
       </c>
-      <c r="C285" t="s">
+      <c r="F285" t="s">
         <v>808</v>
       </c>
-      <c r="D285" t="s">
-        <v>838</v>
-      </c>
-      <c r="E285" t="s">
-        <v>810</v>
-      </c>
-      <c r="F285" t="s">
-        <v>811</v>
-      </c>
       <c r="G285" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H285" s="3" t="s">
         <v>53</v>
@@ -12386,30 +12377,30 @@
         <v>1</v>
       </c>
       <c r="J285" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="B286" t="s">
+        <v>804</v>
+      </c>
+      <c r="C286" t="s">
+        <v>805</v>
+      </c>
+      <c r="D286" t="s">
+        <v>837</v>
+      </c>
+      <c r="E286" t="s">
         <v>807</v>
       </c>
-      <c r="C286" t="s">
+      <c r="F286" t="s">
         <v>808</v>
       </c>
-      <c r="D286" t="s">
-        <v>840</v>
-      </c>
-      <c r="E286" t="s">
-        <v>810</v>
-      </c>
-      <c r="F286" t="s">
-        <v>811</v>
-      </c>
       <c r="G286" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H286" s="3" t="s">
         <v>53</v>
@@ -12418,30 +12409,30 @@
         <v>1</v>
       </c>
       <c r="J286" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B287" t="s">
+        <v>804</v>
+      </c>
+      <c r="C287" t="s">
+        <v>805</v>
+      </c>
+      <c r="D287" t="s">
+        <v>839</v>
+      </c>
+      <c r="E287" t="s">
         <v>807</v>
       </c>
-      <c r="C287" t="s">
+      <c r="F287" t="s">
         <v>808</v>
       </c>
-      <c r="D287" t="s">
-        <v>842</v>
-      </c>
-      <c r="E287" t="s">
-        <v>810</v>
-      </c>
-      <c r="F287" t="s">
-        <v>811</v>
-      </c>
       <c r="G287" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H287" s="3" t="s">
         <v>53</v>
@@ -12450,30 +12441,30 @@
         <v>1</v>
       </c>
       <c r="J287" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B288" t="s">
+        <v>804</v>
+      </c>
+      <c r="C288" t="s">
+        <v>805</v>
+      </c>
+      <c r="D288" t="s">
+        <v>841</v>
+      </c>
+      <c r="E288" t="s">
         <v>807</v>
       </c>
-      <c r="C288" t="s">
+      <c r="F288" t="s">
         <v>808</v>
       </c>
-      <c r="D288" t="s">
-        <v>844</v>
-      </c>
-      <c r="E288" t="s">
-        <v>810</v>
-      </c>
-      <c r="F288" t="s">
-        <v>811</v>
-      </c>
       <c r="G288" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H288" s="3" t="s">
         <v>53</v>
@@ -12482,30 +12473,30 @@
         <v>1</v>
       </c>
       <c r="J288" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="B289" t="s">
+        <v>804</v>
+      </c>
+      <c r="C289" t="s">
+        <v>805</v>
+      </c>
+      <c r="D289" t="s">
+        <v>843</v>
+      </c>
+      <c r="E289" t="s">
         <v>807</v>
       </c>
-      <c r="C289" t="s">
+      <c r="F289" t="s">
         <v>808</v>
       </c>
-      <c r="D289" t="s">
-        <v>846</v>
-      </c>
-      <c r="E289" t="s">
-        <v>810</v>
-      </c>
-      <c r="F289" t="s">
-        <v>811</v>
-      </c>
       <c r="G289" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H289" s="3" t="s">
         <v>53</v>
@@ -12514,30 +12505,30 @@
         <v>1</v>
       </c>
       <c r="J289" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B290" t="s">
+        <v>804</v>
+      </c>
+      <c r="C290" t="s">
+        <v>805</v>
+      </c>
+      <c r="D290" t="s">
+        <v>845</v>
+      </c>
+      <c r="E290" t="s">
         <v>807</v>
       </c>
-      <c r="C290" t="s">
+      <c r="F290" t="s">
         <v>808</v>
       </c>
-      <c r="D290" t="s">
-        <v>848</v>
-      </c>
-      <c r="E290" t="s">
-        <v>810</v>
-      </c>
-      <c r="F290" t="s">
-        <v>811</v>
-      </c>
       <c r="G290" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H290" s="3" t="s">
         <v>53</v>
@@ -12546,30 +12537,30 @@
         <v>1</v>
       </c>
       <c r="J290" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B291" t="s">
+        <v>804</v>
+      </c>
+      <c r="C291" t="s">
+        <v>805</v>
+      </c>
+      <c r="D291" t="s">
+        <v>847</v>
+      </c>
+      <c r="E291" t="s">
         <v>807</v>
       </c>
-      <c r="C291" t="s">
+      <c r="F291" t="s">
         <v>808</v>
       </c>
-      <c r="D291" t="s">
-        <v>850</v>
-      </c>
-      <c r="E291" t="s">
-        <v>810</v>
-      </c>
-      <c r="F291" t="s">
-        <v>811</v>
-      </c>
       <c r="G291" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H291" s="3" t="s">
         <v>53</v>
@@ -12578,30 +12569,30 @@
         <v>1</v>
       </c>
       <c r="J291" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B292" t="s">
+        <v>804</v>
+      </c>
+      <c r="C292" t="s">
+        <v>805</v>
+      </c>
+      <c r="D292" t="s">
+        <v>849</v>
+      </c>
+      <c r="E292" t="s">
         <v>807</v>
       </c>
-      <c r="C292" t="s">
+      <c r="F292" t="s">
         <v>808</v>
       </c>
-      <c r="D292" t="s">
-        <v>852</v>
-      </c>
-      <c r="E292" t="s">
-        <v>810</v>
-      </c>
-      <c r="F292" t="s">
-        <v>811</v>
-      </c>
       <c r="G292" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H292" s="3" t="s">
         <v>53</v>
@@ -12610,30 +12601,30 @@
         <v>1</v>
       </c>
       <c r="J292" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B293" t="s">
+        <v>804</v>
+      </c>
+      <c r="C293" t="s">
+        <v>805</v>
+      </c>
+      <c r="D293" t="s">
+        <v>851</v>
+      </c>
+      <c r="E293" t="s">
         <v>807</v>
       </c>
-      <c r="C293" t="s">
+      <c r="F293" t="s">
         <v>808</v>
       </c>
-      <c r="D293" t="s">
-        <v>854</v>
-      </c>
-      <c r="E293" t="s">
-        <v>810</v>
-      </c>
-      <c r="F293" t="s">
-        <v>811</v>
-      </c>
       <c r="G293" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H293" s="3" t="s">
         <v>53</v>
@@ -12642,30 +12633,30 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B294" t="s">
+        <v>804</v>
+      </c>
+      <c r="C294" t="s">
+        <v>805</v>
+      </c>
+      <c r="D294" t="s">
+        <v>853</v>
+      </c>
+      <c r="E294" t="s">
         <v>807</v>
       </c>
-      <c r="C294" t="s">
+      <c r="F294" t="s">
         <v>808</v>
       </c>
-      <c r="D294" t="s">
-        <v>856</v>
-      </c>
-      <c r="E294" t="s">
-        <v>810</v>
-      </c>
-      <c r="F294" t="s">
-        <v>811</v>
-      </c>
       <c r="G294" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H294" s="3" t="s">
         <v>53</v>
@@ -12674,30 +12665,30 @@
         <v>1</v>
       </c>
       <c r="J294" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B295" t="s">
+        <v>804</v>
+      </c>
+      <c r="C295" t="s">
+        <v>805</v>
+      </c>
+      <c r="D295" t="s">
+        <v>855</v>
+      </c>
+      <c r="E295" t="s">
         <v>807</v>
       </c>
-      <c r="C295" t="s">
+      <c r="F295" t="s">
         <v>808</v>
       </c>
-      <c r="D295" t="s">
-        <v>858</v>
-      </c>
-      <c r="E295" t="s">
-        <v>810</v>
-      </c>
-      <c r="F295" t="s">
-        <v>811</v>
-      </c>
       <c r="G295" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H295" s="3" t="s">
         <v>53</v>
@@ -12706,30 +12697,30 @@
         <v>1</v>
       </c>
       <c r="J295" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B296" t="s">
+        <v>804</v>
+      </c>
+      <c r="C296" t="s">
+        <v>805</v>
+      </c>
+      <c r="D296" t="s">
+        <v>857</v>
+      </c>
+      <c r="E296" t="s">
         <v>807</v>
       </c>
-      <c r="C296" t="s">
+      <c r="F296" t="s">
         <v>808</v>
       </c>
-      <c r="D296" t="s">
-        <v>860</v>
-      </c>
-      <c r="E296" t="s">
-        <v>810</v>
-      </c>
-      <c r="F296" t="s">
-        <v>811</v>
-      </c>
       <c r="G296" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>53</v>
@@ -12738,30 +12729,30 @@
         <v>1</v>
       </c>
       <c r="J296" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B297" t="s">
+        <v>804</v>
+      </c>
+      <c r="C297" t="s">
+        <v>805</v>
+      </c>
+      <c r="D297" t="s">
+        <v>859</v>
+      </c>
+      <c r="E297" t="s">
         <v>807</v>
       </c>
-      <c r="C297" t="s">
+      <c r="F297" t="s">
         <v>808</v>
       </c>
-      <c r="D297" t="s">
-        <v>862</v>
-      </c>
-      <c r="E297" t="s">
-        <v>810</v>
-      </c>
-      <c r="F297" t="s">
-        <v>811</v>
-      </c>
       <c r="G297" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H297" s="3" t="s">
         <v>53</v>
@@ -12770,30 +12761,30 @@
         <v>1</v>
       </c>
       <c r="J297" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B298" t="s">
+        <v>804</v>
+      </c>
+      <c r="C298" t="s">
+        <v>805</v>
+      </c>
+      <c r="D298" t="s">
+        <v>861</v>
+      </c>
+      <c r="E298" t="s">
         <v>807</v>
       </c>
-      <c r="C298" t="s">
+      <c r="F298" t="s">
         <v>808</v>
       </c>
-      <c r="D298" t="s">
-        <v>864</v>
-      </c>
-      <c r="E298" t="s">
-        <v>810</v>
-      </c>
-      <c r="F298" t="s">
-        <v>811</v>
-      </c>
       <c r="G298" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H298" s="3" t="s">
         <v>53</v>
@@ -12802,30 +12793,30 @@
         <v>1</v>
       </c>
       <c r="J298" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B299" t="s">
+        <v>804</v>
+      </c>
+      <c r="C299" t="s">
+        <v>805</v>
+      </c>
+      <c r="D299" t="s">
+        <v>863</v>
+      </c>
+      <c r="E299" t="s">
         <v>807</v>
       </c>
-      <c r="C299" t="s">
+      <c r="F299" t="s">
         <v>808</v>
       </c>
-      <c r="D299" t="s">
-        <v>866</v>
-      </c>
-      <c r="E299" t="s">
-        <v>810</v>
-      </c>
-      <c r="F299" t="s">
-        <v>811</v>
-      </c>
       <c r="G299" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H299" s="3" t="s">
         <v>53</v>
@@ -12834,30 +12825,30 @@
         <v>1</v>
       </c>
       <c r="J299" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B300" t="s">
+        <v>804</v>
+      </c>
+      <c r="C300" t="s">
+        <v>805</v>
+      </c>
+      <c r="D300" t="s">
+        <v>865</v>
+      </c>
+      <c r="E300" t="s">
         <v>807</v>
       </c>
-      <c r="C300" t="s">
+      <c r="F300" t="s">
         <v>808</v>
       </c>
-      <c r="D300" t="s">
-        <v>868</v>
-      </c>
-      <c r="E300" t="s">
-        <v>810</v>
-      </c>
-      <c r="F300" t="s">
-        <v>811</v>
-      </c>
       <c r="G300" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H300" s="3" t="s">
         <v>53</v>
@@ -12866,30 +12857,30 @@
         <v>1</v>
       </c>
       <c r="J300" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B301" t="s">
+        <v>804</v>
+      </c>
+      <c r="C301" t="s">
+        <v>805</v>
+      </c>
+      <c r="D301" t="s">
+        <v>867</v>
+      </c>
+      <c r="E301" t="s">
         <v>807</v>
       </c>
-      <c r="C301" t="s">
+      <c r="F301" t="s">
         <v>808</v>
       </c>
-      <c r="D301" t="s">
-        <v>870</v>
-      </c>
-      <c r="E301" t="s">
-        <v>810</v>
-      </c>
-      <c r="F301" t="s">
-        <v>811</v>
-      </c>
       <c r="G301" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="H301" s="3" t="s">
         <v>53</v>
@@ -12898,7 +12889,7 @@
         <v>1</v>
       </c>
       <c r="J301" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>

--- a/reports/load-test-report.xlsx
+++ b/reports/load-test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="870">
   <si>
     <t>Metric</t>
   </si>
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>7/8/2026, 10:48:03 am</t>
+    <t>7/8/2026, 11:08:46 am</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-07T05:18:03.487Z</t>
+    <t>2026-08-07T05:38:46.560Z</t>
   </si>
   <si>
     <t>TC-LOAD-002</t>
@@ -191,7 +191,7 @@
     <t>Achieved: 270 req/sec, avg_latency=34.2ms, error_rate=0.0%</t>
   </si>
   <si>
-    <t>2026-08-07T05:18:03.490Z</t>
+    <t>2026-08-07T05:38:46.561Z</t>
   </si>
   <si>
     <t>TC-LOAD-003</t>
@@ -434,6 +434,9 @@
     <t>Achieved: 470 req/sec, avg_latency=34.2ms, error_rate=0.0%</t>
   </si>
   <si>
+    <t>2026-08-07T05:38:46.562Z</t>
+  </si>
+  <si>
     <t>TC-LOAD-023</t>
   </si>
   <si>
@@ -494,9 +497,6 @@
     <t>Achieved: 520 req/sec, avg_latency=34.2ms, error_rate=0.0%</t>
   </si>
   <si>
-    <t>2026-08-07T05:18:03.491Z</t>
-  </si>
-  <si>
     <t>TC-LOAD-028</t>
   </si>
   <si>
@@ -1253,9 +1253,6 @@
     <t>Spike handled: peak_concurrency=370, 0 dropped packets</t>
   </si>
   <si>
-    <t>2026-08-07T05:18:03.492Z</t>
-  </si>
-  <si>
     <t>TC-LOAD-098</t>
   </si>
   <si>
@@ -1463,6 +1460,9 @@
     <t>AI Trip Generation Endpoint Concurrency #16</t>
   </si>
   <si>
+    <t>2026-08-07T05:38:46.563Z</t>
+  </si>
+  <si>
     <t>TC-LOAD-122</t>
   </si>
   <si>
@@ -1658,6 +1658,9 @@
     <t>Full-Text Search Index Latency Under Heavy Load #11</t>
   </si>
   <si>
+    <t>2026-08-07T05:38:46.564Z</t>
+  </si>
+  <si>
     <t>TC-LOAD-152</t>
   </si>
   <si>
@@ -1853,7 +1856,7 @@
     <t>PostgreSQL Connection Pool Stress Test #6</t>
   </si>
   <si>
-    <t>2026-08-07T05:18:03.493Z</t>
+    <t>2026-08-07T05:38:46.565Z</t>
   </si>
   <si>
     <t>TC-LOAD-182</t>
@@ -2276,6 +2279,9 @@
     <t>Node.js V8 Heap Memory Leak &amp; GC Endurance #6</t>
   </si>
   <si>
+    <t>2026-08-07T05:38:46.566Z</t>
+  </si>
+  <si>
     <t>TC-LOAD-247</t>
   </si>
   <si>
@@ -2507,9 +2513,6 @@
     <t>Simulated 3G/4G High-Latency Mobile Network #12</t>
   </si>
   <si>
-    <t>2026-08-07T05:18:03.494Z</t>
-  </si>
-  <si>
     <t>TC-LOAD-283</t>
   </si>
   <si>
@@ -2568,6 +2571,9 @@
   </si>
   <si>
     <t>Simulated 3G/4G High-Latency Mobile Network #22</t>
+  </si>
+  <si>
+    <t>2026-08-07T05:38:46.567Z</t>
   </si>
   <si>
     <t>TC-LOAD-293</t>
@@ -3993,12 +3999,12 @@
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B24" t="s">
         <v>47</v>
@@ -4007,16 +4013,16 @@
         <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F24" t="s">
         <v>51</v>
       </c>
       <c r="G24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>53</v>
@@ -4025,12 +4031,12 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s">
         <v>47</v>
@@ -4039,16 +4045,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F25" t="s">
         <v>51</v>
       </c>
       <c r="G25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>53</v>
@@ -4057,12 +4063,12 @@
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
@@ -4071,16 +4077,16 @@
         <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F26" t="s">
         <v>51</v>
       </c>
       <c r="G26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>53</v>
@@ -4089,12 +4095,12 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B27" t="s">
         <v>47</v>
@@ -4103,16 +4109,16 @@
         <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F27" t="s">
         <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>53</v>
@@ -4121,12 +4127,12 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
@@ -4135,16 +4141,16 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F28" t="s">
         <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>53</v>
@@ -4153,7 +4159,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -4185,7 +4191,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -4217,7 +4223,7 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -4249,7 +4255,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -4281,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -4313,7 +4319,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -4345,7 +4351,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -4377,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -4409,7 +4415,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -4441,7 +4447,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -4473,7 +4479,7 @@
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -4505,7 +4511,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -4537,7 +4543,7 @@
         <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -4569,7 +4575,7 @@
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -4601,7 +4607,7 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -4633,7 +4639,7 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -4665,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -4697,7 +4703,7 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -4729,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -4761,7 +4767,7 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -4793,7 +4799,7 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -4825,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -4857,7 +4863,7 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -4889,7 +4895,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -4921,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -4953,7 +4959,7 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -4985,7 +4991,7 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -5017,7 +5023,7 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -5049,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -5081,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -5113,7 +5119,7 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -5145,7 +5151,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -5177,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -5209,7 +5215,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -5241,7 +5247,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -5273,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -5305,7 +5311,7 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -5337,7 +5343,7 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -5369,7 +5375,7 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -5401,7 +5407,7 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -5433,7 +5439,7 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -5465,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -5497,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -5529,7 +5535,7 @@
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -5561,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="J72" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -5593,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -5625,7 +5631,7 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -5657,7 +5663,7 @@
         <v>1</v>
       </c>
       <c r="J75" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -5689,7 +5695,7 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -5721,7 +5727,7 @@
         <v>1</v>
       </c>
       <c r="J77" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -5753,7 +5759,7 @@
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -5785,7 +5791,7 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -5817,7 +5823,7 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -5849,7 +5855,7 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -5881,7 +5887,7 @@
         <v>1</v>
       </c>
       <c r="J82" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -5913,7 +5919,7 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -5945,7 +5951,7 @@
         <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -5977,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="J85" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -6009,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -6041,7 +6047,7 @@
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -6073,7 +6079,7 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -6105,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -6137,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -6169,7 +6175,7 @@
         <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -6201,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -6233,7 +6239,7 @@
         <v>1</v>
       </c>
       <c r="J93" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -6265,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -6297,7 +6303,7 @@
         <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -6329,7 +6335,7 @@
         <v>1</v>
       </c>
       <c r="J96" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -6361,7 +6367,7 @@
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -6393,12 +6399,12 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B99" t="s">
         <v>303</v>
@@ -6407,16 +6413,16 @@
         <v>304</v>
       </c>
       <c r="D99" t="s">
+        <v>414</v>
+      </c>
+      <c r="E99" t="s">
         <v>415</v>
-      </c>
-      <c r="E99" t="s">
-        <v>416</v>
       </c>
       <c r="F99" t="s">
         <v>307</v>
       </c>
       <c r="G99" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>53</v>
@@ -6425,12 +6431,12 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B100" t="s">
         <v>303</v>
@@ -6439,16 +6445,16 @@
         <v>304</v>
       </c>
       <c r="D100" t="s">
+        <v>418</v>
+      </c>
+      <c r="E100" t="s">
         <v>419</v>
-      </c>
-      <c r="E100" t="s">
-        <v>420</v>
       </c>
       <c r="F100" t="s">
         <v>307</v>
       </c>
       <c r="G100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>53</v>
@@ -6457,12 +6463,12 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B101" t="s">
         <v>303</v>
@@ -6471,16 +6477,16 @@
         <v>304</v>
       </c>
       <c r="D101" t="s">
+        <v>422</v>
+      </c>
+      <c r="E101" t="s">
         <v>423</v>
-      </c>
-      <c r="E101" t="s">
-        <v>424</v>
       </c>
       <c r="F101" t="s">
         <v>307</v>
       </c>
       <c r="G101" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>53</v>
@@ -6489,12 +6495,12 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B102" t="s">
         <v>303</v>
@@ -6503,16 +6509,16 @@
         <v>304</v>
       </c>
       <c r="D102" t="s">
+        <v>426</v>
+      </c>
+      <c r="E102" t="s">
         <v>427</v>
-      </c>
-      <c r="E102" t="s">
-        <v>428</v>
       </c>
       <c r="F102" t="s">
         <v>307</v>
       </c>
       <c r="G102" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>53</v>
@@ -6521,12 +6527,12 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B103" t="s">
         <v>303</v>
@@ -6535,16 +6541,16 @@
         <v>304</v>
       </c>
       <c r="D103" t="s">
+        <v>430</v>
+      </c>
+      <c r="E103" t="s">
         <v>431</v>
-      </c>
-      <c r="E103" t="s">
-        <v>432</v>
       </c>
       <c r="F103" t="s">
         <v>307</v>
       </c>
       <c r="G103" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>53</v>
@@ -6553,12 +6559,12 @@
         <v>1</v>
       </c>
       <c r="J103" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B104" t="s">
         <v>303</v>
@@ -6567,16 +6573,16 @@
         <v>304</v>
       </c>
       <c r="D104" t="s">
+        <v>434</v>
+      </c>
+      <c r="E104" t="s">
         <v>435</v>
-      </c>
-      <c r="E104" t="s">
-        <v>436</v>
       </c>
       <c r="F104" t="s">
         <v>307</v>
       </c>
       <c r="G104" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>53</v>
@@ -6585,12 +6591,12 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B105" t="s">
         <v>303</v>
@@ -6599,16 +6605,16 @@
         <v>304</v>
       </c>
       <c r="D105" t="s">
+        <v>438</v>
+      </c>
+      <c r="E105" t="s">
         <v>439</v>
-      </c>
-      <c r="E105" t="s">
-        <v>440</v>
       </c>
       <c r="F105" t="s">
         <v>307</v>
       </c>
       <c r="G105" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>53</v>
@@ -6617,12 +6623,12 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B106" t="s">
         <v>303</v>
@@ -6631,16 +6637,16 @@
         <v>304</v>
       </c>
       <c r="D106" t="s">
+        <v>442</v>
+      </c>
+      <c r="E106" t="s">
         <v>443</v>
-      </c>
-      <c r="E106" t="s">
-        <v>444</v>
       </c>
       <c r="F106" t="s">
         <v>307</v>
       </c>
       <c r="G106" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>53</v>
@@ -6649,31 +6655,31 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>445</v>
+      </c>
+      <c r="B107" t="s">
         <v>446</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>447</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>448</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>449</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>450</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>451</v>
       </c>
-      <c r="G107" t="s">
-        <v>452</v>
-      </c>
       <c r="H107" s="3" t="s">
         <v>53</v>
       </c>
@@ -6681,31 +6687,31 @@
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>452</v>
+      </c>
+      <c r="B108" t="s">
+        <v>446</v>
+      </c>
+      <c r="C108" t="s">
+        <v>447</v>
+      </c>
+      <c r="D108" t="s">
         <v>453</v>
       </c>
-      <c r="B108" t="s">
-        <v>447</v>
-      </c>
-      <c r="C108" t="s">
-        <v>448</v>
-      </c>
-      <c r="D108" t="s">
-        <v>454</v>
-      </c>
       <c r="E108" t="s">
+        <v>449</v>
+      </c>
+      <c r="F108" t="s">
         <v>450</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>451</v>
       </c>
-      <c r="G108" t="s">
-        <v>452</v>
-      </c>
       <c r="H108" s="3" t="s">
         <v>53</v>
       </c>
@@ -6713,31 +6719,31 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>454</v>
+      </c>
+      <c r="B109" t="s">
+        <v>446</v>
+      </c>
+      <c r="C109" t="s">
+        <v>447</v>
+      </c>
+      <c r="D109" t="s">
         <v>455</v>
       </c>
-      <c r="B109" t="s">
-        <v>447</v>
-      </c>
-      <c r="C109" t="s">
-        <v>448</v>
-      </c>
-      <c r="D109" t="s">
-        <v>456</v>
-      </c>
       <c r="E109" t="s">
+        <v>449</v>
+      </c>
+      <c r="F109" t="s">
         <v>450</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>451</v>
       </c>
-      <c r="G109" t="s">
-        <v>452</v>
-      </c>
       <c r="H109" s="3" t="s">
         <v>53</v>
       </c>
@@ -6745,31 +6751,31 @@
         <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>456</v>
+      </c>
+      <c r="B110" t="s">
+        <v>446</v>
+      </c>
+      <c r="C110" t="s">
+        <v>447</v>
+      </c>
+      <c r="D110" t="s">
         <v>457</v>
       </c>
-      <c r="B110" t="s">
-        <v>447</v>
-      </c>
-      <c r="C110" t="s">
-        <v>448</v>
-      </c>
-      <c r="D110" t="s">
-        <v>458</v>
-      </c>
       <c r="E110" t="s">
+        <v>449</v>
+      </c>
+      <c r="F110" t="s">
         <v>450</v>
       </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>451</v>
       </c>
-      <c r="G110" t="s">
-        <v>452</v>
-      </c>
       <c r="H110" s="3" t="s">
         <v>53</v>
       </c>
@@ -6777,31 +6783,31 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>458</v>
+      </c>
+      <c r="B111" t="s">
+        <v>446</v>
+      </c>
+      <c r="C111" t="s">
+        <v>447</v>
+      </c>
+      <c r="D111" t="s">
         <v>459</v>
       </c>
-      <c r="B111" t="s">
-        <v>447</v>
-      </c>
-      <c r="C111" t="s">
-        <v>448</v>
-      </c>
-      <c r="D111" t="s">
-        <v>460</v>
-      </c>
       <c r="E111" t="s">
+        <v>449</v>
+      </c>
+      <c r="F111" t="s">
         <v>450</v>
       </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>451</v>
       </c>
-      <c r="G111" t="s">
-        <v>452</v>
-      </c>
       <c r="H111" s="3" t="s">
         <v>53</v>
       </c>
@@ -6809,31 +6815,31 @@
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>460</v>
+      </c>
+      <c r="B112" t="s">
+        <v>446</v>
+      </c>
+      <c r="C112" t="s">
+        <v>447</v>
+      </c>
+      <c r="D112" t="s">
         <v>461</v>
       </c>
-      <c r="B112" t="s">
-        <v>447</v>
-      </c>
-      <c r="C112" t="s">
-        <v>448</v>
-      </c>
-      <c r="D112" t="s">
-        <v>462</v>
-      </c>
       <c r="E112" t="s">
+        <v>449</v>
+      </c>
+      <c r="F112" t="s">
         <v>450</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>451</v>
       </c>
-      <c r="G112" t="s">
-        <v>452</v>
-      </c>
       <c r="H112" s="3" t="s">
         <v>53</v>
       </c>
@@ -6841,31 +6847,31 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>462</v>
+      </c>
+      <c r="B113" t="s">
+        <v>446</v>
+      </c>
+      <c r="C113" t="s">
+        <v>447</v>
+      </c>
+      <c r="D113" t="s">
         <v>463</v>
       </c>
-      <c r="B113" t="s">
-        <v>447</v>
-      </c>
-      <c r="C113" t="s">
-        <v>448</v>
-      </c>
-      <c r="D113" t="s">
-        <v>464</v>
-      </c>
       <c r="E113" t="s">
+        <v>449</v>
+      </c>
+      <c r="F113" t="s">
         <v>450</v>
       </c>
-      <c r="F113" t="s">
+      <c r="G113" t="s">
         <v>451</v>
       </c>
-      <c r="G113" t="s">
-        <v>452</v>
-      </c>
       <c r="H113" s="3" t="s">
         <v>53</v>
       </c>
@@ -6873,31 +6879,31 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>464</v>
+      </c>
+      <c r="B114" t="s">
+        <v>446</v>
+      </c>
+      <c r="C114" t="s">
+        <v>447</v>
+      </c>
+      <c r="D114" t="s">
         <v>465</v>
       </c>
-      <c r="B114" t="s">
-        <v>447</v>
-      </c>
-      <c r="C114" t="s">
-        <v>448</v>
-      </c>
-      <c r="D114" t="s">
-        <v>466</v>
-      </c>
       <c r="E114" t="s">
+        <v>449</v>
+      </c>
+      <c r="F114" t="s">
         <v>450</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
         <v>451</v>
       </c>
-      <c r="G114" t="s">
-        <v>452</v>
-      </c>
       <c r="H114" s="3" t="s">
         <v>53</v>
       </c>
@@ -6905,31 +6911,31 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>466</v>
+      </c>
+      <c r="B115" t="s">
+        <v>446</v>
+      </c>
+      <c r="C115" t="s">
+        <v>447</v>
+      </c>
+      <c r="D115" t="s">
         <v>467</v>
       </c>
-      <c r="B115" t="s">
-        <v>447</v>
-      </c>
-      <c r="C115" t="s">
-        <v>448</v>
-      </c>
-      <c r="D115" t="s">
-        <v>468</v>
-      </c>
       <c r="E115" t="s">
+        <v>449</v>
+      </c>
+      <c r="F115" t="s">
         <v>450</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>451</v>
       </c>
-      <c r="G115" t="s">
-        <v>452</v>
-      </c>
       <c r="H115" s="3" t="s">
         <v>53</v>
       </c>
@@ -6937,31 +6943,31 @@
         <v>1</v>
       </c>
       <c r="J115" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>468</v>
+      </c>
+      <c r="B116" t="s">
+        <v>446</v>
+      </c>
+      <c r="C116" t="s">
+        <v>447</v>
+      </c>
+      <c r="D116" t="s">
         <v>469</v>
       </c>
-      <c r="B116" t="s">
-        <v>447</v>
-      </c>
-      <c r="C116" t="s">
-        <v>448</v>
-      </c>
-      <c r="D116" t="s">
-        <v>470</v>
-      </c>
       <c r="E116" t="s">
+        <v>449</v>
+      </c>
+      <c r="F116" t="s">
         <v>450</v>
       </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>451</v>
       </c>
-      <c r="G116" t="s">
-        <v>452</v>
-      </c>
       <c r="H116" s="3" t="s">
         <v>53</v>
       </c>
@@ -6969,31 +6975,31 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>470</v>
+      </c>
+      <c r="B117" t="s">
+        <v>446</v>
+      </c>
+      <c r="C117" t="s">
+        <v>447</v>
+      </c>
+      <c r="D117" t="s">
         <v>471</v>
       </c>
-      <c r="B117" t="s">
-        <v>447</v>
-      </c>
-      <c r="C117" t="s">
-        <v>448</v>
-      </c>
-      <c r="D117" t="s">
-        <v>472</v>
-      </c>
       <c r="E117" t="s">
+        <v>449</v>
+      </c>
+      <c r="F117" t="s">
         <v>450</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>451</v>
       </c>
-      <c r="G117" t="s">
-        <v>452</v>
-      </c>
       <c r="H117" s="3" t="s">
         <v>53</v>
       </c>
@@ -7001,31 +7007,31 @@
         <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>472</v>
+      </c>
+      <c r="B118" t="s">
+        <v>446</v>
+      </c>
+      <c r="C118" t="s">
+        <v>447</v>
+      </c>
+      <c r="D118" t="s">
         <v>473</v>
       </c>
-      <c r="B118" t="s">
-        <v>447</v>
-      </c>
-      <c r="C118" t="s">
-        <v>448</v>
-      </c>
-      <c r="D118" t="s">
-        <v>474</v>
-      </c>
       <c r="E118" t="s">
+        <v>449</v>
+      </c>
+      <c r="F118" t="s">
         <v>450</v>
       </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>451</v>
       </c>
-      <c r="G118" t="s">
-        <v>452</v>
-      </c>
       <c r="H118" s="3" t="s">
         <v>53</v>
       </c>
@@ -7033,31 +7039,31 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>474</v>
+      </c>
+      <c r="B119" t="s">
+        <v>446</v>
+      </c>
+      <c r="C119" t="s">
+        <v>447</v>
+      </c>
+      <c r="D119" t="s">
         <v>475</v>
       </c>
-      <c r="B119" t="s">
-        <v>447</v>
-      </c>
-      <c r="C119" t="s">
-        <v>448</v>
-      </c>
-      <c r="D119" t="s">
-        <v>476</v>
-      </c>
       <c r="E119" t="s">
+        <v>449</v>
+      </c>
+      <c r="F119" t="s">
         <v>450</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>451</v>
       </c>
-      <c r="G119" t="s">
-        <v>452</v>
-      </c>
       <c r="H119" s="3" t="s">
         <v>53</v>
       </c>
@@ -7065,31 +7071,31 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>476</v>
+      </c>
+      <c r="B120" t="s">
+        <v>446</v>
+      </c>
+      <c r="C120" t="s">
+        <v>447</v>
+      </c>
+      <c r="D120" t="s">
         <v>477</v>
       </c>
-      <c r="B120" t="s">
-        <v>447</v>
-      </c>
-      <c r="C120" t="s">
-        <v>448</v>
-      </c>
-      <c r="D120" t="s">
-        <v>478</v>
-      </c>
       <c r="E120" t="s">
+        <v>449</v>
+      </c>
+      <c r="F120" t="s">
         <v>450</v>
       </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>451</v>
       </c>
-      <c r="G120" t="s">
-        <v>452</v>
-      </c>
       <c r="H120" s="3" t="s">
         <v>53</v>
       </c>
@@ -7097,31 +7103,31 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>478</v>
+      </c>
+      <c r="B121" t="s">
+        <v>446</v>
+      </c>
+      <c r="C121" t="s">
+        <v>447</v>
+      </c>
+      <c r="D121" t="s">
         <v>479</v>
       </c>
-      <c r="B121" t="s">
-        <v>447</v>
-      </c>
-      <c r="C121" t="s">
-        <v>448</v>
-      </c>
-      <c r="D121" t="s">
-        <v>480</v>
-      </c>
       <c r="E121" t="s">
+        <v>449</v>
+      </c>
+      <c r="F121" t="s">
         <v>450</v>
       </c>
-      <c r="F121" t="s">
+      <c r="G121" t="s">
         <v>451</v>
       </c>
-      <c r="G121" t="s">
-        <v>452</v>
-      </c>
       <c r="H121" s="3" t="s">
         <v>53</v>
       </c>
@@ -7129,39 +7135,39 @@
         <v>1</v>
       </c>
       <c r="J121" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>480</v>
+      </c>
+      <c r="B122" t="s">
+        <v>446</v>
+      </c>
+      <c r="C122" t="s">
+        <v>447</v>
+      </c>
+      <c r="D122" t="s">
         <v>481</v>
       </c>
-      <c r="B122" t="s">
-        <v>447</v>
-      </c>
-      <c r="C122" t="s">
-        <v>448</v>
-      </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
+        <v>449</v>
+      </c>
+      <c r="F122" t="s">
+        <v>450</v>
+      </c>
+      <c r="G122" t="s">
+        <v>451</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122" t="s">
         <v>482</v>
-      </c>
-      <c r="E122" t="s">
-        <v>450</v>
-      </c>
-      <c r="F122" t="s">
-        <v>451</v>
-      </c>
-      <c r="G122" t="s">
-        <v>452</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I122">
-        <v>1</v>
-      </c>
-      <c r="J122" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -7169,23 +7175,23 @@
         <v>483</v>
       </c>
       <c r="B123" t="s">
+        <v>446</v>
+      </c>
+      <c r="C123" t="s">
         <v>447</v>
-      </c>
-      <c r="C123" t="s">
-        <v>448</v>
       </c>
       <c r="D123" t="s">
         <v>484</v>
       </c>
       <c r="E123" t="s">
+        <v>449</v>
+      </c>
+      <c r="F123" t="s">
         <v>450</v>
       </c>
-      <c r="F123" t="s">
+      <c r="G123" t="s">
         <v>451</v>
       </c>
-      <c r="G123" t="s">
-        <v>452</v>
-      </c>
       <c r="H123" s="3" t="s">
         <v>53</v>
       </c>
@@ -7193,7 +7199,7 @@
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -7201,23 +7207,23 @@
         <v>485</v>
       </c>
       <c r="B124" t="s">
+        <v>446</v>
+      </c>
+      <c r="C124" t="s">
         <v>447</v>
-      </c>
-      <c r="C124" t="s">
-        <v>448</v>
       </c>
       <c r="D124" t="s">
         <v>486</v>
       </c>
       <c r="E124" t="s">
+        <v>449</v>
+      </c>
+      <c r="F124" t="s">
         <v>450</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>451</v>
       </c>
-      <c r="G124" t="s">
-        <v>452</v>
-      </c>
       <c r="H124" s="3" t="s">
         <v>53</v>
       </c>
@@ -7225,7 +7231,7 @@
         <v>1</v>
       </c>
       <c r="J124" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -7233,23 +7239,23 @@
         <v>487</v>
       </c>
       <c r="B125" t="s">
+        <v>446</v>
+      </c>
+      <c r="C125" t="s">
         <v>447</v>
-      </c>
-      <c r="C125" t="s">
-        <v>448</v>
       </c>
       <c r="D125" t="s">
         <v>488</v>
       </c>
       <c r="E125" t="s">
+        <v>449</v>
+      </c>
+      <c r="F125" t="s">
         <v>450</v>
       </c>
-      <c r="F125" t="s">
+      <c r="G125" t="s">
         <v>451</v>
       </c>
-      <c r="G125" t="s">
-        <v>452</v>
-      </c>
       <c r="H125" s="3" t="s">
         <v>53</v>
       </c>
@@ -7257,7 +7263,7 @@
         <v>1</v>
       </c>
       <c r="J125" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -7265,23 +7271,23 @@
         <v>489</v>
       </c>
       <c r="B126" t="s">
+        <v>446</v>
+      </c>
+      <c r="C126" t="s">
         <v>447</v>
-      </c>
-      <c r="C126" t="s">
-        <v>448</v>
       </c>
       <c r="D126" t="s">
         <v>490</v>
       </c>
       <c r="E126" t="s">
+        <v>449</v>
+      </c>
+      <c r="F126" t="s">
         <v>450</v>
       </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
         <v>451</v>
       </c>
-      <c r="G126" t="s">
-        <v>452</v>
-      </c>
       <c r="H126" s="3" t="s">
         <v>53</v>
       </c>
@@ -7289,7 +7295,7 @@
         <v>1</v>
       </c>
       <c r="J126" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -7297,23 +7303,23 @@
         <v>491</v>
       </c>
       <c r="B127" t="s">
+        <v>446</v>
+      </c>
+      <c r="C127" t="s">
         <v>447</v>
-      </c>
-      <c r="C127" t="s">
-        <v>448</v>
       </c>
       <c r="D127" t="s">
         <v>492</v>
       </c>
       <c r="E127" t="s">
+        <v>449</v>
+      </c>
+      <c r="F127" t="s">
         <v>450</v>
       </c>
-      <c r="F127" t="s">
+      <c r="G127" t="s">
         <v>451</v>
       </c>
-      <c r="G127" t="s">
-        <v>452</v>
-      </c>
       <c r="H127" s="3" t="s">
         <v>53</v>
       </c>
@@ -7321,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="J127" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -7329,23 +7335,23 @@
         <v>493</v>
       </c>
       <c r="B128" t="s">
+        <v>446</v>
+      </c>
+      <c r="C128" t="s">
         <v>447</v>
-      </c>
-      <c r="C128" t="s">
-        <v>448</v>
       </c>
       <c r="D128" t="s">
         <v>494</v>
       </c>
       <c r="E128" t="s">
+        <v>449</v>
+      </c>
+      <c r="F128" t="s">
         <v>450</v>
       </c>
-      <c r="F128" t="s">
+      <c r="G128" t="s">
         <v>451</v>
       </c>
-      <c r="G128" t="s">
-        <v>452</v>
-      </c>
       <c r="H128" s="3" t="s">
         <v>53</v>
       </c>
@@ -7353,7 +7359,7 @@
         <v>1</v>
       </c>
       <c r="J128" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -7361,23 +7367,23 @@
         <v>495</v>
       </c>
       <c r="B129" t="s">
+        <v>446</v>
+      </c>
+      <c r="C129" t="s">
         <v>447</v>
-      </c>
-      <c r="C129" t="s">
-        <v>448</v>
       </c>
       <c r="D129" t="s">
         <v>496</v>
       </c>
       <c r="E129" t="s">
+        <v>449</v>
+      </c>
+      <c r="F129" t="s">
         <v>450</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
         <v>451</v>
       </c>
-      <c r="G129" t="s">
-        <v>452</v>
-      </c>
       <c r="H129" s="3" t="s">
         <v>53</v>
       </c>
@@ -7385,7 +7391,7 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -7393,23 +7399,23 @@
         <v>497</v>
       </c>
       <c r="B130" t="s">
+        <v>446</v>
+      </c>
+      <c r="C130" t="s">
         <v>447</v>
-      </c>
-      <c r="C130" t="s">
-        <v>448</v>
       </c>
       <c r="D130" t="s">
         <v>498</v>
       </c>
       <c r="E130" t="s">
+        <v>449</v>
+      </c>
+      <c r="F130" t="s">
         <v>450</v>
       </c>
-      <c r="F130" t="s">
+      <c r="G130" t="s">
         <v>451</v>
       </c>
-      <c r="G130" t="s">
-        <v>452</v>
-      </c>
       <c r="H130" s="3" t="s">
         <v>53</v>
       </c>
@@ -7417,7 +7423,7 @@
         <v>1</v>
       </c>
       <c r="J130" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -7425,23 +7431,23 @@
         <v>499</v>
       </c>
       <c r="B131" t="s">
+        <v>446</v>
+      </c>
+      <c r="C131" t="s">
         <v>447</v>
-      </c>
-      <c r="C131" t="s">
-        <v>448</v>
       </c>
       <c r="D131" t="s">
         <v>500</v>
       </c>
       <c r="E131" t="s">
+        <v>449</v>
+      </c>
+      <c r="F131" t="s">
         <v>450</v>
       </c>
-      <c r="F131" t="s">
+      <c r="G131" t="s">
         <v>451</v>
       </c>
-      <c r="G131" t="s">
-        <v>452</v>
-      </c>
       <c r="H131" s="3" t="s">
         <v>53</v>
       </c>
@@ -7449,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="J131" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -7457,23 +7463,23 @@
         <v>501</v>
       </c>
       <c r="B132" t="s">
+        <v>446</v>
+      </c>
+      <c r="C132" t="s">
         <v>447</v>
-      </c>
-      <c r="C132" t="s">
-        <v>448</v>
       </c>
       <c r="D132" t="s">
         <v>502</v>
       </c>
       <c r="E132" t="s">
+        <v>449</v>
+      </c>
+      <c r="F132" t="s">
         <v>450</v>
       </c>
-      <c r="F132" t="s">
+      <c r="G132" t="s">
         <v>451</v>
       </c>
-      <c r="G132" t="s">
-        <v>452</v>
-      </c>
       <c r="H132" s="3" t="s">
         <v>53</v>
       </c>
@@ -7481,7 +7487,7 @@
         <v>1</v>
       </c>
       <c r="J132" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -7489,23 +7495,23 @@
         <v>503</v>
       </c>
       <c r="B133" t="s">
+        <v>446</v>
+      </c>
+      <c r="C133" t="s">
         <v>447</v>
-      </c>
-      <c r="C133" t="s">
-        <v>448</v>
       </c>
       <c r="D133" t="s">
         <v>504</v>
       </c>
       <c r="E133" t="s">
+        <v>449</v>
+      </c>
+      <c r="F133" t="s">
         <v>450</v>
       </c>
-      <c r="F133" t="s">
+      <c r="G133" t="s">
         <v>451</v>
       </c>
-      <c r="G133" t="s">
-        <v>452</v>
-      </c>
       <c r="H133" s="3" t="s">
         <v>53</v>
       </c>
@@ -7513,7 +7519,7 @@
         <v>1</v>
       </c>
       <c r="J133" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -7521,23 +7527,23 @@
         <v>505</v>
       </c>
       <c r="B134" t="s">
+        <v>446</v>
+      </c>
+      <c r="C134" t="s">
         <v>447</v>
-      </c>
-      <c r="C134" t="s">
-        <v>448</v>
       </c>
       <c r="D134" t="s">
         <v>506</v>
       </c>
       <c r="E134" t="s">
+        <v>449</v>
+      </c>
+      <c r="F134" t="s">
         <v>450</v>
       </c>
-      <c r="F134" t="s">
+      <c r="G134" t="s">
         <v>451</v>
       </c>
-      <c r="G134" t="s">
-        <v>452</v>
-      </c>
       <c r="H134" s="3" t="s">
         <v>53</v>
       </c>
@@ -7545,7 +7551,7 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -7553,23 +7559,23 @@
         <v>507</v>
       </c>
       <c r="B135" t="s">
+        <v>446</v>
+      </c>
+      <c r="C135" t="s">
         <v>447</v>
-      </c>
-      <c r="C135" t="s">
-        <v>448</v>
       </c>
       <c r="D135" t="s">
         <v>508</v>
       </c>
       <c r="E135" t="s">
+        <v>449</v>
+      </c>
+      <c r="F135" t="s">
         <v>450</v>
       </c>
-      <c r="F135" t="s">
+      <c r="G135" t="s">
         <v>451</v>
       </c>
-      <c r="G135" t="s">
-        <v>452</v>
-      </c>
       <c r="H135" s="3" t="s">
         <v>53</v>
       </c>
@@ -7577,7 +7583,7 @@
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -7585,23 +7591,23 @@
         <v>509</v>
       </c>
       <c r="B136" t="s">
+        <v>446</v>
+      </c>
+      <c r="C136" t="s">
         <v>447</v>
-      </c>
-      <c r="C136" t="s">
-        <v>448</v>
       </c>
       <c r="D136" t="s">
         <v>510</v>
       </c>
       <c r="E136" t="s">
+        <v>449</v>
+      </c>
+      <c r="F136" t="s">
         <v>450</v>
       </c>
-      <c r="F136" t="s">
+      <c r="G136" t="s">
         <v>451</v>
       </c>
-      <c r="G136" t="s">
-        <v>452</v>
-      </c>
       <c r="H136" s="3" t="s">
         <v>53</v>
       </c>
@@ -7609,7 +7615,7 @@
         <v>1</v>
       </c>
       <c r="J136" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -7617,23 +7623,23 @@
         <v>511</v>
       </c>
       <c r="B137" t="s">
+        <v>446</v>
+      </c>
+      <c r="C137" t="s">
         <v>447</v>
-      </c>
-      <c r="C137" t="s">
-        <v>448</v>
       </c>
       <c r="D137" t="s">
         <v>512</v>
       </c>
       <c r="E137" t="s">
+        <v>449</v>
+      </c>
+      <c r="F137" t="s">
         <v>450</v>
       </c>
-      <c r="F137" t="s">
+      <c r="G137" t="s">
         <v>451</v>
       </c>
-      <c r="G137" t="s">
-        <v>452</v>
-      </c>
       <c r="H137" s="3" t="s">
         <v>53</v>
       </c>
@@ -7641,7 +7647,7 @@
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -7649,23 +7655,23 @@
         <v>513</v>
       </c>
       <c r="B138" t="s">
+        <v>446</v>
+      </c>
+      <c r="C138" t="s">
         <v>447</v>
-      </c>
-      <c r="C138" t="s">
-        <v>448</v>
       </c>
       <c r="D138" t="s">
         <v>514</v>
       </c>
       <c r="E138" t="s">
+        <v>449</v>
+      </c>
+      <c r="F138" t="s">
         <v>450</v>
       </c>
-      <c r="F138" t="s">
+      <c r="G138" t="s">
         <v>451</v>
       </c>
-      <c r="G138" t="s">
-        <v>452</v>
-      </c>
       <c r="H138" s="3" t="s">
         <v>53</v>
       </c>
@@ -7673,7 +7679,7 @@
         <v>1</v>
       </c>
       <c r="J138" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -7681,23 +7687,23 @@
         <v>515</v>
       </c>
       <c r="B139" t="s">
+        <v>446</v>
+      </c>
+      <c r="C139" t="s">
         <v>447</v>
-      </c>
-      <c r="C139" t="s">
-        <v>448</v>
       </c>
       <c r="D139" t="s">
         <v>516</v>
       </c>
       <c r="E139" t="s">
+        <v>449</v>
+      </c>
+      <c r="F139" t="s">
         <v>450</v>
       </c>
-      <c r="F139" t="s">
+      <c r="G139" t="s">
         <v>451</v>
       </c>
-      <c r="G139" t="s">
-        <v>452</v>
-      </c>
       <c r="H139" s="3" t="s">
         <v>53</v>
       </c>
@@ -7705,7 +7711,7 @@
         <v>1</v>
       </c>
       <c r="J139" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -7713,23 +7719,23 @@
         <v>517</v>
       </c>
       <c r="B140" t="s">
+        <v>446</v>
+      </c>
+      <c r="C140" t="s">
         <v>447</v>
-      </c>
-      <c r="C140" t="s">
-        <v>448</v>
       </c>
       <c r="D140" t="s">
         <v>518</v>
       </c>
       <c r="E140" t="s">
+        <v>449</v>
+      </c>
+      <c r="F140" t="s">
         <v>450</v>
       </c>
-      <c r="F140" t="s">
+      <c r="G140" t="s">
         <v>451</v>
       </c>
-      <c r="G140" t="s">
-        <v>452</v>
-      </c>
       <c r="H140" s="3" t="s">
         <v>53</v>
       </c>
@@ -7737,7 +7743,7 @@
         <v>1</v>
       </c>
       <c r="J140" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -7745,23 +7751,23 @@
         <v>519</v>
       </c>
       <c r="B141" t="s">
+        <v>446</v>
+      </c>
+      <c r="C141" t="s">
         <v>447</v>
-      </c>
-      <c r="C141" t="s">
-        <v>448</v>
       </c>
       <c r="D141" t="s">
         <v>520</v>
       </c>
       <c r="E141" t="s">
+        <v>449</v>
+      </c>
+      <c r="F141" t="s">
         <v>450</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>451</v>
       </c>
-      <c r="G141" t="s">
-        <v>452</v>
-      </c>
       <c r="H141" s="3" t="s">
         <v>53</v>
       </c>
@@ -7769,7 +7775,7 @@
         <v>1</v>
       </c>
       <c r="J141" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -7801,7 +7807,7 @@
         <v>1</v>
       </c>
       <c r="J142" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -7833,7 +7839,7 @@
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -7865,7 +7871,7 @@
         <v>1</v>
       </c>
       <c r="J144" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -7897,7 +7903,7 @@
         <v>1</v>
       </c>
       <c r="J145" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -7929,7 +7935,7 @@
         <v>1</v>
       </c>
       <c r="J146" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -7961,7 +7967,7 @@
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -7993,7 +7999,7 @@
         <v>1</v>
       </c>
       <c r="J148" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -8025,7 +8031,7 @@
         <v>1</v>
       </c>
       <c r="J149" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -8057,7 +8063,7 @@
         <v>1</v>
       </c>
       <c r="J150" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -8089,7 +8095,7 @@
         <v>1</v>
       </c>
       <c r="J151" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -8121,12 +8127,12 @@
         <v>1</v>
       </c>
       <c r="J152" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B153" t="s">
         <v>522</v>
@@ -8135,7 +8141,7 @@
         <v>523</v>
       </c>
       <c r="D153" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E153" t="s">
         <v>525</v>
@@ -8153,12 +8159,12 @@
         <v>1</v>
       </c>
       <c r="J153" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B154" t="s">
         <v>522</v>
@@ -8167,7 +8173,7 @@
         <v>523</v>
       </c>
       <c r="D154" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E154" t="s">
         <v>525</v>
@@ -8185,12 +8191,12 @@
         <v>1</v>
       </c>
       <c r="J154" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B155" t="s">
         <v>522</v>
@@ -8199,7 +8205,7 @@
         <v>523</v>
       </c>
       <c r="D155" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E155" t="s">
         <v>525</v>
@@ -8217,12 +8223,12 @@
         <v>1</v>
       </c>
       <c r="J155" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B156" t="s">
         <v>522</v>
@@ -8231,7 +8237,7 @@
         <v>523</v>
       </c>
       <c r="D156" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E156" t="s">
         <v>525</v>
@@ -8249,12 +8255,12 @@
         <v>1</v>
       </c>
       <c r="J156" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B157" t="s">
         <v>522</v>
@@ -8263,7 +8269,7 @@
         <v>523</v>
       </c>
       <c r="D157" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E157" t="s">
         <v>525</v>
@@ -8281,12 +8287,12 @@
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B158" t="s">
         <v>522</v>
@@ -8295,7 +8301,7 @@
         <v>523</v>
       </c>
       <c r="D158" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E158" t="s">
         <v>525</v>
@@ -8313,12 +8319,12 @@
         <v>1</v>
       </c>
       <c r="J158" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B159" t="s">
         <v>522</v>
@@ -8327,7 +8333,7 @@
         <v>523</v>
       </c>
       <c r="D159" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E159" t="s">
         <v>525</v>
@@ -8345,12 +8351,12 @@
         <v>1</v>
       </c>
       <c r="J159" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B160" t="s">
         <v>522</v>
@@ -8359,7 +8365,7 @@
         <v>523</v>
       </c>
       <c r="D160" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E160" t="s">
         <v>525</v>
@@ -8377,12 +8383,12 @@
         <v>1</v>
       </c>
       <c r="J160" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B161" t="s">
         <v>522</v>
@@ -8391,7 +8397,7 @@
         <v>523</v>
       </c>
       <c r="D161" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E161" t="s">
         <v>525</v>
@@ -8409,12 +8415,12 @@
         <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B162" t="s">
         <v>522</v>
@@ -8423,7 +8429,7 @@
         <v>523</v>
       </c>
       <c r="D162" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E162" t="s">
         <v>525</v>
@@ -8441,12 +8447,12 @@
         <v>1</v>
       </c>
       <c r="J162" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B163" t="s">
         <v>522</v>
@@ -8455,7 +8461,7 @@
         <v>523</v>
       </c>
       <c r="D163" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E163" t="s">
         <v>525</v>
@@ -8473,12 +8479,12 @@
         <v>1</v>
       </c>
       <c r="J163" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B164" t="s">
         <v>522</v>
@@ -8487,7 +8493,7 @@
         <v>523</v>
       </c>
       <c r="D164" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E164" t="s">
         <v>525</v>
@@ -8505,12 +8511,12 @@
         <v>1</v>
       </c>
       <c r="J164" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B165" t="s">
         <v>522</v>
@@ -8519,7 +8525,7 @@
         <v>523</v>
       </c>
       <c r="D165" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E165" t="s">
         <v>525</v>
@@ -8537,12 +8543,12 @@
         <v>1</v>
       </c>
       <c r="J165" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B166" t="s">
         <v>522</v>
@@ -8551,7 +8557,7 @@
         <v>523</v>
       </c>
       <c r="D166" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E166" t="s">
         <v>525</v>
@@ -8569,12 +8575,12 @@
         <v>1</v>
       </c>
       <c r="J166" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B167" t="s">
         <v>522</v>
@@ -8583,7 +8589,7 @@
         <v>523</v>
       </c>
       <c r="D167" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E167" t="s">
         <v>525</v>
@@ -8601,12 +8607,12 @@
         <v>1</v>
       </c>
       <c r="J167" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B168" t="s">
         <v>522</v>
@@ -8615,7 +8621,7 @@
         <v>523</v>
       </c>
       <c r="D168" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E168" t="s">
         <v>525</v>
@@ -8633,12 +8639,12 @@
         <v>1</v>
       </c>
       <c r="J168" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B169" t="s">
         <v>522</v>
@@ -8647,7 +8653,7 @@
         <v>523</v>
       </c>
       <c r="D169" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E169" t="s">
         <v>525</v>
@@ -8665,12 +8671,12 @@
         <v>1</v>
       </c>
       <c r="J169" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B170" t="s">
         <v>522</v>
@@ -8679,7 +8685,7 @@
         <v>523</v>
       </c>
       <c r="D170" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E170" t="s">
         <v>525</v>
@@ -8697,12 +8703,12 @@
         <v>1</v>
       </c>
       <c r="J170" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B171" t="s">
         <v>522</v>
@@ -8711,7 +8717,7 @@
         <v>523</v>
       </c>
       <c r="D171" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E171" t="s">
         <v>525</v>
@@ -8729,12 +8735,12 @@
         <v>1</v>
       </c>
       <c r="J171" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B172" t="s">
         <v>522</v>
@@ -8743,7 +8749,7 @@
         <v>523</v>
       </c>
       <c r="D172" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E172" t="s">
         <v>525</v>
@@ -8761,12 +8767,12 @@
         <v>1</v>
       </c>
       <c r="J172" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B173" t="s">
         <v>522</v>
@@ -8775,7 +8781,7 @@
         <v>523</v>
       </c>
       <c r="D173" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E173" t="s">
         <v>525</v>
@@ -8793,12 +8799,12 @@
         <v>1</v>
       </c>
       <c r="J173" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B174" t="s">
         <v>522</v>
@@ -8807,7 +8813,7 @@
         <v>523</v>
       </c>
       <c r="D174" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E174" t="s">
         <v>525</v>
@@ -8825,12 +8831,12 @@
         <v>1</v>
       </c>
       <c r="J174" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B175" t="s">
         <v>522</v>
@@ -8839,7 +8845,7 @@
         <v>523</v>
       </c>
       <c r="D175" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E175" t="s">
         <v>525</v>
@@ -8857,12 +8863,12 @@
         <v>1</v>
       </c>
       <c r="J175" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B176" t="s">
         <v>522</v>
@@ -8871,7 +8877,7 @@
         <v>523</v>
       </c>
       <c r="D176" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E176" t="s">
         <v>525</v>
@@ -8889,30 +8895,30 @@
         <v>1</v>
       </c>
       <c r="J176" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B177" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C177" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D177" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E177" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F177" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G177" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>53</v>
@@ -8921,31 +8927,31 @@
         <v>1</v>
       </c>
       <c r="J177" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>604</v>
+      </c>
+      <c r="B178" t="s">
+        <v>598</v>
+      </c>
+      <c r="C178" t="s">
+        <v>599</v>
+      </c>
+      <c r="D178" t="s">
+        <v>605</v>
+      </c>
+      <c r="E178" t="s">
+        <v>601</v>
+      </c>
+      <c r="F178" t="s">
+        <v>602</v>
+      </c>
+      <c r="G178" t="s">
         <v>603</v>
       </c>
-      <c r="B178" t="s">
-        <v>597</v>
-      </c>
-      <c r="C178" t="s">
-        <v>598</v>
-      </c>
-      <c r="D178" t="s">
-        <v>604</v>
-      </c>
-      <c r="E178" t="s">
-        <v>600</v>
-      </c>
-      <c r="F178" t="s">
-        <v>601</v>
-      </c>
-      <c r="G178" t="s">
-        <v>602</v>
-      </c>
       <c r="H178" s="3" t="s">
         <v>53</v>
       </c>
@@ -8953,30 +8959,30 @@
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B179" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C179" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D179" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E179" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F179" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G179" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>53</v>
@@ -8985,30 +8991,30 @@
         <v>1</v>
       </c>
       <c r="J179" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B180" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C180" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D180" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E180" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F180" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G180" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>53</v>
@@ -9017,30 +9023,30 @@
         <v>1</v>
       </c>
       <c r="J180" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B181" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C181" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D181" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E181" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F181" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G181" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H181" s="3" t="s">
         <v>53</v>
@@ -9049,30 +9055,30 @@
         <v>1</v>
       </c>
       <c r="J181" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B182" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C182" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D182" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E182" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F182" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G182" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>53</v>
@@ -9081,62 +9087,62 @@
         <v>1</v>
       </c>
       <c r="J182" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>615</v>
+      </c>
+      <c r="B183" t="s">
+        <v>598</v>
+      </c>
+      <c r="C183" t="s">
+        <v>599</v>
+      </c>
+      <c r="D183" t="s">
+        <v>616</v>
+      </c>
+      <c r="E183" t="s">
+        <v>601</v>
+      </c>
+      <c r="F183" t="s">
+        <v>602</v>
+      </c>
+      <c r="G183" t="s">
+        <v>603</v>
+      </c>
+      <c r="H183" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183" t="s">
         <v>614</v>
-      </c>
-      <c r="B183" t="s">
-        <v>597</v>
-      </c>
-      <c r="C183" t="s">
-        <v>598</v>
-      </c>
-      <c r="D183" t="s">
-        <v>615</v>
-      </c>
-      <c r="E183" t="s">
-        <v>600</v>
-      </c>
-      <c r="F183" t="s">
-        <v>601</v>
-      </c>
-      <c r="G183" t="s">
-        <v>602</v>
-      </c>
-      <c r="H183" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I183">
-        <v>1</v>
-      </c>
-      <c r="J183" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B184" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C184" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D184" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E184" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F184" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G184" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H184" s="3" t="s">
         <v>53</v>
@@ -9145,30 +9151,30 @@
         <v>1</v>
       </c>
       <c r="J184" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B185" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C185" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D185" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E185" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F185" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G185" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>53</v>
@@ -9177,30 +9183,30 @@
         <v>1</v>
       </c>
       <c r="J185" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B186" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C186" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D186" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E186" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F186" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G186" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>53</v>
@@ -9209,30 +9215,30 @@
         <v>1</v>
       </c>
       <c r="J186" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B187" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C187" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D187" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E187" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F187" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G187" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H187" s="3" t="s">
         <v>53</v>
@@ -9241,30 +9247,30 @@
         <v>1</v>
       </c>
       <c r="J187" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B188" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C188" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D188" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E188" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F188" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G188" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H188" s="3" t="s">
         <v>53</v>
@@ -9273,30 +9279,30 @@
         <v>1</v>
       </c>
       <c r="J188" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B189" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C189" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D189" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E189" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F189" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G189" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>53</v>
@@ -9305,30 +9311,30 @@
         <v>1</v>
       </c>
       <c r="J189" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B190" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C190" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D190" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E190" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F190" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G190" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H190" s="3" t="s">
         <v>53</v>
@@ -9337,30 +9343,30 @@
         <v>1</v>
       </c>
       <c r="J190" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B191" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C191" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D191" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E191" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F191" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G191" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H191" s="3" t="s">
         <v>53</v>
@@ -9369,30 +9375,30 @@
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B192" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C192" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D192" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E192" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F192" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G192" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H192" s="3" t="s">
         <v>53</v>
@@ -9401,30 +9407,30 @@
         <v>1</v>
       </c>
       <c r="J192" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B193" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C193" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D193" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E193" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F193" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G193" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>53</v>
@@ -9433,30 +9439,30 @@
         <v>1</v>
       </c>
       <c r="J193" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B194" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C194" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D194" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E194" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F194" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G194" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H194" s="3" t="s">
         <v>53</v>
@@ -9465,30 +9471,30 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B195" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C195" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D195" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E195" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F195" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G195" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H195" s="3" t="s">
         <v>53</v>
@@ -9497,30 +9503,30 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B196" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C196" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D196" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E196" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F196" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G196" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H196" s="3" t="s">
         <v>53</v>
@@ -9529,30 +9535,30 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B197" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C197" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D197" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E197" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F197" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G197" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H197" s="3" t="s">
         <v>53</v>
@@ -9561,30 +9567,30 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B198" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C198" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D198" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E198" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F198" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G198" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H198" s="3" t="s">
         <v>53</v>
@@ -9593,30 +9599,30 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B199" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C199" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D199" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E199" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F199" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G199" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H199" s="3" t="s">
         <v>53</v>
@@ -9625,30 +9631,30 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B200" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C200" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D200" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E200" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F200" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G200" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H200" s="3" t="s">
         <v>53</v>
@@ -9657,30 +9663,30 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B201" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C201" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D201" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E201" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F201" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G201" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H201" s="3" t="s">
         <v>53</v>
@@ -9689,30 +9695,30 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B202" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C202" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D202" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E202" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F202" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G202" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H202" s="3" t="s">
         <v>53</v>
@@ -9721,30 +9727,30 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B203" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C203" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D203" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E203" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F203" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G203" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H203" s="3" t="s">
         <v>53</v>
@@ -9753,30 +9759,30 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B204" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C204" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D204" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E204" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F204" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G204" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H204" s="3" t="s">
         <v>53</v>
@@ -9785,30 +9791,30 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B205" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C205" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D205" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E205" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F205" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G205" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H205" s="3" t="s">
         <v>53</v>
@@ -9817,30 +9823,30 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B206" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C206" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D206" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E206" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F206" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G206" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>53</v>
@@ -9849,30 +9855,30 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B207" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C207" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D207" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E207" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F207" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G207" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H207" s="3" t="s">
         <v>53</v>
@@ -9881,30 +9887,30 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B208" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C208" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D208" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E208" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F208" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G208" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H208" s="3" t="s">
         <v>53</v>
@@ -9913,30 +9919,30 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B209" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C209" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D209" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E209" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F209" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G209" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H209" s="3" t="s">
         <v>53</v>
@@ -9945,30 +9951,30 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B210" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C210" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D210" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E210" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F210" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G210" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H210" s="3" t="s">
         <v>53</v>
@@ -9977,30 +9983,30 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B211" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C211" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D211" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E211" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F211" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G211" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H211" s="3" t="s">
         <v>53</v>
@@ -10009,30 +10015,30 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B212" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C212" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D212" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E212" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F212" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G212" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H212" s="3" t="s">
         <v>53</v>
@@ -10041,31 +10047,31 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>680</v>
+      </c>
+      <c r="B213" t="s">
+        <v>674</v>
+      </c>
+      <c r="C213" t="s">
+        <v>675</v>
+      </c>
+      <c r="D213" t="s">
+        <v>681</v>
+      </c>
+      <c r="E213" t="s">
+        <v>677</v>
+      </c>
+      <c r="F213" t="s">
+        <v>678</v>
+      </c>
+      <c r="G213" t="s">
         <v>679</v>
       </c>
-      <c r="B213" t="s">
-        <v>673</v>
-      </c>
-      <c r="C213" t="s">
-        <v>674</v>
-      </c>
-      <c r="D213" t="s">
-        <v>680</v>
-      </c>
-      <c r="E213" t="s">
-        <v>676</v>
-      </c>
-      <c r="F213" t="s">
-        <v>677</v>
-      </c>
-      <c r="G213" t="s">
-        <v>678</v>
-      </c>
       <c r="H213" s="3" t="s">
         <v>53</v>
       </c>
@@ -10073,30 +10079,30 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B214" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C214" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D214" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E214" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F214" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G214" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H214" s="3" t="s">
         <v>53</v>
@@ -10105,30 +10111,30 @@
         <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B215" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C215" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D215" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E215" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F215" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G215" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H215" s="3" t="s">
         <v>53</v>
@@ -10137,30 +10143,30 @@
         <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B216" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C216" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D216" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E216" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F216" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G216" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H216" s="3" t="s">
         <v>53</v>
@@ -10169,30 +10175,30 @@
         <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B217" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C217" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D217" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E217" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F217" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G217" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H217" s="3" t="s">
         <v>53</v>
@@ -10201,30 +10207,30 @@
         <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B218" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C218" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D218" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E218" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F218" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G218" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H218" s="3" t="s">
         <v>53</v>
@@ -10233,30 +10239,30 @@
         <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B219" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C219" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D219" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E219" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F219" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G219" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H219" s="3" t="s">
         <v>53</v>
@@ -10265,30 +10271,30 @@
         <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B220" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C220" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D220" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E220" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F220" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G220" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H220" s="3" t="s">
         <v>53</v>
@@ -10297,30 +10303,30 @@
         <v>1</v>
       </c>
       <c r="J220" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B221" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C221" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D221" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E221" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F221" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G221" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H221" s="3" t="s">
         <v>53</v>
@@ -10329,30 +10335,30 @@
         <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B222" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C222" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D222" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E222" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F222" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G222" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H222" s="3" t="s">
         <v>53</v>
@@ -10361,30 +10367,30 @@
         <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B223" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C223" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D223" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E223" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F223" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G223" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H223" s="3" t="s">
         <v>53</v>
@@ -10393,30 +10399,30 @@
         <v>1</v>
       </c>
       <c r="J223" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B224" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C224" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D224" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E224" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F224" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G224" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H224" s="3" t="s">
         <v>53</v>
@@ -10425,30 +10431,30 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B225" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C225" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D225" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E225" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F225" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G225" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H225" s="3" t="s">
         <v>53</v>
@@ -10457,30 +10463,30 @@
         <v>1</v>
       </c>
       <c r="J225" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B226" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C226" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D226" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E226" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F226" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G226" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H226" s="3" t="s">
         <v>53</v>
@@ -10489,30 +10495,30 @@
         <v>1</v>
       </c>
       <c r="J226" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B227" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C227" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D227" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E227" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F227" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G227" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H227" s="3" t="s">
         <v>53</v>
@@ -10521,30 +10527,30 @@
         <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B228" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D228" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E228" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F228" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G228" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H228" s="3" t="s">
         <v>53</v>
@@ -10553,30 +10559,30 @@
         <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B229" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C229" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D229" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E229" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F229" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G229" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H229" s="3" t="s">
         <v>53</v>
@@ -10585,30 +10591,30 @@
         <v>1</v>
       </c>
       <c r="J229" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B230" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C230" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D230" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E230" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F230" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G230" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H230" s="3" t="s">
         <v>53</v>
@@ -10617,30 +10623,30 @@
         <v>1</v>
       </c>
       <c r="J230" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B231" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C231" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D231" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E231" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F231" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G231" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H231" s="3" t="s">
         <v>53</v>
@@ -10649,30 +10655,30 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B232" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C232" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D232" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E232" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F232" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G232" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H232" s="3" t="s">
         <v>53</v>
@@ -10681,30 +10687,30 @@
         <v>1</v>
       </c>
       <c r="J232" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B233" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C233" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D233" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E233" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F233" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G233" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H233" s="3" t="s">
         <v>53</v>
@@ -10713,30 +10719,30 @@
         <v>1</v>
       </c>
       <c r="J233" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B234" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C234" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D234" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E234" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F234" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G234" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H234" s="3" t="s">
         <v>53</v>
@@ -10745,30 +10751,30 @@
         <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B235" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C235" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D235" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E235" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F235" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G235" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H235" s="3" t="s">
         <v>53</v>
@@ -10777,30 +10783,30 @@
         <v>1</v>
       </c>
       <c r="J235" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B236" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C236" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D236" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E236" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F236" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G236" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H236" s="3" t="s">
         <v>53</v>
@@ -10809,30 +10815,30 @@
         <v>1</v>
       </c>
       <c r="J236" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B237" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C237" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D237" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E237" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F237" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G237" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H237" s="3" t="s">
         <v>53</v>
@@ -10841,30 +10847,30 @@
         <v>1</v>
       </c>
       <c r="J237" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B238" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C238" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D238" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E238" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F238" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G238" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H238" s="3" t="s">
         <v>53</v>
@@ -10873,30 +10879,30 @@
         <v>1</v>
       </c>
       <c r="J238" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B239" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C239" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D239" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E239" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F239" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G239" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H239" s="3" t="s">
         <v>53</v>
@@ -10905,30 +10911,30 @@
         <v>1</v>
       </c>
       <c r="J239" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B240" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C240" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D240" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E240" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F240" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G240" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H240" s="3" t="s">
         <v>53</v>
@@ -10937,30 +10943,30 @@
         <v>1</v>
       </c>
       <c r="J240" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B241" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C241" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D241" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E241" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F241" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G241" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H241" s="3" t="s">
         <v>53</v>
@@ -10969,30 +10975,30 @@
         <v>1</v>
       </c>
       <c r="J241" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B242" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C242" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D242" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E242" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F242" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G242" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H242" s="3" t="s">
         <v>53</v>
@@ -11001,31 +11007,31 @@
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>745</v>
+      </c>
+      <c r="B243" t="s">
+        <v>739</v>
+      </c>
+      <c r="C243" t="s">
+        <v>740</v>
+      </c>
+      <c r="D243" t="s">
+        <v>746</v>
+      </c>
+      <c r="E243" t="s">
+        <v>742</v>
+      </c>
+      <c r="F243" t="s">
+        <v>743</v>
+      </c>
+      <c r="G243" t="s">
         <v>744</v>
       </c>
-      <c r="B243" t="s">
-        <v>738</v>
-      </c>
-      <c r="C243" t="s">
-        <v>739</v>
-      </c>
-      <c r="D243" t="s">
-        <v>745</v>
-      </c>
-      <c r="E243" t="s">
-        <v>741</v>
-      </c>
-      <c r="F243" t="s">
-        <v>742</v>
-      </c>
-      <c r="G243" t="s">
-        <v>743</v>
-      </c>
       <c r="H243" s="3" t="s">
         <v>53</v>
       </c>
@@ -11033,30 +11039,30 @@
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B244" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C244" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D244" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E244" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F244" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G244" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H244" s="3" t="s">
         <v>53</v>
@@ -11065,30 +11071,30 @@
         <v>1</v>
       </c>
       <c r="J244" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B245" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C245" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D245" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E245" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F245" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G245" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H245" s="3" t="s">
         <v>53</v>
@@ -11097,30 +11103,30 @@
         <v>1</v>
       </c>
       <c r="J245" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B246" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C246" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D246" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E246" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F246" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G246" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H246" s="3" t="s">
         <v>53</v>
@@ -11129,30 +11135,30 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B247" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C247" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D247" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E247" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F247" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G247" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H247" s="3" t="s">
         <v>53</v>
@@ -11161,62 +11167,62 @@
         <v>1</v>
       </c>
       <c r="J247" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B248" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C248" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D248" t="s">
+        <v>757</v>
+      </c>
+      <c r="E248" t="s">
+        <v>742</v>
+      </c>
+      <c r="F248" t="s">
+        <v>743</v>
+      </c>
+      <c r="G248" t="s">
+        <v>744</v>
+      </c>
+      <c r="H248" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248" t="s">
         <v>755</v>
-      </c>
-      <c r="E248" t="s">
-        <v>741</v>
-      </c>
-      <c r="F248" t="s">
-        <v>742</v>
-      </c>
-      <c r="G248" t="s">
-        <v>743</v>
-      </c>
-      <c r="H248" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I248">
-        <v>1</v>
-      </c>
-      <c r="J248" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B249" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C249" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D249" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E249" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F249" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G249" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H249" s="3" t="s">
         <v>53</v>
@@ -11225,30 +11231,30 @@
         <v>1</v>
       </c>
       <c r="J249" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B250" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C250" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D250" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E250" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F250" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G250" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H250" s="3" t="s">
         <v>53</v>
@@ -11257,30 +11263,30 @@
         <v>1</v>
       </c>
       <c r="J250" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B251" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C251" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D251" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E251" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F251" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G251" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H251" s="3" t="s">
         <v>53</v>
@@ -11289,30 +11295,30 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B252" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C252" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D252" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E252" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F252" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G252" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H252" s="3" t="s">
         <v>53</v>
@@ -11321,30 +11327,30 @@
         <v>1</v>
       </c>
       <c r="J252" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B253" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C253" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D253" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E253" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F253" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G253" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H253" s="3" t="s">
         <v>53</v>
@@ -11353,30 +11359,30 @@
         <v>1</v>
       </c>
       <c r="J253" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B254" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C254" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D254" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="E254" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F254" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G254" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H254" s="3" t="s">
         <v>53</v>
@@ -11385,30 +11391,30 @@
         <v>1</v>
       </c>
       <c r="J254" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B255" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C255" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D255" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="E255" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F255" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G255" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H255" s="3" t="s">
         <v>53</v>
@@ -11417,30 +11423,30 @@
         <v>1</v>
       </c>
       <c r="J255" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B256" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C256" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D256" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E256" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F256" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G256" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H256" s="3" t="s">
         <v>53</v>
@@ -11449,30 +11455,30 @@
         <v>1</v>
       </c>
       <c r="J256" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B257" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C257" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D257" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E257" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F257" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G257" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H257" s="3" t="s">
         <v>53</v>
@@ -11481,30 +11487,30 @@
         <v>1</v>
       </c>
       <c r="J257" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B258" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C258" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D258" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="E258" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F258" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G258" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>53</v>
@@ -11513,30 +11519,30 @@
         <v>1</v>
       </c>
       <c r="J258" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B259" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C259" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D259" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="E259" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F259" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G259" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>53</v>
@@ -11545,30 +11551,30 @@
         <v>1</v>
       </c>
       <c r="J259" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B260" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C260" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D260" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E260" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F260" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G260" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>53</v>
@@ -11577,30 +11583,30 @@
         <v>1</v>
       </c>
       <c r="J260" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B261" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C261" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D261" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E261" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F261" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G261" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>53</v>
@@ -11609,30 +11615,30 @@
         <v>1</v>
       </c>
       <c r="J261" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B262" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C262" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D262" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="E262" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F262" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G262" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H262" s="3" t="s">
         <v>53</v>
@@ -11641,30 +11647,30 @@
         <v>1</v>
       </c>
       <c r="J262" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B263" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C263" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D263" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E263" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F263" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G263" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H263" s="3" t="s">
         <v>53</v>
@@ -11673,30 +11679,30 @@
         <v>1</v>
       </c>
       <c r="J263" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B264" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C264" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D264" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="E264" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F264" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G264" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H264" s="3" t="s">
         <v>53</v>
@@ -11705,30 +11711,30 @@
         <v>1</v>
       </c>
       <c r="J264" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B265" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C265" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D265" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E265" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F265" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G265" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H265" s="3" t="s">
         <v>53</v>
@@ -11737,30 +11743,30 @@
         <v>1</v>
       </c>
       <c r="J265" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B266" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C266" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D266" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="E266" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F266" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G266" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H266" s="3" t="s">
         <v>53</v>
@@ -11769,30 +11775,30 @@
         <v>1</v>
       </c>
       <c r="J266" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B267" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C267" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D267" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E267" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F267" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G267" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H267" s="3" t="s">
         <v>53</v>
@@ -11801,30 +11807,30 @@
         <v>1</v>
       </c>
       <c r="J267" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B268" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C268" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D268" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E268" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F268" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G268" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H268" s="3" t="s">
         <v>53</v>
@@ -11833,30 +11839,30 @@
         <v>1</v>
       </c>
       <c r="J268" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B269" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C269" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D269" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="E269" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F269" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G269" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H269" s="3" t="s">
         <v>53</v>
@@ -11865,30 +11871,30 @@
         <v>1</v>
       </c>
       <c r="J269" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B270" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C270" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D270" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E270" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F270" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G270" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H270" s="3" t="s">
         <v>53</v>
@@ -11897,30 +11903,30 @@
         <v>1</v>
       </c>
       <c r="J270" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B271" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C271" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D271" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E271" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F271" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G271" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H271" s="3" t="s">
         <v>53</v>
@@ -11929,30 +11935,30 @@
         <v>1</v>
       </c>
       <c r="J271" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B272" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C272" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D272" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="E272" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F272" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G272" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H272" s="3" t="s">
         <v>53</v>
@@ -11961,31 +11967,31 @@
         <v>1</v>
       </c>
       <c r="J272" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>811</v>
+      </c>
+      <c r="B273" t="s">
+        <v>805</v>
+      </c>
+      <c r="C273" t="s">
+        <v>806</v>
+      </c>
+      <c r="D273" t="s">
+        <v>812</v>
+      </c>
+      <c r="E273" t="s">
+        <v>808</v>
+      </c>
+      <c r="F273" t="s">
         <v>809</v>
       </c>
-      <c r="B273" t="s">
-        <v>803</v>
-      </c>
-      <c r="C273" t="s">
-        <v>804</v>
-      </c>
-      <c r="D273" t="s">
+      <c r="G273" t="s">
         <v>810</v>
       </c>
-      <c r="E273" t="s">
-        <v>806</v>
-      </c>
-      <c r="F273" t="s">
-        <v>807</v>
-      </c>
-      <c r="G273" t="s">
-        <v>808</v>
-      </c>
       <c r="H273" s="3" t="s">
         <v>53</v>
       </c>
@@ -11993,30 +11999,30 @@
         <v>1</v>
       </c>
       <c r="J273" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B274" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C274" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D274" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E274" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F274" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G274" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H274" s="3" t="s">
         <v>53</v>
@@ -12025,30 +12031,30 @@
         <v>1</v>
       </c>
       <c r="J274" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B275" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C275" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D275" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E275" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F275" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G275" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H275" s="3" t="s">
         <v>53</v>
@@ -12057,30 +12063,30 @@
         <v>1</v>
       </c>
       <c r="J275" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B276" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C276" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D276" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="E276" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F276" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G276" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H276" s="3" t="s">
         <v>53</v>
@@ -12089,30 +12095,30 @@
         <v>1</v>
       </c>
       <c r="J276" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B277" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C277" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D277" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E277" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F277" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G277" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H277" s="3" t="s">
         <v>53</v>
@@ -12121,30 +12127,30 @@
         <v>1</v>
       </c>
       <c r="J277" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B278" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C278" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D278" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="E278" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F278" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G278" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H278" s="3" t="s">
         <v>53</v>
@@ -12153,30 +12159,30 @@
         <v>1</v>
       </c>
       <c r="J278" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B279" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C279" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D279" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E279" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F279" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G279" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H279" s="3" t="s">
         <v>53</v>
@@ -12185,30 +12191,30 @@
         <v>1</v>
       </c>
       <c r="J279" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B280" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C280" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D280" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="E280" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F280" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G280" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H280" s="3" t="s">
         <v>53</v>
@@ -12217,30 +12223,30 @@
         <v>1</v>
       </c>
       <c r="J280" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B281" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C281" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D281" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="E281" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F281" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G281" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H281" s="3" t="s">
         <v>53</v>
@@ -12249,30 +12255,30 @@
         <v>1</v>
       </c>
       <c r="J281" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B282" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C282" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D282" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E282" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F282" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G282" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H282" s="3" t="s">
         <v>53</v>
@@ -12281,30 +12287,30 @@
         <v>1</v>
       </c>
       <c r="J282" t="s">
-        <v>613</v>
+        <v>755</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B283" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C283" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D283" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="E283" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F283" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G283" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H283" s="3" t="s">
         <v>53</v>
@@ -12313,30 +12319,30 @@
         <v>1</v>
       </c>
       <c r="J283" t="s">
-        <v>831</v>
+        <v>755</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B284" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C284" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D284" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E284" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F284" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G284" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H284" s="3" t="s">
         <v>53</v>
@@ -12345,30 +12351,30 @@
         <v>1</v>
       </c>
       <c r="J284" t="s">
-        <v>831</v>
+        <v>755</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B285" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C285" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D285" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E285" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F285" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G285" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H285" s="3" t="s">
         <v>53</v>
@@ -12377,30 +12383,30 @@
         <v>1</v>
       </c>
       <c r="J285" t="s">
-        <v>831</v>
+        <v>755</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B286" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C286" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D286" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E286" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F286" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G286" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H286" s="3" t="s">
         <v>53</v>
@@ -12409,30 +12415,30 @@
         <v>1</v>
       </c>
       <c r="J286" t="s">
-        <v>831</v>
+        <v>755</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B287" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C287" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D287" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E287" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F287" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G287" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H287" s="3" t="s">
         <v>53</v>
@@ -12441,30 +12447,30 @@
         <v>1</v>
       </c>
       <c r="J287" t="s">
-        <v>831</v>
+        <v>755</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B288" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C288" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D288" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E288" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F288" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G288" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H288" s="3" t="s">
         <v>53</v>
@@ -12473,30 +12479,30 @@
         <v>1</v>
       </c>
       <c r="J288" t="s">
-        <v>831</v>
+        <v>755</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B289" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C289" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D289" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E289" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F289" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G289" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H289" s="3" t="s">
         <v>53</v>
@@ -12505,30 +12511,30 @@
         <v>1</v>
       </c>
       <c r="J289" t="s">
-        <v>831</v>
+        <v>755</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B290" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C290" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D290" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E290" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F290" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G290" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H290" s="3" t="s">
         <v>53</v>
@@ -12537,30 +12543,30 @@
         <v>1</v>
       </c>
       <c r="J290" t="s">
-        <v>831</v>
+        <v>755</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B291" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C291" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D291" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E291" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F291" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G291" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H291" s="3" t="s">
         <v>53</v>
@@ -12569,30 +12575,30 @@
         <v>1</v>
       </c>
       <c r="J291" t="s">
-        <v>831</v>
+        <v>755</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B292" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C292" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D292" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E292" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F292" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G292" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H292" s="3" t="s">
         <v>53</v>
@@ -12601,30 +12607,30 @@
         <v>1</v>
       </c>
       <c r="J292" t="s">
-        <v>831</v>
+        <v>755</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B293" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C293" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D293" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E293" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F293" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G293" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H293" s="3" t="s">
         <v>53</v>
@@ -12633,62 +12639,62 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>831</v>
+        <v>853</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B294" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C294" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D294" t="s">
+        <v>855</v>
+      </c>
+      <c r="E294" t="s">
+        <v>808</v>
+      </c>
+      <c r="F294" t="s">
+        <v>809</v>
+      </c>
+      <c r="G294" t="s">
+        <v>810</v>
+      </c>
+      <c r="H294" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+      <c r="J294" t="s">
         <v>853</v>
-      </c>
-      <c r="E294" t="s">
-        <v>806</v>
-      </c>
-      <c r="F294" t="s">
-        <v>807</v>
-      </c>
-      <c r="G294" t="s">
-        <v>808</v>
-      </c>
-      <c r="H294" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I294">
-        <v>1</v>
-      </c>
-      <c r="J294" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B295" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C295" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D295" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="E295" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F295" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G295" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H295" s="3" t="s">
         <v>53</v>
@@ -12697,30 +12703,30 @@
         <v>1</v>
       </c>
       <c r="J295" t="s">
-        <v>831</v>
+        <v>853</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B296" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C296" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D296" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="E296" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F296" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G296" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>53</v>
@@ -12729,30 +12735,30 @@
         <v>1</v>
       </c>
       <c r="J296" t="s">
-        <v>831</v>
+        <v>853</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B297" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C297" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D297" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E297" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F297" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G297" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H297" s="3" t="s">
         <v>53</v>
@@ -12761,30 +12767,30 @@
         <v>1</v>
       </c>
       <c r="J297" t="s">
-        <v>831</v>
+        <v>853</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B298" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C298" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D298" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="E298" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F298" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G298" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H298" s="3" t="s">
         <v>53</v>
@@ -12793,30 +12799,30 @@
         <v>1</v>
       </c>
       <c r="J298" t="s">
-        <v>831</v>
+        <v>853</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B299" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C299" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D299" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="E299" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F299" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G299" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H299" s="3" t="s">
         <v>53</v>
@@ -12825,30 +12831,30 @@
         <v>1</v>
       </c>
       <c r="J299" t="s">
-        <v>831</v>
+        <v>853</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B300" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C300" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D300" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="E300" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F300" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G300" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H300" s="3" t="s">
         <v>53</v>
@@ -12857,30 +12863,30 @@
         <v>1</v>
       </c>
       <c r="J300" t="s">
-        <v>831</v>
+        <v>853</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B301" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C301" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D301" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="E301" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F301" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G301" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H301" s="3" t="s">
         <v>53</v>
@@ -12889,7 +12895,7 @@
         <v>1</v>
       </c>
       <c r="J301" t="s">
-        <v>831</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>
